--- a/public/docs/datas/world.xlsx
+++ b/public/docs/datas/world.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Docs\byMe\vue_platform\public\docs\datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395A9257-E367-4E4B-8170-E0757B742B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28815" yWindow="-2190" windowWidth="23325" windowHeight="17730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28260" windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="382">
   <si>
     <t>no</t>
   </si>
@@ -36,31 +38,1508 @@
     <t>name</t>
   </si>
   <si>
+    <t>fullName</t>
+  </si>
+  <si>
+    <t>enName</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>enCity</t>
+  </si>
+  <si>
+    <t>continent</t>
+  </si>
+  <si>
+    <t>partition</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
     <t>country</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>中华人民共和国</t>
+  </si>
+  <si>
+    <t>the People's Republic of China</t>
+  </si>
+  <si>
+    <t>China.png</t>
+  </si>
+  <si>
+    <t>北京</t>
+  </si>
+  <si>
+    <t>Beijing</t>
+  </si>
+  <si>
+    <t>亚洲</t>
+  </si>
+  <si>
+    <t>东亚</t>
+  </si>
+  <si>
+    <t>CHN</t>
+  </si>
+  <si>
+    <t>日本</t>
+  </si>
+  <si>
+    <t>日本国</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Japan.png</t>
+  </si>
+  <si>
+    <t>东京</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>JPN</t>
+  </si>
+  <si>
+    <t>朝鲜</t>
+  </si>
+  <si>
+    <t>朝鲜民主主义人民共和国</t>
+  </si>
+  <si>
+    <t>Democratic People's Republic of Korea</t>
+  </si>
+  <si>
+    <t>NorthKorea.png</t>
+  </si>
+  <si>
+    <t>平壤</t>
+  </si>
+  <si>
+    <t>Pyongyang</t>
+  </si>
+  <si>
+    <t>PRK</t>
+  </si>
+  <si>
+    <t>韩国</t>
+  </si>
+  <si>
+    <t>大韩民国</t>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
+  </si>
+  <si>
+    <t>Korea.png</t>
+  </si>
+  <si>
+    <t>首尔</t>
+  </si>
+  <si>
+    <t>Seoul</t>
+  </si>
+  <si>
+    <t>KOR</t>
+  </si>
+  <si>
+    <t>蒙古</t>
+  </si>
+  <si>
+    <t>蒙古国</t>
+  </si>
+  <si>
+    <t>Mongolia</t>
+  </si>
+  <si>
+    <t>Mongolia.png</t>
+  </si>
+  <si>
+    <t>乌兰巴托</t>
+  </si>
+  <si>
+    <t>Ulaanbaatar</t>
+  </si>
+  <si>
+    <t>MNG</t>
+  </si>
+  <si>
+    <t>俄罗斯</t>
+  </si>
+  <si>
+    <t>俄罗斯联邦</t>
+  </si>
+  <si>
+    <t>Russian Federation</t>
+  </si>
+  <si>
+    <t>Russia.png</t>
+  </si>
+  <si>
+    <t>莫斯科</t>
+  </si>
+  <si>
+    <t>欧洲</t>
+  </si>
+  <si>
+    <t>东欧</t>
+  </si>
+  <si>
+    <t>RUS</t>
+  </si>
+  <si>
+    <t>缅甸</t>
+  </si>
+  <si>
+    <t>东南亚</t>
+  </si>
+  <si>
+    <t>文莱</t>
+  </si>
+  <si>
+    <t>柬埔寨</t>
+  </si>
+  <si>
+    <t>东帝汶</t>
+  </si>
+  <si>
+    <t>印度尼西亚</t>
+  </si>
+  <si>
+    <t>老挝</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Malaysia.png</t>
+  </si>
+  <si>
+    <t>吉隆坡</t>
+  </si>
+  <si>
+    <t>MYS</t>
+  </si>
+  <si>
+    <t>菲律宾</t>
+  </si>
+  <si>
+    <t>新加坡</t>
+  </si>
+  <si>
+    <t>新加坡共和国</t>
+  </si>
+  <si>
+    <t>Republic of Singapore</t>
+  </si>
+  <si>
+    <t>Singapore.png</t>
+  </si>
+  <si>
+    <t>新加坡市</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>泰国</t>
+  </si>
+  <si>
+    <t>泰王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Thailand</t>
+  </si>
+  <si>
+    <t>Thailand.png</t>
+  </si>
+  <si>
+    <t>曼谷</t>
+  </si>
+  <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>越南</t>
+  </si>
+  <si>
+    <t>孟加拉国</t>
+  </si>
+  <si>
+    <t>南亚</t>
+  </si>
+  <si>
+    <t>不丹</t>
+  </si>
+  <si>
+    <t>印度</t>
+  </si>
+  <si>
+    <t>印度共和国</t>
+  </si>
+  <si>
+    <t>The Republic of India</t>
+  </si>
+  <si>
+    <t>India.png</t>
+  </si>
+  <si>
+    <t>新德里</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>马尔代夫</t>
+  </si>
+  <si>
+    <t>尼泊尔</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>斯里兰卡</t>
+  </si>
+  <si>
+    <t>哈萨克斯坦</t>
+  </si>
+  <si>
+    <t>中亚</t>
+  </si>
+  <si>
+    <t>吉尔吉斯斯坦</t>
+  </si>
+  <si>
+    <t>塔吉克斯坦</t>
+  </si>
+  <si>
+    <t>土库曼斯坦</t>
+  </si>
+  <si>
+    <t>乌兹别克斯坦</t>
+  </si>
+  <si>
+    <t>阿富汗</t>
+  </si>
+  <si>
+    <t>西亚</t>
+  </si>
+  <si>
+    <t>亚美尼亚</t>
+  </si>
+  <si>
+    <t>阿塞拜疆</t>
+  </si>
+  <si>
+    <t>阿塞拜疆共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Azerbaijan</t>
+  </si>
+  <si>
+    <t>Azerbaijan.png</t>
+  </si>
+  <si>
+    <t>巴库</t>
+  </si>
+  <si>
+    <t>AZE</t>
+  </si>
+  <si>
+    <t>巴林</t>
+  </si>
+  <si>
+    <t>巴林王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Bahrain</t>
+  </si>
+  <si>
+    <t>Bahrain.png</t>
+  </si>
+  <si>
+    <t>麦纳麦</t>
+  </si>
+  <si>
+    <t>BHR</t>
+  </si>
+  <si>
+    <t>塞浦路斯</t>
+  </si>
+  <si>
+    <t>格鲁吉亚</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>伊朗伊斯兰共和国</t>
+  </si>
+  <si>
+    <t>The Islamic Republic of Iran</t>
+  </si>
+  <si>
+    <t>Iran.png</t>
+  </si>
+  <si>
+    <t>德黑兰</t>
+  </si>
+  <si>
+    <t>IRN</t>
+  </si>
+  <si>
+    <t>伊拉克</t>
+  </si>
+  <si>
+    <t>以色列</t>
+  </si>
+  <si>
+    <t>以色列国</t>
+  </si>
+  <si>
+    <t>The State of Israel</t>
+  </si>
+  <si>
+    <t>Israel.png</t>
+  </si>
+  <si>
+    <t>耶路撒冷</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
+    <t>约旦</t>
+  </si>
+  <si>
+    <t>科威特</t>
+  </si>
+  <si>
+    <t>黎巴嫩</t>
+  </si>
+  <si>
+    <t>阿曼</t>
+  </si>
+  <si>
+    <t>巴勒斯坦</t>
+  </si>
+  <si>
+    <t>卡塔尔</t>
+  </si>
+  <si>
+    <t>卡塔尔国</t>
+  </si>
+  <si>
+    <t>The State of Qatar</t>
+  </si>
+  <si>
+    <t>Qatar.png</t>
+  </si>
+  <si>
+    <t>多哈</t>
+  </si>
+  <si>
+    <t>QAT</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>土耳其</t>
+  </si>
+  <si>
+    <t>土耳其共和国</t>
+  </si>
+  <si>
+    <t>Republic of Türkiye</t>
+  </si>
+  <si>
+    <t>Türkiye.png</t>
+  </si>
+  <si>
+    <t>安卡拉</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>阿拉伯联合酋长国</t>
+  </si>
+  <si>
+    <t>The United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Abu Dhabi.png</t>
+  </si>
+  <si>
+    <t>阿布扎比</t>
+  </si>
+  <si>
+    <t>Abu Dhabi</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>也门</t>
+  </si>
+  <si>
+    <t>比利时</t>
+  </si>
+  <si>
+    <t>比利时王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Belgium</t>
+  </si>
+  <si>
+    <t>Belgium.png</t>
+  </si>
+  <si>
+    <t>布鲁塞尔</t>
+  </si>
+  <si>
+    <t>西欧</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>法国</t>
+  </si>
+  <si>
+    <t>法兰西共和国</t>
+  </si>
+  <si>
+    <t>The French Republic</t>
+  </si>
+  <si>
+    <t>France.png</t>
+  </si>
+  <si>
+    <t>巴黎</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>爱尔兰</t>
+  </si>
+  <si>
+    <t>卢森堡</t>
+  </si>
+  <si>
+    <t>摩纳哥</t>
+  </si>
+  <si>
+    <t>摩纳哥公国</t>
+  </si>
+  <si>
+    <t>The Principality of Monaco</t>
+  </si>
+  <si>
+    <t>Monaco.png</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>荷兰</t>
+  </si>
+  <si>
+    <t>英国</t>
+  </si>
+  <si>
+    <t>丹麦</t>
+  </si>
+  <si>
+    <t>北欧</t>
+  </si>
+  <si>
+    <t>芬兰</t>
+  </si>
+  <si>
+    <t>芬兰共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Finland</t>
+  </si>
+  <si>
+    <t>Finland.png</t>
+  </si>
+  <si>
+    <t>赫尔辛基</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>冰岛</t>
+  </si>
+  <si>
+    <t>挪威</t>
+  </si>
+  <si>
+    <t>瑞典</t>
+  </si>
+  <si>
+    <t>白俄罗斯</t>
+  </si>
+  <si>
+    <t>爱沙尼亚</t>
+  </si>
+  <si>
+    <t>拉脱维亚</t>
+  </si>
+  <si>
+    <t>立陶宛</t>
+  </si>
+  <si>
+    <t>摩尔多瓦</t>
+  </si>
+  <si>
+    <t>乌克兰</t>
+  </si>
+  <si>
+    <t>德国</t>
+  </si>
+  <si>
+    <t>德意志联邦共和国</t>
+  </si>
+  <si>
+    <t>Federal Republic of Germany</t>
+  </si>
+  <si>
+    <t>Germany.png</t>
+  </si>
+  <si>
+    <t>柏林</t>
+  </si>
+  <si>
+    <t>中欧</t>
+  </si>
+  <si>
+    <t>DEU</t>
+  </si>
+  <si>
+    <t>波兰</t>
+  </si>
+  <si>
+    <t>斯洛伐克</t>
+  </si>
+  <si>
+    <t>匈牙利</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Hungary.png</t>
+  </si>
+  <si>
+    <t>布达佩斯</t>
+  </si>
+  <si>
+    <t>HUN</t>
+  </si>
+  <si>
+    <t>奥地利</t>
+  </si>
+  <si>
+    <t>奥地利共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Austria</t>
+  </si>
+  <si>
+    <t>Austria.png</t>
+  </si>
+  <si>
+    <t>维也纳</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>捷克</t>
+  </si>
+  <si>
+    <t>列支敦士登</t>
+  </si>
+  <si>
+    <t>瑞士</t>
+  </si>
+  <si>
+    <t>阿尔巴里亚</t>
+  </si>
+  <si>
+    <t>南欧</t>
+  </si>
+  <si>
+    <t>安道尔</t>
+  </si>
+  <si>
+    <t>波斯尼亚和黑塞哥维那</t>
+  </si>
+  <si>
+    <t>保加利亚</t>
+  </si>
+  <si>
+    <t>克罗地亚</t>
+  </si>
+  <si>
+    <t>希腊</t>
+  </si>
+  <si>
+    <t>意大利</t>
+  </si>
+  <si>
+    <t>意大利共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Italy</t>
+  </si>
+  <si>
+    <t>Italy.png</t>
+  </si>
+  <si>
+    <t>罗马</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>北马其顿</t>
+  </si>
+  <si>
+    <t>马耳他</t>
+  </si>
+  <si>
+    <t>黑山</t>
+  </si>
+  <si>
+    <t>葡萄牙</t>
+  </si>
+  <si>
+    <t>罗马尼亚</t>
+  </si>
+  <si>
+    <t>圣马力诺</t>
+  </si>
+  <si>
+    <t>塞尔维亚</t>
+  </si>
+  <si>
+    <t>斯洛文尼亚</t>
+  </si>
+  <si>
+    <t>西班牙</t>
+  </si>
+  <si>
+    <t>梵蒂冈</t>
+  </si>
+  <si>
+    <t>加拿大</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Canada.png</t>
+  </si>
+  <si>
+    <t>渥太华</t>
+  </si>
+  <si>
+    <t>北美州</t>
+  </si>
+  <si>
+    <t>北美</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>美国</t>
+  </si>
+  <si>
+    <t>墨西哥</t>
+  </si>
+  <si>
+    <t>墨西哥合众国</t>
+  </si>
+  <si>
+    <t>The United Mexican States</t>
+  </si>
+  <si>
+    <t>Mexico.png</t>
+  </si>
+  <si>
+    <t>墨西哥城</t>
+  </si>
+  <si>
+    <t>中美</t>
+  </si>
+  <si>
+    <t>MEX</t>
+  </si>
+  <si>
+    <t>伯利兹</t>
+  </si>
+  <si>
+    <t>哥斯达黎加</t>
+  </si>
+  <si>
+    <t>萨尔瓦多</t>
+  </si>
+  <si>
+    <t>危地马拉</t>
+  </si>
+  <si>
+    <t>洪都拉斯</t>
+  </si>
+  <si>
+    <t>尼加拉瓜</t>
+  </si>
+  <si>
+    <t>巴拿马</t>
+  </si>
+  <si>
+    <t>安提瓜和巴布达</t>
+  </si>
+  <si>
+    <t>加勒比</t>
+  </si>
+  <si>
+    <t>巴哈马</t>
+  </si>
+  <si>
+    <t>巴巴多斯</t>
+  </si>
+  <si>
+    <t>古巴</t>
+  </si>
+  <si>
+    <t>多米尼克</t>
+  </si>
+  <si>
+    <t>多米尼加</t>
+  </si>
+  <si>
+    <t>格林纳达</t>
+  </si>
+  <si>
+    <t>海地</t>
+  </si>
+  <si>
+    <t>牙买加</t>
+  </si>
+  <si>
+    <t>圣基茨和尼维斯</t>
+  </si>
+  <si>
+    <t>圣卢西亚</t>
+  </si>
+  <si>
+    <t>圣文森特和格林纳丁斯</t>
+  </si>
+  <si>
+    <t>特立尼达和多巴哥</t>
+  </si>
+  <si>
+    <t>阿根廷</t>
+  </si>
+  <si>
+    <t>Republic of Argentina</t>
+  </si>
+  <si>
+    <t>Argentina.png</t>
+  </si>
+  <si>
+    <t>布宜诺斯艾利斯</t>
+  </si>
+  <si>
+    <t>南美洲</t>
+  </si>
+  <si>
+    <t>南美</t>
+  </si>
+  <si>
+    <t>ARG</t>
+  </si>
+  <si>
+    <t>玻利维亚</t>
+  </si>
+  <si>
+    <t>巴西</t>
+  </si>
+  <si>
+    <t>巴西联邦共和国</t>
+  </si>
+  <si>
+    <t>The Federative Republic of Brazil</t>
+  </si>
+  <si>
+    <t>Brazil.png</t>
+  </si>
+  <si>
+    <t>巴西利亚</t>
+  </si>
+  <si>
+    <t>BRA</t>
+  </si>
+  <si>
+    <t>智利</t>
+  </si>
+  <si>
+    <t>哥伦比亚</t>
+  </si>
+  <si>
+    <t>厄过多尔</t>
+  </si>
+  <si>
+    <t>圭亚那</t>
+  </si>
+  <si>
+    <t>秘鲁</t>
+  </si>
+  <si>
+    <t>巴拉圭</t>
+  </si>
+  <si>
+    <t>苏里南</t>
+  </si>
+  <si>
+    <t>乌拉圭</t>
+  </si>
+  <si>
+    <t>委内瑞拉</t>
+  </si>
+  <si>
+    <t>澳大利亚</t>
+  </si>
+  <si>
+    <t>澳大利亚联邦</t>
+  </si>
+  <si>
+    <t>Commonwealth of Australia</t>
+  </si>
+  <si>
+    <t>Australia.png</t>
+  </si>
+  <si>
+    <t>堪培拉</t>
+  </si>
+  <si>
+    <t>大洋洲</t>
+  </si>
+  <si>
+    <t>斐济</t>
+  </si>
+  <si>
+    <t>斯里巴斯</t>
+  </si>
+  <si>
+    <t>马绍尔群岛</t>
+  </si>
+  <si>
+    <t>密克罗尼西亚联邦</t>
+  </si>
+  <si>
+    <t>瑙鲁</t>
+  </si>
+  <si>
+    <t>新西兰</t>
+  </si>
+  <si>
+    <t>帕劳</t>
+  </si>
+  <si>
+    <t>巴布亚新几内亚</t>
+  </si>
+  <si>
+    <t>萨摩亚</t>
+  </si>
+  <si>
+    <t>所罗门群岛</t>
+  </si>
+  <si>
+    <t>汤加</t>
+  </si>
+  <si>
+    <t>图瓦卢</t>
+  </si>
+  <si>
+    <t>瓦努阿图共和国</t>
+  </si>
+  <si>
+    <t>纽埃</t>
+  </si>
+  <si>
+    <t>库克群岛</t>
+  </si>
+  <si>
+    <t>阿尔及利亚</t>
+  </si>
+  <si>
+    <t>非洲</t>
+  </si>
+  <si>
+    <t>北非</t>
+  </si>
+  <si>
+    <t>埃及</t>
+  </si>
+  <si>
+    <t>利比亚</t>
+  </si>
+  <si>
+    <t>摩洛哥</t>
+  </si>
+  <si>
+    <t>苏丹</t>
+  </si>
+  <si>
+    <t>突尼斯</t>
+  </si>
+  <si>
+    <t>贝宁</t>
+  </si>
+  <si>
+    <t>西非</t>
+  </si>
+  <si>
+    <t>布基纳法索</t>
+  </si>
+  <si>
+    <t>科特迪瓦</t>
+  </si>
+  <si>
+    <t>冈比亚</t>
+  </si>
+  <si>
+    <t>加纳</t>
+  </si>
+  <si>
+    <t>几内亚</t>
+  </si>
+  <si>
+    <t>几内亚比绍</t>
+  </si>
+  <si>
+    <t>利比里亚</t>
+  </si>
+  <si>
+    <t>马里</t>
+  </si>
+  <si>
+    <t>尼日尔</t>
+  </si>
+  <si>
+    <t>毛里塔尼亚</t>
+  </si>
+  <si>
+    <t>尼日利亚</t>
+  </si>
+  <si>
+    <t>塞内加尔</t>
+  </si>
+  <si>
+    <t>塞拉利昂</t>
+  </si>
+  <si>
+    <t>多哥</t>
+  </si>
+  <si>
+    <t>佛得角</t>
+  </si>
+  <si>
+    <t>布隆迪</t>
+  </si>
+  <si>
+    <t>东非</t>
+  </si>
+  <si>
+    <t>吉布提</t>
+  </si>
+  <si>
+    <t>厄立特里亚</t>
+  </si>
+  <si>
+    <t>埃塞俄比亚</t>
+  </si>
+  <si>
+    <t>肯尼亚</t>
+  </si>
+  <si>
+    <t>卢旺达</t>
+  </si>
+  <si>
+    <t>塞舌尔</t>
+  </si>
+  <si>
+    <t>索马里</t>
+  </si>
+  <si>
+    <t>坦桑尼亚</t>
+  </si>
+  <si>
+    <t>乌干达</t>
+  </si>
+  <si>
+    <t>南苏丹</t>
+  </si>
+  <si>
+    <t>喀麦隆</t>
+  </si>
+  <si>
+    <t>中非</t>
+  </si>
+  <si>
+    <t>乍得</t>
+  </si>
+  <si>
+    <t>赤道几内亚</t>
+  </si>
+  <si>
+    <t>加蓬</t>
+  </si>
+  <si>
+    <t>刚果共和国</t>
+  </si>
+  <si>
+    <t>刚果民主共和国</t>
+  </si>
+  <si>
+    <t>圣多美和普林西比</t>
+  </si>
+  <si>
+    <t>安哥拉</t>
+  </si>
+  <si>
+    <t>南非</t>
+  </si>
+  <si>
+    <t>博茨瓦纳</t>
+  </si>
+  <si>
+    <t>科摩罗</t>
+  </si>
+  <si>
+    <t>莱托索</t>
+  </si>
+  <si>
+    <t>马达加斯加</t>
+  </si>
+  <si>
+    <t>马拉维</t>
+  </si>
+  <si>
+    <t>毛里求斯</t>
+  </si>
+  <si>
+    <t>莫桑比克</t>
+  </si>
+  <si>
+    <t>纳米利亚</t>
+  </si>
+  <si>
+    <t>斯威士兰</t>
+  </si>
+  <si>
+    <t>赞比亚</t>
+  </si>
+  <si>
+    <t>津巴布韦</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -68,24 +1547,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -134,7 +1899,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -169,7 +1934,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -343,26 +2108,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K198"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="7.35714285714286" customWidth="1"/>
+    <col min="3" max="3" width="22.9285714285714" customWidth="1"/>
+    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="35.7857142857143" customWidth="1"/>
+    <col min="6" max="6" width="17.4285714285714" customWidth="1"/>
+    <col min="7" max="7" width="16.2142857142857" customWidth="1"/>
+    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
+    <col min="9" max="9" width="8.78571428571429" customWidth="1"/>
+    <col min="10" max="10" width="7.57142857142857" customWidth="1"/>
+    <col min="11" max="11" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -375,8 +2143,3844 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I14" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" t="s">
+        <v>58</v>
+      </c>
+      <c r="K16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+      <c r="I17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I20" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
+        <v>89</v>
+      </c>
+      <c r="G21" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" t="s">
+        <v>84</v>
+      </c>
+      <c r="K21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>92</v>
+      </c>
+      <c r="I22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>101</v>
+      </c>
+      <c r="I30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
+        <v>106</v>
+      </c>
+      <c r="E33" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s">
+        <v>114</v>
+      </c>
+      <c r="G34" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+      <c r="E37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F37" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" t="s">
+        <v>123</v>
+      </c>
+      <c r="I37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>125</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" t="s">
+        <v>127</v>
+      </c>
+      <c r="E39" t="s">
+        <v>128</v>
+      </c>
+      <c r="F39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" t="s">
+        <v>103</v>
+      </c>
+      <c r="K39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>132</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>134</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>135</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>136</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D45" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" t="s">
+        <v>139</v>
+      </c>
+      <c r="F45" t="s">
+        <v>140</v>
+      </c>
+      <c r="G45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" t="s">
+        <v>103</v>
+      </c>
+      <c r="K45" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>144</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" t="s">
+        <v>148</v>
+      </c>
+      <c r="G48" t="s">
+        <v>149</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" t="s">
+        <v>103</v>
+      </c>
+      <c r="K48" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>152</v>
+      </c>
+      <c r="E49" t="s">
+        <v>153</v>
+      </c>
+      <c r="F49" t="s">
+        <v>154</v>
+      </c>
+      <c r="G49" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" t="s">
+        <v>103</v>
+      </c>
+      <c r="K49" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
+        <v>158</v>
+      </c>
+      <c r="I50" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" t="s">
+        <v>161</v>
+      </c>
+      <c r="F51" t="s">
+        <v>162</v>
+      </c>
+      <c r="G51" t="s">
+        <v>163</v>
+      </c>
+      <c r="I51" t="s">
+        <v>54</v>
+      </c>
+      <c r="J51" t="s">
+        <v>164</v>
+      </c>
+      <c r="K51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>166</v>
+      </c>
+      <c r="D52" t="s">
+        <v>167</v>
+      </c>
+      <c r="E52" t="s">
+        <v>168</v>
+      </c>
+      <c r="F52" t="s">
+        <v>169</v>
+      </c>
+      <c r="G52" t="s">
+        <v>170</v>
+      </c>
+      <c r="I52" t="s">
+        <v>54</v>
+      </c>
+      <c r="J52" t="s">
+        <v>164</v>
+      </c>
+      <c r="K52" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>172</v>
+      </c>
+      <c r="I53" t="s">
+        <v>54</v>
+      </c>
+      <c r="J53" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>173</v>
+      </c>
+      <c r="I54" t="s">
+        <v>54</v>
+      </c>
+      <c r="J54" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>174</v>
+      </c>
+      <c r="D55" t="s">
+        <v>175</v>
+      </c>
+      <c r="E55" t="s">
+        <v>176</v>
+      </c>
+      <c r="F55" t="s">
+        <v>177</v>
+      </c>
+      <c r="G55" t="s">
+        <v>174</v>
+      </c>
+      <c r="I55" t="s">
+        <v>54</v>
+      </c>
+      <c r="J55" t="s">
+        <v>164</v>
+      </c>
+      <c r="K55" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>179</v>
+      </c>
+      <c r="I56" t="s">
+        <v>54</v>
+      </c>
+      <c r="J56" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>180</v>
+      </c>
+      <c r="I57" t="s">
+        <v>54</v>
+      </c>
+      <c r="J57" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>181</v>
+      </c>
+      <c r="I58" t="s">
+        <v>54</v>
+      </c>
+      <c r="J58" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" t="s">
+        <v>185</v>
+      </c>
+      <c r="F59" t="s">
+        <v>186</v>
+      </c>
+      <c r="G59" t="s">
+        <v>187</v>
+      </c>
+      <c r="I59" t="s">
+        <v>54</v>
+      </c>
+      <c r="J59" t="s">
+        <v>182</v>
+      </c>
+      <c r="K59" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>189</v>
+      </c>
+      <c r="I60" t="s">
+        <v>54</v>
+      </c>
+      <c r="J60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>190</v>
+      </c>
+      <c r="I61" t="s">
+        <v>54</v>
+      </c>
+      <c r="J61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>191</v>
+      </c>
+      <c r="I62" t="s">
+        <v>54</v>
+      </c>
+      <c r="J62" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>192</v>
+      </c>
+      <c r="I63" t="s">
+        <v>54</v>
+      </c>
+      <c r="J63" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>193</v>
+      </c>
+      <c r="I64" t="s">
+        <v>54</v>
+      </c>
+      <c r="J64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>194</v>
+      </c>
+      <c r="I65" t="s">
+        <v>54</v>
+      </c>
+      <c r="J65" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>195</v>
+      </c>
+      <c r="I66" t="s">
+        <v>54</v>
+      </c>
+      <c r="J66" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>196</v>
+      </c>
+      <c r="I67" t="s">
+        <v>54</v>
+      </c>
+      <c r="J67" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>197</v>
+      </c>
+      <c r="I68" t="s">
+        <v>54</v>
+      </c>
+      <c r="J68" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>198</v>
+      </c>
+      <c r="D69" t="s">
+        <v>199</v>
+      </c>
+      <c r="E69" t="s">
+        <v>200</v>
+      </c>
+      <c r="F69" t="s">
+        <v>201</v>
+      </c>
+      <c r="G69" t="s">
+        <v>202</v>
+      </c>
+      <c r="I69" t="s">
+        <v>54</v>
+      </c>
+      <c r="J69" t="s">
+        <v>203</v>
+      </c>
+      <c r="K69" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>205</v>
+      </c>
+      <c r="I70" t="s">
+        <v>54</v>
+      </c>
+      <c r="J70" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>206</v>
+      </c>
+      <c r="I71" t="s">
+        <v>54</v>
+      </c>
+      <c r="J71" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>207</v>
+      </c>
+      <c r="D72" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" t="s">
+        <v>208</v>
+      </c>
+      <c r="F72" t="s">
+        <v>209</v>
+      </c>
+      <c r="G72" t="s">
+        <v>210</v>
+      </c>
+      <c r="I72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J72" t="s">
+        <v>203</v>
+      </c>
+      <c r="K72" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>212</v>
+      </c>
+      <c r="D73" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" t="s">
+        <v>214</v>
+      </c>
+      <c r="F73" t="s">
+        <v>215</v>
+      </c>
+      <c r="G73" t="s">
+        <v>216</v>
+      </c>
+      <c r="I73" t="s">
+        <v>54</v>
+      </c>
+      <c r="J73" t="s">
+        <v>203</v>
+      </c>
+      <c r="K73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>218</v>
+      </c>
+      <c r="I74" t="s">
+        <v>54</v>
+      </c>
+      <c r="J74" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>219</v>
+      </c>
+      <c r="I75" t="s">
+        <v>54</v>
+      </c>
+      <c r="J75" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>220</v>
+      </c>
+      <c r="I76" t="s">
+        <v>54</v>
+      </c>
+      <c r="J76" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>221</v>
+      </c>
+      <c r="I77" t="s">
+        <v>54</v>
+      </c>
+      <c r="J77" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>223</v>
+      </c>
+      <c r="I78" t="s">
+        <v>54</v>
+      </c>
+      <c r="J78" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>224</v>
+      </c>
+      <c r="I79" t="s">
+        <v>54</v>
+      </c>
+      <c r="J79" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>225</v>
+      </c>
+      <c r="I80" t="s">
+        <v>54</v>
+      </c>
+      <c r="J80" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>226</v>
+      </c>
+      <c r="I81" t="s">
+        <v>54</v>
+      </c>
+      <c r="J81" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>227</v>
+      </c>
+      <c r="I82" t="s">
+        <v>54</v>
+      </c>
+      <c r="J82" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>228</v>
+      </c>
+      <c r="D83" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" t="s">
+        <v>230</v>
+      </c>
+      <c r="F83" t="s">
+        <v>231</v>
+      </c>
+      <c r="G83" t="s">
+        <v>232</v>
+      </c>
+      <c r="I83" t="s">
+        <v>54</v>
+      </c>
+      <c r="J83" t="s">
+        <v>222</v>
+      </c>
+      <c r="K83" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>234</v>
+      </c>
+      <c r="I84" t="s">
+        <v>54</v>
+      </c>
+      <c r="J84" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>235</v>
+      </c>
+      <c r="I85" t="s">
+        <v>54</v>
+      </c>
+      <c r="J85" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>236</v>
+      </c>
+      <c r="I86" t="s">
+        <v>54</v>
+      </c>
+      <c r="J86" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>237</v>
+      </c>
+      <c r="I87" t="s">
+        <v>54</v>
+      </c>
+      <c r="J87" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>238</v>
+      </c>
+      <c r="I88" t="s">
+        <v>54</v>
+      </c>
+      <c r="J88" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>239</v>
+      </c>
+      <c r="I89" t="s">
+        <v>54</v>
+      </c>
+      <c r="J89" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>240</v>
+      </c>
+      <c r="I90" t="s">
+        <v>54</v>
+      </c>
+      <c r="J90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>241</v>
+      </c>
+      <c r="I91" t="s">
+        <v>54</v>
+      </c>
+      <c r="J91" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>242</v>
+      </c>
+      <c r="I92" t="s">
+        <v>54</v>
+      </c>
+      <c r="J92" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>243</v>
+      </c>
+      <c r="I93" t="s">
+        <v>54</v>
+      </c>
+      <c r="J93" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>244</v>
+      </c>
+      <c r="D94" t="s">
+        <v>244</v>
+      </c>
+      <c r="E94" t="s">
+        <v>245</v>
+      </c>
+      <c r="F94" t="s">
+        <v>246</v>
+      </c>
+      <c r="G94" t="s">
+        <v>247</v>
+      </c>
+      <c r="I94" t="s">
+        <v>248</v>
+      </c>
+      <c r="J94" t="s">
+        <v>249</v>
+      </c>
+      <c r="K94" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>251</v>
+      </c>
+      <c r="I95" t="s">
+        <v>248</v>
+      </c>
+      <c r="J95" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>252</v>
+      </c>
+      <c r="D96" t="s">
+        <v>253</v>
+      </c>
+      <c r="E96" t="s">
+        <v>254</v>
+      </c>
+      <c r="F96" t="s">
+        <v>255</v>
+      </c>
+      <c r="G96" t="s">
+        <v>256</v>
+      </c>
+      <c r="I96" t="s">
+        <v>248</v>
+      </c>
+      <c r="J96" t="s">
+        <v>257</v>
+      </c>
+      <c r="K96" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>259</v>
+      </c>
+      <c r="I97" t="s">
+        <v>248</v>
+      </c>
+      <c r="J97" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>260</v>
+      </c>
+      <c r="I98" t="s">
+        <v>248</v>
+      </c>
+      <c r="J98" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>261</v>
+      </c>
+      <c r="I99" t="s">
+        <v>248</v>
+      </c>
+      <c r="J99" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>262</v>
+      </c>
+      <c r="I100" t="s">
+        <v>248</v>
+      </c>
+      <c r="J100" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>263</v>
+      </c>
+      <c r="I101" t="s">
+        <v>248</v>
+      </c>
+      <c r="J101" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>264</v>
+      </c>
+      <c r="I102" t="s">
+        <v>248</v>
+      </c>
+      <c r="J102" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>265</v>
+      </c>
+      <c r="I103" t="s">
+        <v>248</v>
+      </c>
+      <c r="J103" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>266</v>
+      </c>
+      <c r="I104" t="s">
+        <v>248</v>
+      </c>
+      <c r="J104" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>268</v>
+      </c>
+      <c r="I105" t="s">
+        <v>248</v>
+      </c>
+      <c r="J105" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>269</v>
+      </c>
+      <c r="I106" t="s">
+        <v>248</v>
+      </c>
+      <c r="J106" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>270</v>
+      </c>
+      <c r="I107" t="s">
+        <v>248</v>
+      </c>
+      <c r="J107" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>271</v>
+      </c>
+      <c r="I108" t="s">
+        <v>248</v>
+      </c>
+      <c r="J108" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>272</v>
+      </c>
+      <c r="I109" t="s">
+        <v>248</v>
+      </c>
+      <c r="J109" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>273</v>
+      </c>
+      <c r="I110" t="s">
+        <v>248</v>
+      </c>
+      <c r="J110" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>274</v>
+      </c>
+      <c r="I111" t="s">
+        <v>248</v>
+      </c>
+      <c r="J111" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>275</v>
+      </c>
+      <c r="I112" t="s">
+        <v>248</v>
+      </c>
+      <c r="J112" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>276</v>
+      </c>
+      <c r="I113" t="s">
+        <v>248</v>
+      </c>
+      <c r="J113" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
+        <v>277</v>
+      </c>
+      <c r="I114" t="s">
+        <v>248</v>
+      </c>
+      <c r="J114" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" t="s">
+        <v>278</v>
+      </c>
+      <c r="I115" t="s">
+        <v>248</v>
+      </c>
+      <c r="J115" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>279</v>
+      </c>
+      <c r="I116" t="s">
+        <v>248</v>
+      </c>
+      <c r="J116" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>280</v>
+      </c>
+      <c r="D117" t="s">
+        <v>280</v>
+      </c>
+      <c r="E117" t="s">
+        <v>281</v>
+      </c>
+      <c r="F117" t="s">
+        <v>282</v>
+      </c>
+      <c r="G117" t="s">
+        <v>283</v>
+      </c>
+      <c r="I117" t="s">
+        <v>284</v>
+      </c>
+      <c r="J117" t="s">
+        <v>285</v>
+      </c>
+      <c r="K117" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>287</v>
+      </c>
+      <c r="I118" t="s">
+        <v>284</v>
+      </c>
+      <c r="J118" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>288</v>
+      </c>
+      <c r="D119" t="s">
+        <v>289</v>
+      </c>
+      <c r="E119" t="s">
+        <v>290</v>
+      </c>
+      <c r="F119" t="s">
+        <v>291</v>
+      </c>
+      <c r="G119" t="s">
+        <v>292</v>
+      </c>
+      <c r="I119" t="s">
+        <v>284</v>
+      </c>
+      <c r="J119" t="s">
+        <v>285</v>
+      </c>
+      <c r="K119" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>294</v>
+      </c>
+      <c r="I120" t="s">
+        <v>284</v>
+      </c>
+      <c r="J120" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>295</v>
+      </c>
+      <c r="I121" t="s">
+        <v>284</v>
+      </c>
+      <c r="J121" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>296</v>
+      </c>
+      <c r="I122" t="s">
+        <v>284</v>
+      </c>
+      <c r="J122" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" t="s">
+        <v>297</v>
+      </c>
+      <c r="I123" t="s">
+        <v>284</v>
+      </c>
+      <c r="J123" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>298</v>
+      </c>
+      <c r="I124" t="s">
+        <v>284</v>
+      </c>
+      <c r="J124" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" t="s">
+        <v>299</v>
+      </c>
+      <c r="I125" t="s">
+        <v>284</v>
+      </c>
+      <c r="J125" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>300</v>
+      </c>
+      <c r="I126" t="s">
+        <v>284</v>
+      </c>
+      <c r="J126" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>301</v>
+      </c>
+      <c r="I127" t="s">
+        <v>284</v>
+      </c>
+      <c r="J127" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>302</v>
+      </c>
+      <c r="I128" t="s">
+        <v>284</v>
+      </c>
+      <c r="J128" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>303</v>
+      </c>
+      <c r="D129" t="s">
+        <v>304</v>
+      </c>
+      <c r="E129" t="s">
+        <v>305</v>
+      </c>
+      <c r="F129" t="s">
+        <v>306</v>
+      </c>
+      <c r="G129" t="s">
+        <v>307</v>
+      </c>
+      <c r="I129" t="s">
+        <v>308</v>
+      </c>
+      <c r="J129" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>309</v>
+      </c>
+      <c r="I130" t="s">
+        <v>308</v>
+      </c>
+      <c r="J130" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>310</v>
+      </c>
+      <c r="I131" t="s">
+        <v>308</v>
+      </c>
+      <c r="J131" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>311</v>
+      </c>
+      <c r="I132" t="s">
+        <v>308</v>
+      </c>
+      <c r="J132" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>312</v>
+      </c>
+      <c r="I133" t="s">
+        <v>308</v>
+      </c>
+      <c r="J133" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>313</v>
+      </c>
+      <c r="I134" t="s">
+        <v>308</v>
+      </c>
+      <c r="J134" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>314</v>
+      </c>
+      <c r="I135" t="s">
+        <v>308</v>
+      </c>
+      <c r="J135" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>315</v>
+      </c>
+      <c r="I136" t="s">
+        <v>308</v>
+      </c>
+      <c r="J136" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>316</v>
+      </c>
+      <c r="I137" t="s">
+        <v>308</v>
+      </c>
+      <c r="J137" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>317</v>
+      </c>
+      <c r="I138" t="s">
+        <v>308</v>
+      </c>
+      <c r="J138" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>318</v>
+      </c>
+      <c r="I139" t="s">
+        <v>308</v>
+      </c>
+      <c r="J139" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>319</v>
+      </c>
+      <c r="I140" t="s">
+        <v>308</v>
+      </c>
+      <c r="J140" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>320</v>
+      </c>
+      <c r="I141" t="s">
+        <v>308</v>
+      </c>
+      <c r="J141" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>321</v>
+      </c>
+      <c r="I142" t="s">
+        <v>308</v>
+      </c>
+      <c r="J142" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>322</v>
+      </c>
+      <c r="I143" t="s">
+        <v>308</v>
+      </c>
+      <c r="J143" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>323</v>
+      </c>
+      <c r="I144" t="s">
+        <v>308</v>
+      </c>
+      <c r="J144" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>324</v>
+      </c>
+      <c r="I145" t="s">
+        <v>325</v>
+      </c>
+      <c r="J145" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>327</v>
+      </c>
+      <c r="I146" t="s">
+        <v>325</v>
+      </c>
+      <c r="J146" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>328</v>
+      </c>
+      <c r="I147" t="s">
+        <v>325</v>
+      </c>
+      <c r="J147" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" t="s">
+        <v>329</v>
+      </c>
+      <c r="I148" t="s">
+        <v>325</v>
+      </c>
+      <c r="J148" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>330</v>
+      </c>
+      <c r="I149" t="s">
+        <v>325</v>
+      </c>
+      <c r="J149" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" t="s">
+        <v>331</v>
+      </c>
+      <c r="I150" t="s">
+        <v>325</v>
+      </c>
+      <c r="J150" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>332</v>
+      </c>
+      <c r="I151" t="s">
+        <v>325</v>
+      </c>
+      <c r="J151" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>334</v>
+      </c>
+      <c r="I152" t="s">
+        <v>325</v>
+      </c>
+      <c r="J152" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>335</v>
+      </c>
+      <c r="I153" t="s">
+        <v>325</v>
+      </c>
+      <c r="J153" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>336</v>
+      </c>
+      <c r="I154" t="s">
+        <v>325</v>
+      </c>
+      <c r="J154" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>337</v>
+      </c>
+      <c r="I155" t="s">
+        <v>325</v>
+      </c>
+      <c r="J155" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>338</v>
+      </c>
+      <c r="I156" t="s">
+        <v>325</v>
+      </c>
+      <c r="J156" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>339</v>
+      </c>
+      <c r="I157" t="s">
+        <v>325</v>
+      </c>
+      <c r="J157" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>340</v>
+      </c>
+      <c r="I158" t="s">
+        <v>325</v>
+      </c>
+      <c r="J158" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" t="s">
+        <v>341</v>
+      </c>
+      <c r="I159" t="s">
+        <v>325</v>
+      </c>
+      <c r="J159" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>342</v>
+      </c>
+      <c r="I160" t="s">
+        <v>325</v>
+      </c>
+      <c r="J160" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>343</v>
+      </c>
+      <c r="I161" t="s">
+        <v>325</v>
+      </c>
+      <c r="J161" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>344</v>
+      </c>
+      <c r="I162" t="s">
+        <v>325</v>
+      </c>
+      <c r="J162" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>345</v>
+      </c>
+      <c r="I163" t="s">
+        <v>325</v>
+      </c>
+      <c r="J163" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>346</v>
+      </c>
+      <c r="I164" t="s">
+        <v>325</v>
+      </c>
+      <c r="J164" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>347</v>
+      </c>
+      <c r="I165" t="s">
+        <v>325</v>
+      </c>
+      <c r="J165" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>348</v>
+      </c>
+      <c r="I166" t="s">
+        <v>325</v>
+      </c>
+      <c r="J166" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>349</v>
+      </c>
+      <c r="I167" t="s">
+        <v>325</v>
+      </c>
+      <c r="J167" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>351</v>
+      </c>
+      <c r="I168" t="s">
+        <v>325</v>
+      </c>
+      <c r="J168" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>352</v>
+      </c>
+      <c r="I169" t="s">
+        <v>325</v>
+      </c>
+      <c r="J169" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" t="s">
+        <v>353</v>
+      </c>
+      <c r="I170" t="s">
+        <v>325</v>
+      </c>
+      <c r="J170" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" t="s">
+        <v>354</v>
+      </c>
+      <c r="I171" t="s">
+        <v>325</v>
+      </c>
+      <c r="J171" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" t="s">
+        <v>355</v>
+      </c>
+      <c r="I172" t="s">
+        <v>325</v>
+      </c>
+      <c r="J172" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" t="s">
+        <v>356</v>
+      </c>
+      <c r="I173" t="s">
+        <v>325</v>
+      </c>
+      <c r="J173" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" t="s">
+        <v>357</v>
+      </c>
+      <c r="I174" t="s">
+        <v>325</v>
+      </c>
+      <c r="J174" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>358</v>
+      </c>
+      <c r="I175" t="s">
+        <v>325</v>
+      </c>
+      <c r="J175" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>359</v>
+      </c>
+      <c r="I176" t="s">
+        <v>325</v>
+      </c>
+      <c r="J176" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>360</v>
+      </c>
+      <c r="I177" t="s">
+        <v>325</v>
+      </c>
+      <c r="J177" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>361</v>
+      </c>
+      <c r="I178" t="s">
+        <v>325</v>
+      </c>
+      <c r="J178" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>363</v>
+      </c>
+      <c r="I179" t="s">
+        <v>325</v>
+      </c>
+      <c r="J179" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>362</v>
+      </c>
+      <c r="I180" t="s">
+        <v>325</v>
+      </c>
+      <c r="J180" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>364</v>
+      </c>
+      <c r="I181" t="s">
+        <v>325</v>
+      </c>
+      <c r="J181" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>365</v>
+      </c>
+      <c r="I182" t="s">
+        <v>325</v>
+      </c>
+      <c r="J182" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>366</v>
+      </c>
+      <c r="I183" t="s">
+        <v>325</v>
+      </c>
+      <c r="J183" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>367</v>
+      </c>
+      <c r="I184" t="s">
+        <v>325</v>
+      </c>
+      <c r="J184" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>368</v>
+      </c>
+      <c r="I185" t="s">
+        <v>325</v>
+      </c>
+      <c r="J185" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>369</v>
+      </c>
+      <c r="I186" t="s">
+        <v>325</v>
+      </c>
+      <c r="J186" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>371</v>
+      </c>
+      <c r="I187" t="s">
+        <v>325</v>
+      </c>
+      <c r="J187" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>372</v>
+      </c>
+      <c r="I188" t="s">
+        <v>325</v>
+      </c>
+      <c r="J188" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>373</v>
+      </c>
+      <c r="I189" t="s">
+        <v>325</v>
+      </c>
+      <c r="J189" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>374</v>
+      </c>
+      <c r="I190" t="s">
+        <v>325</v>
+      </c>
+      <c r="J190" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>375</v>
+      </c>
+      <c r="I191" t="s">
+        <v>325</v>
+      </c>
+      <c r="J191" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>376</v>
+      </c>
+      <c r="I192" t="s">
+        <v>325</v>
+      </c>
+      <c r="J192" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>377</v>
+      </c>
+      <c r="I193" t="s">
+        <v>325</v>
+      </c>
+      <c r="J193" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>378</v>
+      </c>
+      <c r="I194" t="s">
+        <v>325</v>
+      </c>
+      <c r="J194" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>379</v>
+      </c>
+      <c r="I195" t="s">
+        <v>325</v>
+      </c>
+      <c r="J195" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>370</v>
+      </c>
+      <c r="I196" t="s">
+        <v>325</v>
+      </c>
+      <c r="J196" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>380</v>
+      </c>
+      <c r="I197" t="s">
+        <v>325</v>
+      </c>
+      <c r="J197" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>381</v>
+      </c>
+      <c r="I198" t="s">
+        <v>325</v>
+      </c>
+      <c r="J198" t="s">
+        <v>370</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/public/docs/datas/world.xlsx
+++ b/public/docs/datas/world.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="15240"/>
+    <workbookView windowWidth="24700" windowHeight="17260"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="country" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">country!$A$1:$L$198</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="545">
   <si>
     <t>no</t>
   </si>
@@ -44,6 +47,9 @@
     <t>enName</t>
   </si>
   <si>
+    <t>shortName</t>
+  </si>
+  <si>
     <t>flag</t>
   </si>
   <si>
@@ -122,7 +128,7 @@
     <t>Democratic People's Republic of Korea</t>
   </si>
   <si>
-    <t>NorthKorea.png</t>
+    <t>North Korea.png</t>
   </si>
   <si>
     <t>平壤</t>
@@ -185,12 +191,18 @@
     <t>Russian Federation</t>
   </si>
   <si>
+    <t>Russia</t>
+  </si>
+  <si>
     <t>Russia.png</t>
   </si>
   <si>
     <t>莫斯科</t>
   </si>
   <si>
+    <t>Moscow</t>
+  </si>
+  <si>
     <t>欧洲</t>
   </si>
   <si>
@@ -203,24 +215,144 @@
     <t>缅甸</t>
   </si>
   <si>
+    <t>缅甸联邦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of the Union of Myanmar</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>Myanmar.jpg</t>
+  </si>
+  <si>
+    <t>内比都</t>
+  </si>
+  <si>
+    <t>Nay Pyi Taw</t>
+  </si>
+  <si>
     <t>东南亚</t>
   </si>
   <si>
+    <t>MMR</t>
+  </si>
+  <si>
     <t>文莱</t>
   </si>
   <si>
+    <t>文莱达鲁萨兰国</t>
+  </si>
+  <si>
+    <t>Negara Brunei Darussalam</t>
+  </si>
+  <si>
+    <t>Brunei</t>
+  </si>
+  <si>
+    <t>Brunei.png</t>
+  </si>
+  <si>
+    <t>斯里巴加湾市</t>
+  </si>
+  <si>
+    <t>Bandar Seri Begawan</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
     <t>柬埔寨</t>
   </si>
   <si>
+    <t>柬埔寨王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Cambodia</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>Cambodia.png</t>
+  </si>
+  <si>
+    <t>金边</t>
+  </si>
+  <si>
+    <t>Phnom Penh</t>
+  </si>
+  <si>
+    <t>KHM</t>
+  </si>
+  <si>
     <t>东帝汶</t>
   </si>
   <si>
+    <t>东帝汶民主共和国</t>
+  </si>
+  <si>
+    <t>Democratic Republic of Timor-Leste</t>
+  </si>
+  <si>
+    <t>Timor-Leste.png</t>
+  </si>
+  <si>
+    <t>帝力</t>
+  </si>
+  <si>
+    <t>Díli</t>
+  </si>
+  <si>
+    <t>TLS</t>
+  </si>
+  <si>
     <t>印度尼西亚</t>
   </si>
   <si>
+    <t>印度尼西亚共和国</t>
+  </si>
+  <si>
+    <t>Republic of Indonesia</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Indonesia.png</t>
+  </si>
+  <si>
+    <t>努山塔拉</t>
+  </si>
+  <si>
+    <t>Nusantara</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
     <t>老挝</t>
   </si>
   <si>
+    <t>老挝人民民主共和国</t>
+  </si>
+  <si>
+    <t>The Lao People’s Democratic Republic</t>
+  </si>
+  <si>
+    <t>Laos.png</t>
+  </si>
+  <si>
+    <t>万象</t>
+  </si>
+  <si>
+    <t>Vientiane</t>
+  </si>
+  <si>
+    <t>LAO</t>
+  </si>
+  <si>
     <t>马来西亚</t>
   </si>
   <si>
@@ -233,12 +365,36 @@
     <t>吉隆坡</t>
   </si>
   <si>
+    <t>Kuala Lumpur</t>
+  </si>
+  <si>
     <t>MYS</t>
   </si>
   <si>
     <t>菲律宾</t>
   </si>
   <si>
+    <t>菲律宾共和国</t>
+  </si>
+  <si>
+    <t>Republic of the Philippines</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>Philippines.png</t>
+  </si>
+  <si>
+    <t>大马尼拉市</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
     <t>新加坡</t>
   </si>
   <si>
@@ -248,12 +404,18 @@
     <t>Republic of Singapore</t>
   </si>
   <si>
+    <t>Singapore</t>
+  </si>
+  <si>
     <t>Singapore.png</t>
   </si>
   <si>
     <t>新加坡市</t>
   </si>
   <si>
+    <t>Singapore City</t>
+  </si>
+  <si>
     <t>SGP</t>
   </si>
   <si>
@@ -266,27 +428,87 @@
     <t>The Kingdom of Thailand</t>
   </si>
   <si>
+    <t>Thailand</t>
+  </si>
+  <si>
     <t>Thailand.png</t>
   </si>
   <si>
     <t>曼谷</t>
   </si>
   <si>
+    <t>Krung Thep Maha Nakhon</t>
+  </si>
+  <si>
     <t>THA</t>
   </si>
   <si>
     <t>越南</t>
   </si>
   <si>
+    <t>越南社会主义共和国</t>
+  </si>
+  <si>
+    <t>The Socialist Republic of Viet Nam</t>
+  </si>
+  <si>
+    <t>Vietnam.png</t>
+  </si>
+  <si>
+    <t>河内</t>
+  </si>
+  <si>
+    <t>Hanoi</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
     <t>孟加拉国</t>
   </si>
   <si>
+    <t>孟加拉人民共和国</t>
+  </si>
+  <si>
+    <t>The People’s Republic of Bangladesh</t>
+  </si>
+  <si>
+    <t>Bangladesh.png</t>
+  </si>
+  <si>
+    <t>达卡</t>
+  </si>
+  <si>
+    <t>Dhaka</t>
+  </si>
+  <si>
     <t>南亚</t>
   </si>
   <si>
+    <t>BGD</t>
+  </si>
+  <si>
     <t>不丹</t>
   </si>
   <si>
+    <t>不丹王国</t>
+  </si>
+  <si>
+    <t>Kingdom of Bhutan</t>
+  </si>
+  <si>
+    <t>Bhutan.png</t>
+  </si>
+  <si>
+    <t>廷布</t>
+  </si>
+  <si>
+    <t>Thimphu</t>
+  </si>
+  <si>
+    <t>BTN</t>
+  </si>
+  <si>
     <t>印度</t>
   </si>
   <si>
@@ -302,39 +524,207 @@
     <t>新德里</t>
   </si>
   <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
     <t>IND</t>
   </si>
   <si>
     <t>马尔代夫</t>
   </si>
   <si>
+    <t>马尔代夫共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Maldives</t>
+  </si>
+  <si>
+    <t>Maldives.png</t>
+  </si>
+  <si>
+    <t>马累</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>MDV</t>
+  </si>
+  <si>
     <t>尼泊尔</t>
   </si>
   <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>Nepal.png</t>
+  </si>
+  <si>
+    <t>加德满都</t>
+  </si>
+  <si>
+    <t>Kathmandu</t>
+  </si>
+  <si>
+    <t>NPL</t>
+  </si>
+  <si>
     <t>巴基斯坦</t>
   </si>
   <si>
+    <t>巴基斯坦伊斯兰共和国</t>
+  </si>
+  <si>
+    <t>Islamic Republic of Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan.png</t>
+  </si>
+  <si>
+    <t>伊斯兰堡</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
     <t>斯里兰卡</t>
   </si>
   <si>
+    <t>斯里兰卡民主社会主义共和国</t>
+  </si>
+  <si>
+    <t>The Democratic Socialist Republic of Sri Lanka</t>
+  </si>
+  <si>
+    <t>Sri Lanka.png</t>
+  </si>
+  <si>
+    <t>科伦坡</t>
+  </si>
+  <si>
+    <t>Colombo</t>
+  </si>
+  <si>
+    <t>LKA</t>
+  </si>
+  <si>
     <t>哈萨克斯坦</t>
   </si>
   <si>
+    <t>哈萨克斯坦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Kazakhstan</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>Kazakhstan.png</t>
+  </si>
+  <si>
+    <t>阿斯塔纳</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
     <t>中亚</t>
   </si>
   <si>
+    <t>KAZ</t>
+  </si>
+  <si>
     <t>吉尔吉斯斯坦</t>
   </si>
   <si>
+    <t>吉尔吉斯共和国</t>
+  </si>
+  <si>
+    <t>Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan.png</t>
+  </si>
+  <si>
+    <t>比什凯克</t>
+  </si>
+  <si>
+    <t>Bishkek</t>
+  </si>
+  <si>
+    <t>KGZ</t>
+  </si>
+  <si>
     <t>塔吉克斯坦</t>
   </si>
   <si>
+    <t>塔吉克斯坦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Tajikistan</t>
+  </si>
+  <si>
+    <t>Tajikistan.png</t>
+  </si>
+  <si>
+    <t>杜尚别</t>
+  </si>
+  <si>
+    <t>Dushanbe</t>
+  </si>
+  <si>
+    <t>TJK</t>
+  </si>
+  <si>
     <t>土库曼斯坦</t>
   </si>
   <si>
+    <t>Turkmenistan</t>
+  </si>
+  <si>
+    <t>Turkmenistan.png</t>
+  </si>
+  <si>
+    <t>阿什哈巴德市</t>
+  </si>
+  <si>
+    <t>Ashgabat</t>
+  </si>
+  <si>
+    <t>TKM</t>
+  </si>
+  <si>
     <t>乌兹别克斯坦</t>
   </si>
   <si>
+    <t>乌兹别克斯坦共和国</t>
+  </si>
+  <si>
+    <t>Republic of Uzbekistan</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Uzbekistan.png</t>
+  </si>
+  <si>
+    <t>塔什干</t>
+  </si>
+  <si>
+    <t>Tashkent</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
     <t>阿富汗</t>
   </si>
   <si>
@@ -521,6 +911,9 @@
     <t>布鲁塞尔</t>
   </si>
   <si>
+    <t>Brussels</t>
+  </si>
+  <si>
     <t>西欧</t>
   </si>
   <si>
@@ -542,15 +935,51 @@
     <t>巴黎</t>
   </si>
   <si>
+    <t>Paris</t>
+  </si>
+  <si>
     <t>FRA</t>
   </si>
   <si>
     <t>爱尔兰</t>
   </si>
   <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Ireland.png</t>
+  </si>
+  <si>
+    <t>都柏林市</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>IRL</t>
+  </si>
+  <si>
     <t>卢森堡</t>
   </si>
   <si>
+    <t>卢森堡大公国</t>
+  </si>
+  <si>
+    <t>The Grand Duchy of Luxembourg</t>
+  </si>
+  <si>
+    <t>Luxembourg.png</t>
+  </si>
+  <si>
+    <t>卢森堡市</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>LUX</t>
+  </si>
+  <si>
     <t>摩纳哥</t>
   </si>
   <si>
@@ -563,15 +992,54 @@
     <t>Monaco.png</t>
   </si>
   <si>
+    <t>Monaco</t>
+  </si>
+  <si>
     <t>MCO</t>
   </si>
   <si>
     <t>荷兰</t>
   </si>
   <si>
+    <t>荷兰王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of the Netherlands</t>
+  </si>
+  <si>
+    <t>Netherlands.png</t>
+  </si>
+  <si>
+    <t>阿姆斯特丹</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>NLD</t>
+  </si>
+  <si>
     <t>英国</t>
   </si>
   <si>
+    <t>大不列颠及北爱尔兰联合王国</t>
+  </si>
+  <si>
+    <t>The United Kingdom of Great Britain and Northern Ireland</t>
+  </si>
+  <si>
+    <t>United Kingdom.png</t>
+  </si>
+  <si>
+    <t>伦敦</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
     <t>丹麦</t>
   </si>
   <si>
@@ -593,6 +1061,9 @@
     <t>赫尔辛基</t>
   </si>
   <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
     <t>FIN</t>
   </si>
   <si>
@@ -773,6 +1244,9 @@
     <t>渥太华</t>
   </si>
   <si>
+    <t>Ottawa</t>
+  </si>
+  <si>
     <t>北美州</t>
   </si>
   <si>
@@ -783,6 +1257,24 @@
   </si>
   <si>
     <t>美国</t>
+  </si>
+  <si>
+    <t>美利坚合众国</t>
+  </si>
+  <si>
+    <t>The United States of America</t>
+  </si>
+  <si>
+    <t>United States.png</t>
+  </si>
+  <si>
+    <t>华盛顿哥伦比亚特区</t>
+  </si>
+  <si>
+    <t>Washington, D.C.</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
   <si>
     <t>墨西哥</t>
@@ -1194,8 +1686,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10.5"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1648,19 +2140,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1669,7 +2161,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1793,8 +2285,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2114,23 +2607,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:L198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="4.57142857142857" customWidth="1"/>
     <col min="2" max="2" width="7.35714285714286" customWidth="1"/>
-    <col min="3" max="3" width="22.9285714285714" customWidth="1"/>
-    <col min="4" max="4" width="25.1428571428571" customWidth="1"/>
-    <col min="5" max="5" width="35.7857142857143" customWidth="1"/>
-    <col min="6" max="6" width="17.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="16.2142857142857" customWidth="1"/>
-    <col min="8" max="8" width="9.57142857142857" customWidth="1"/>
-    <col min="9" max="9" width="8.78571428571429" customWidth="1"/>
-    <col min="10" max="10" width="7.57142857142857" customWidth="1"/>
-    <col min="11" max="11" width="5.42857142857143" customWidth="1"/>
+    <col min="3" max="3" width="13.9821428571429" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="28.4196428571429" customWidth="1"/>
+    <col min="6" max="6" width="15.7678571428571" customWidth="1"/>
+    <col min="7" max="7" width="16.0714285714286" customWidth="1"/>
+    <col min="8" max="8" width="16.2142857142857" customWidth="1"/>
+    <col min="9" max="9" width="12.7857142857143" customWidth="1"/>
+    <col min="10" max="10" width="8.78571428571429" customWidth="1"/>
+    <col min="11" max="11" width="7.57142857142857" customWidth="1"/>
+    <col min="12" max="12" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2164,24 +2658,24 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="G2" t="s">
@@ -2199,26 +2693,27 @@
       <c r="K2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" t="s">
         <v>24</v>
       </c>
+      <c r="F3"/>
       <c r="G3" t="s">
         <v>25</v>
       </c>
@@ -2226,32 +2721,32 @@
         <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" t="s">
         <v>31</v>
       </c>
       <c r="G4" t="s">
@@ -2261,32 +2756,32 @@
         <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
         <v>38</v>
       </c>
       <c r="G5" t="s">
@@ -2296,32 +2791,32 @@
         <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>20</v>
+      </c>
+      <c r="L5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" t="s">
         <v>45</v>
       </c>
       <c r="G6" t="s">
@@ -2331,3655 +2826,4159 @@
         <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
       </c>
       <c r="I7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" t="s">
+        <v>65</v>
       </c>
       <c r="I8" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K8" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>69</v>
+      </c>
+      <c r="D9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K9" t="s">
+        <v>67</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="J10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" t="s">
+        <v>97</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="J12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" t="s">
+        <v>104</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="J13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="G14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" t="s">
         <v>67</v>
       </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>58</v>
-      </c>
-      <c r="K14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H15" t="s">
+        <v>118</v>
       </c>
       <c r="I15" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="J15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>125</v>
+      </c>
+      <c r="H16" t="s">
+        <v>126</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>127</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="K16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>67</v>
+      </c>
+      <c r="L16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>133</v>
+      </c>
+      <c r="H17" t="s">
+        <v>134</v>
       </c>
       <c r="I17" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>67</v>
+      </c>
+      <c r="L17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>137</v>
+      </c>
+      <c r="D18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" t="s">
+        <v>141</v>
       </c>
       <c r="I18" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="J18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K18" t="s">
+        <v>67</v>
+      </c>
+      <c r="L18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>144</v>
+      </c>
+      <c r="D19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="G19" t="s">
+        <v>147</v>
+      </c>
+      <c r="H19" t="s">
+        <v>148</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K19" t="s">
+        <v>150</v>
+      </c>
+      <c r="L19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>152</v>
+      </c>
+      <c r="D20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" t="s">
+        <v>154</v>
+      </c>
+      <c r="G20" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" t="s">
+        <v>156</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
       <c r="J20" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K20" t="s">
+        <v>150</v>
+      </c>
+      <c r="L20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="G21" t="s">
-        <v>90</v>
+        <v>162</v>
+      </c>
+      <c r="H21" t="s">
+        <v>163</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="J21" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="K21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>150</v>
+      </c>
+      <c r="L21" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>166</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" t="s">
+        <v>168</v>
+      </c>
+      <c r="G22" t="s">
+        <v>169</v>
+      </c>
+      <c r="H22" t="s">
+        <v>170</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="J22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K22" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>173</v>
+      </c>
+      <c r="D23" t="s">
+        <v>173</v>
+      </c>
+      <c r="E23" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" t="s">
+        <v>176</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K23" t="s">
+        <v>150</v>
+      </c>
+      <c r="L23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>94</v>
+        <v>179</v>
+      </c>
+      <c r="D24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E24" t="s">
+        <v>181</v>
+      </c>
+      <c r="G24" t="s">
+        <v>182</v>
+      </c>
+      <c r="H24" t="s">
+        <v>183</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K24" t="s">
+        <v>150</v>
+      </c>
+      <c r="L24" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>186</v>
+      </c>
+      <c r="D25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" t="s">
+        <v>188</v>
+      </c>
+      <c r="G25" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" t="s">
+        <v>190</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>191</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K25" t="s">
+        <v>150</v>
+      </c>
+      <c r="L25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>193</v>
+      </c>
+      <c r="D26" t="s">
+        <v>194</v>
+      </c>
+      <c r="E26" t="s">
+        <v>195</v>
+      </c>
+      <c r="F26" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" t="s">
+        <v>197</v>
+      </c>
+      <c r="H26" t="s">
+        <v>198</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
       <c r="J26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K26" t="s">
+        <v>200</v>
+      </c>
+      <c r="L26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>98</v>
+        <v>202</v>
+      </c>
+      <c r="D27" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" t="s">
+        <v>204</v>
+      </c>
+      <c r="F27" t="s">
+        <v>205</v>
+      </c>
+      <c r="G27" t="s">
+        <v>206</v>
+      </c>
+      <c r="H27" t="s">
+        <v>207</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="J27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K27" t="s">
+        <v>200</v>
+      </c>
+      <c r="L27" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>210</v>
+      </c>
+      <c r="D28" t="s">
+        <v>211</v>
+      </c>
+      <c r="E28" t="s">
+        <v>212</v>
+      </c>
+      <c r="G28" t="s">
+        <v>213</v>
+      </c>
+      <c r="H28" t="s">
+        <v>214</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="J28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K28" t="s">
+        <v>200</v>
+      </c>
+      <c r="L28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I29" t="s">
-        <v>18</v>
+        <v>217</v>
+      </c>
+      <c r="D29" t="s">
+        <v>217</v>
+      </c>
+      <c r="E29" t="s">
+        <v>218</v>
+      </c>
+      <c r="G29" t="s">
+        <v>219</v>
+      </c>
+      <c r="H29" t="s">
+        <v>220</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="J29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K29" t="s">
+        <v>200</v>
+      </c>
+      <c r="L29" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>223</v>
+      </c>
+      <c r="D30" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" t="s">
+        <v>226</v>
+      </c>
+      <c r="G30" t="s">
+        <v>227</v>
+      </c>
+      <c r="H30" t="s">
+        <v>228</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>229</v>
       </c>
       <c r="J30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K30" t="s">
+        <v>200</v>
+      </c>
+      <c r="L30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" t="s">
-        <v>18</v>
+        <v>231</v>
       </c>
       <c r="J31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>104</v>
-      </c>
-      <c r="I32" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="J32" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K32" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
       <c r="D33" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
       <c r="E33" t="s">
-        <v>107</v>
-      </c>
-      <c r="F33" t="s">
-        <v>108</v>
+        <v>236</v>
       </c>
       <c r="G33" t="s">
-        <v>109</v>
-      </c>
-      <c r="I33" t="s">
-        <v>18</v>
+        <v>237</v>
+      </c>
+      <c r="H33" t="s">
+        <v>238</v>
       </c>
       <c r="J33" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K33" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L33" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>240</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
       <c r="E34" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" t="s">
-        <v>114</v>
+        <v>242</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
-      </c>
-      <c r="I34" t="s">
-        <v>18</v>
+        <v>243</v>
+      </c>
+      <c r="H34" t="s">
+        <v>244</v>
       </c>
       <c r="J34" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
-      </c>
-      <c r="I35" t="s">
-        <v>18</v>
+        <v>246</v>
       </c>
       <c r="J35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K35" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>118</v>
-      </c>
-      <c r="I36" t="s">
-        <v>18</v>
+        <v>247</v>
       </c>
       <c r="J36" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K36" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="D37" t="s">
-        <v>120</v>
+        <v>249</v>
       </c>
       <c r="E37" t="s">
-        <v>121</v>
-      </c>
-      <c r="F37" t="s">
-        <v>122</v>
+        <v>250</v>
       </c>
       <c r="G37" t="s">
-        <v>123</v>
-      </c>
-      <c r="I37" t="s">
-        <v>18</v>
+        <v>251</v>
+      </c>
+      <c r="H37" t="s">
+        <v>252</v>
       </c>
       <c r="J37" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L37" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
-      </c>
-      <c r="I38" t="s">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="J38" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>256</v>
       </c>
       <c r="E39" t="s">
-        <v>128</v>
-      </c>
-      <c r="F39" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" t="s">
-        <v>18</v>
+        <v>258</v>
+      </c>
+      <c r="H39" t="s">
+        <v>259</v>
       </c>
       <c r="J39" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K39" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L39" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" t="s">
-        <v>18</v>
+        <v>261</v>
       </c>
       <c r="J40" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K40" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>133</v>
-      </c>
-      <c r="I41" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="J41" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K41" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
-      </c>
-      <c r="I42" t="s">
-        <v>18</v>
+        <v>263</v>
       </c>
       <c r="J42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K42" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>135</v>
-      </c>
-      <c r="I43" t="s">
-        <v>18</v>
+        <v>264</v>
       </c>
       <c r="J43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K43" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
-      </c>
-      <c r="I44" t="s">
-        <v>18</v>
+        <v>265</v>
       </c>
       <c r="J44" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K44" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="E45" t="s">
-        <v>139</v>
-      </c>
-      <c r="F45" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="G45" t="s">
-        <v>141</v>
-      </c>
-      <c r="I45" t="s">
-        <v>18</v>
+        <v>269</v>
+      </c>
+      <c r="H45" t="s">
+        <v>270</v>
       </c>
       <c r="J45" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L45" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>143</v>
-      </c>
-      <c r="I46" t="s">
-        <v>18</v>
+        <v>272</v>
       </c>
       <c r="J46" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K46" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>144</v>
-      </c>
-      <c r="I47" t="s">
-        <v>18</v>
+        <v>273</v>
       </c>
       <c r="J47" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K47" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>274</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
-      </c>
-      <c r="F48" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
       <c r="G48" t="s">
-        <v>149</v>
-      </c>
-      <c r="I48" t="s">
-        <v>18</v>
+        <v>277</v>
+      </c>
+      <c r="H48" t="s">
+        <v>278</v>
       </c>
       <c r="J48" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L48" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="D49" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E49" t="s">
-        <v>153</v>
-      </c>
-      <c r="F49" t="s">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="H49" t="s">
-        <v>156</v>
+        <v>284</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>285</v>
       </c>
       <c r="J49" t="s">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>232</v>
+      </c>
+      <c r="L49" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
-      </c>
-      <c r="I50" t="s">
-        <v>18</v>
+        <v>287</v>
       </c>
       <c r="J50" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>19</v>
+      </c>
+      <c r="K50" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="D51" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="E51" t="s">
-        <v>161</v>
-      </c>
-      <c r="F51" t="s">
-        <v>162</v>
+        <v>290</v>
       </c>
       <c r="G51" t="s">
-        <v>163</v>
+        <v>291</v>
+      </c>
+      <c r="H51" t="s">
+        <v>292</v>
       </c>
       <c r="I51" t="s">
-        <v>54</v>
+        <v>293</v>
       </c>
       <c r="J51" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="K51" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>294</v>
+      </c>
+      <c r="L51" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>166</v>
+        <v>296</v>
       </c>
       <c r="D52" t="s">
-        <v>167</v>
+        <v>297</v>
       </c>
       <c r="E52" t="s">
-        <v>168</v>
-      </c>
-      <c r="F52" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="G52" t="s">
-        <v>170</v>
+        <v>299</v>
+      </c>
+      <c r="H52" t="s">
+        <v>300</v>
       </c>
       <c r="I52" t="s">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="J52" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="K52" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>294</v>
+      </c>
+      <c r="L52" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>303</v>
+      </c>
+      <c r="D53" t="s">
+        <v>303</v>
+      </c>
+      <c r="E53" t="s">
+        <v>304</v>
+      </c>
+      <c r="G53" t="s">
+        <v>305</v>
+      </c>
+      <c r="H53" t="s">
+        <v>306</v>
       </c>
       <c r="I53" t="s">
-        <v>54</v>
+        <v>307</v>
       </c>
       <c r="J53" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K53" t="s">
+        <v>294</v>
+      </c>
+      <c r="L53" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>309</v>
+      </c>
+      <c r="D54" t="s">
+        <v>310</v>
+      </c>
+      <c r="E54" t="s">
+        <v>311</v>
+      </c>
+      <c r="G54" t="s">
+        <v>312</v>
+      </c>
+      <c r="H54" t="s">
+        <v>313</v>
       </c>
       <c r="I54" t="s">
-        <v>54</v>
+        <v>314</v>
       </c>
       <c r="J54" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K54" t="s">
+        <v>294</v>
+      </c>
+      <c r="L54" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>317</v>
       </c>
       <c r="E55" t="s">
-        <v>176</v>
-      </c>
-      <c r="F55" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>319</v>
+      </c>
+      <c r="H55" t="s">
+        <v>316</v>
       </c>
       <c r="I55" t="s">
-        <v>54</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>164</v>
+        <v>57</v>
       </c>
       <c r="K55" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>294</v>
+      </c>
+      <c r="L55" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>322</v>
+      </c>
+      <c r="D56" t="s">
+        <v>323</v>
+      </c>
+      <c r="E56" t="s">
+        <v>324</v>
+      </c>
+      <c r="G56" t="s">
+        <v>325</v>
+      </c>
+      <c r="H56" t="s">
+        <v>326</v>
       </c>
       <c r="I56" t="s">
-        <v>54</v>
+        <v>327</v>
       </c>
       <c r="J56" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K56" t="s">
+        <v>294</v>
+      </c>
+      <c r="L56" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>329</v>
+      </c>
+      <c r="D57" t="s">
+        <v>330</v>
+      </c>
+      <c r="E57" t="s">
+        <v>331</v>
+      </c>
+      <c r="G57" t="s">
+        <v>332</v>
+      </c>
+      <c r="H57" t="s">
+        <v>333</v>
       </c>
       <c r="I57" t="s">
-        <v>54</v>
+        <v>334</v>
       </c>
       <c r="J57" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K57" t="s">
+        <v>294</v>
+      </c>
+      <c r="L57" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>181</v>
-      </c>
-      <c r="I58" t="s">
-        <v>54</v>
+        <v>336</v>
       </c>
       <c r="J58" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K58" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>338</v>
       </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>339</v>
       </c>
       <c r="E59" t="s">
-        <v>185</v>
-      </c>
-      <c r="F59" t="s">
-        <v>186</v>
+        <v>340</v>
       </c>
       <c r="G59" t="s">
-        <v>187</v>
+        <v>341</v>
+      </c>
+      <c r="H59" t="s">
+        <v>342</v>
       </c>
       <c r="I59" t="s">
-        <v>54</v>
+        <v>343</v>
       </c>
       <c r="J59" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
       <c r="K59" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>337</v>
+      </c>
+      <c r="L59" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
-      </c>
-      <c r="I60" t="s">
-        <v>54</v>
+        <v>345</v>
       </c>
       <c r="J60" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K60" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
-      </c>
-      <c r="I61" t="s">
-        <v>54</v>
+        <v>346</v>
       </c>
       <c r="J61" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K61" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
-      </c>
-      <c r="I62" t="s">
-        <v>54</v>
+        <v>347</v>
       </c>
       <c r="J62" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K62" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>192</v>
-      </c>
-      <c r="I63" t="s">
-        <v>54</v>
+        <v>348</v>
       </c>
       <c r="J63" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>193</v>
-      </c>
-      <c r="I64" t="s">
-        <v>54</v>
+        <v>349</v>
       </c>
       <c r="J64" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K64" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>194</v>
-      </c>
-      <c r="I65" t="s">
-        <v>54</v>
+        <v>350</v>
       </c>
       <c r="J65" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>195</v>
-      </c>
-      <c r="I66" t="s">
-        <v>54</v>
+        <v>351</v>
       </c>
       <c r="J66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>196</v>
-      </c>
-      <c r="I67" t="s">
-        <v>54</v>
+        <v>352</v>
       </c>
       <c r="J67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K67" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>197</v>
-      </c>
-      <c r="I68" t="s">
-        <v>54</v>
+        <v>353</v>
       </c>
       <c r="J68" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K68" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>198</v>
+        <v>354</v>
       </c>
       <c r="D69" t="s">
-        <v>199</v>
+        <v>355</v>
       </c>
       <c r="E69" t="s">
-        <v>200</v>
-      </c>
-      <c r="F69" t="s">
-        <v>201</v>
+        <v>356</v>
       </c>
       <c r="G69" t="s">
-        <v>202</v>
-      </c>
-      <c r="I69" t="s">
-        <v>54</v>
+        <v>357</v>
+      </c>
+      <c r="H69" t="s">
+        <v>358</v>
       </c>
       <c r="J69" t="s">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="K69" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+        <v>359</v>
+      </c>
+      <c r="L69" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>205</v>
-      </c>
-      <c r="I70" t="s">
-        <v>54</v>
+        <v>361</v>
       </c>
       <c r="J70" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K70" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>206</v>
-      </c>
-      <c r="I71" t="s">
-        <v>54</v>
+        <v>362</v>
       </c>
       <c r="J71" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K71" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>207</v>
+        <v>363</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>363</v>
       </c>
       <c r="E72" t="s">
-        <v>208</v>
-      </c>
-      <c r="F72" t="s">
-        <v>209</v>
+        <v>364</v>
       </c>
       <c r="G72" t="s">
-        <v>210</v>
-      </c>
-      <c r="I72" t="s">
-        <v>54</v>
+        <v>365</v>
+      </c>
+      <c r="H72" t="s">
+        <v>366</v>
       </c>
       <c r="J72" t="s">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="K72" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
+        <v>359</v>
+      </c>
+      <c r="L72" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>212</v>
+        <v>368</v>
       </c>
       <c r="D73" t="s">
-        <v>213</v>
+        <v>369</v>
       </c>
       <c r="E73" t="s">
-        <v>214</v>
-      </c>
-      <c r="F73" t="s">
-        <v>215</v>
+        <v>370</v>
       </c>
       <c r="G73" t="s">
-        <v>216</v>
-      </c>
-      <c r="I73" t="s">
-        <v>54</v>
+        <v>371</v>
+      </c>
+      <c r="H73" t="s">
+        <v>372</v>
       </c>
       <c r="J73" t="s">
-        <v>203</v>
+        <v>57</v>
       </c>
       <c r="K73" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
+        <v>359</v>
+      </c>
+      <c r="L73" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>218</v>
-      </c>
-      <c r="I74" t="s">
-        <v>54</v>
+        <v>374</v>
       </c>
       <c r="J74" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K74" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
-      </c>
-      <c r="I75" t="s">
-        <v>54</v>
+        <v>375</v>
       </c>
       <c r="J75" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K75" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>220</v>
-      </c>
-      <c r="I76" t="s">
-        <v>54</v>
+        <v>376</v>
       </c>
       <c r="J76" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K76" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>221</v>
-      </c>
-      <c r="I77" t="s">
-        <v>54</v>
+        <v>377</v>
       </c>
       <c r="J77" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>223</v>
-      </c>
-      <c r="I78" t="s">
-        <v>54</v>
+        <v>379</v>
       </c>
       <c r="J78" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K78" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>224</v>
-      </c>
-      <c r="I79" t="s">
-        <v>54</v>
+        <v>380</v>
       </c>
       <c r="J79" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K79" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>225</v>
-      </c>
-      <c r="I80" t="s">
-        <v>54</v>
+        <v>381</v>
       </c>
       <c r="J80" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K80" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>226</v>
-      </c>
-      <c r="I81" t="s">
-        <v>54</v>
+        <v>382</v>
       </c>
       <c r="J81" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K81" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>227</v>
-      </c>
-      <c r="I82" t="s">
-        <v>54</v>
+        <v>383</v>
       </c>
       <c r="J82" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K82" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="D83" t="s">
-        <v>229</v>
+        <v>385</v>
       </c>
       <c r="E83" t="s">
-        <v>230</v>
-      </c>
-      <c r="F83" t="s">
-        <v>231</v>
+        <v>386</v>
       </c>
       <c r="G83" t="s">
-        <v>232</v>
-      </c>
-      <c r="I83" t="s">
-        <v>54</v>
+        <v>387</v>
+      </c>
+      <c r="H83" t="s">
+        <v>388</v>
       </c>
       <c r="J83" t="s">
-        <v>222</v>
+        <v>57</v>
       </c>
       <c r="K83" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
+        <v>378</v>
+      </c>
+      <c r="L83" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>234</v>
-      </c>
-      <c r="I84" t="s">
-        <v>54</v>
+        <v>390</v>
       </c>
       <c r="J84" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K84" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
-      </c>
-      <c r="I85" t="s">
-        <v>54</v>
+        <v>391</v>
       </c>
       <c r="J85" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K85" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>236</v>
-      </c>
-      <c r="I86" t="s">
-        <v>54</v>
+        <v>392</v>
       </c>
       <c r="J86" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K86" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>237</v>
-      </c>
-      <c r="I87" t="s">
-        <v>54</v>
+        <v>393</v>
       </c>
       <c r="J87" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K87" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>238</v>
-      </c>
-      <c r="I88" t="s">
-        <v>54</v>
+        <v>394</v>
       </c>
       <c r="J88" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K88" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>239</v>
-      </c>
-      <c r="I89" t="s">
-        <v>54</v>
+        <v>395</v>
       </c>
       <c r="J89" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K89" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
-      </c>
-      <c r="I90" t="s">
-        <v>54</v>
+        <v>396</v>
       </c>
       <c r="J90" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K90" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
-      </c>
-      <c r="I91" t="s">
-        <v>54</v>
+        <v>397</v>
       </c>
       <c r="J91" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K91" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>242</v>
-      </c>
-      <c r="I92" t="s">
-        <v>54</v>
+        <v>398</v>
       </c>
       <c r="J92" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K92" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C93" t="s">
-        <v>243</v>
-      </c>
-      <c r="I93" t="s">
-        <v>54</v>
+        <v>399</v>
       </c>
       <c r="J93" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
+        <v>57</v>
+      </c>
+      <c r="K93" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C94" t="s">
-        <v>244</v>
+        <v>400</v>
       </c>
       <c r="D94" t="s">
-        <v>244</v>
+        <v>400</v>
       </c>
       <c r="E94" t="s">
-        <v>245</v>
-      </c>
-      <c r="F94" t="s">
-        <v>246</v>
+        <v>401</v>
       </c>
       <c r="G94" t="s">
-        <v>247</v>
+        <v>402</v>
+      </c>
+      <c r="H94" t="s">
+        <v>403</v>
       </c>
       <c r="I94" t="s">
-        <v>248</v>
+        <v>404</v>
       </c>
       <c r="J94" t="s">
-        <v>249</v>
+        <v>405</v>
       </c>
       <c r="K94" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
+        <v>406</v>
+      </c>
+      <c r="L94" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C95" t="s">
-        <v>251</v>
+        <v>408</v>
+      </c>
+      <c r="D95" t="s">
+        <v>409</v>
+      </c>
+      <c r="E95" t="s">
+        <v>410</v>
+      </c>
+      <c r="G95" t="s">
+        <v>411</v>
+      </c>
+      <c r="H95" t="s">
+        <v>412</v>
       </c>
       <c r="I95" t="s">
-        <v>248</v>
+        <v>413</v>
       </c>
       <c r="J95" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K95" t="s">
+        <v>406</v>
+      </c>
+      <c r="L95" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
+        <v>415</v>
       </c>
       <c r="D96" t="s">
-        <v>253</v>
+        <v>416</v>
       </c>
       <c r="E96" t="s">
-        <v>254</v>
-      </c>
-      <c r="F96" t="s">
-        <v>255</v>
+        <v>417</v>
       </c>
       <c r="G96" t="s">
-        <v>256</v>
-      </c>
-      <c r="I96" t="s">
-        <v>248</v>
+        <v>418</v>
+      </c>
+      <c r="H96" t="s">
+        <v>419</v>
       </c>
       <c r="J96" t="s">
-        <v>257</v>
+        <v>405</v>
       </c>
       <c r="K96" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>420</v>
+      </c>
+      <c r="L96" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>259</v>
-      </c>
-      <c r="I97" t="s">
-        <v>248</v>
+        <v>422</v>
       </c>
       <c r="J97" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K97" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>260</v>
-      </c>
-      <c r="I98" t="s">
-        <v>248</v>
+        <v>423</v>
       </c>
       <c r="J98" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K98" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>261</v>
-      </c>
-      <c r="I99" t="s">
-        <v>248</v>
+        <v>424</v>
       </c>
       <c r="J99" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K99" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C100" t="s">
-        <v>262</v>
-      </c>
-      <c r="I100" t="s">
-        <v>248</v>
+        <v>425</v>
       </c>
       <c r="J100" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K100" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
-      </c>
-      <c r="I101" t="s">
-        <v>248</v>
+        <v>426</v>
       </c>
       <c r="J101" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K101" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C102" t="s">
-        <v>264</v>
-      </c>
-      <c r="I102" t="s">
-        <v>248</v>
+        <v>427</v>
       </c>
       <c r="J102" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K102" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>265</v>
-      </c>
-      <c r="I103" t="s">
-        <v>248</v>
+        <v>428</v>
       </c>
       <c r="J103" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K103" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C104" t="s">
-        <v>266</v>
-      </c>
-      <c r="I104" t="s">
-        <v>248</v>
+        <v>429</v>
       </c>
       <c r="J104" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K104" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C105" t="s">
-        <v>268</v>
-      </c>
-      <c r="I105" t="s">
-        <v>248</v>
+        <v>431</v>
       </c>
       <c r="J105" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K105" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C106" t="s">
-        <v>269</v>
-      </c>
-      <c r="I106" t="s">
-        <v>248</v>
+        <v>432</v>
       </c>
       <c r="J106" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K106" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>270</v>
-      </c>
-      <c r="I107" t="s">
-        <v>248</v>
+        <v>433</v>
       </c>
       <c r="J107" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K107" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C108" t="s">
-        <v>271</v>
-      </c>
-      <c r="I108" t="s">
-        <v>248</v>
+        <v>434</v>
       </c>
       <c r="J108" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K108" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>272</v>
-      </c>
-      <c r="I109" t="s">
-        <v>248</v>
+        <v>435</v>
       </c>
       <c r="J109" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K109" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>273</v>
-      </c>
-      <c r="I110" t="s">
-        <v>248</v>
+        <v>436</v>
       </c>
       <c r="J110" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K110" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C111" t="s">
-        <v>274</v>
-      </c>
-      <c r="I111" t="s">
-        <v>248</v>
+        <v>437</v>
       </c>
       <c r="J111" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
+        <v>405</v>
+      </c>
+      <c r="K111" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C112" t="s">
-        <v>275</v>
-      </c>
-      <c r="I112" t="s">
-        <v>248</v>
+        <v>438</v>
       </c>
       <c r="J112" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K112" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C113" t="s">
-        <v>276</v>
-      </c>
-      <c r="I113" t="s">
-        <v>248</v>
+        <v>439</v>
       </c>
       <c r="J113" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K113" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>277</v>
-      </c>
-      <c r="I114" t="s">
-        <v>248</v>
+        <v>440</v>
       </c>
       <c r="J114" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K114" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C115" t="s">
-        <v>278</v>
-      </c>
-      <c r="I115" t="s">
-        <v>248</v>
+        <v>441</v>
       </c>
       <c r="J115" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K115" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
-        <v>279</v>
-      </c>
-      <c r="I116" t="s">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="J116" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
+        <v>405</v>
+      </c>
+      <c r="K116" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>280</v>
+        <v>443</v>
       </c>
       <c r="D117" t="s">
-        <v>280</v>
+        <v>443</v>
       </c>
       <c r="E117" t="s">
-        <v>281</v>
-      </c>
-      <c r="F117" t="s">
-        <v>282</v>
+        <v>444</v>
       </c>
       <c r="G117" t="s">
-        <v>283</v>
-      </c>
-      <c r="I117" t="s">
-        <v>284</v>
+        <v>445</v>
+      </c>
+      <c r="H117" t="s">
+        <v>446</v>
       </c>
       <c r="J117" t="s">
-        <v>285</v>
+        <v>447</v>
       </c>
       <c r="K117" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
+        <v>448</v>
+      </c>
+      <c r="L117" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>287</v>
-      </c>
-      <c r="I118" t="s">
-        <v>284</v>
+        <v>450</v>
       </c>
       <c r="J118" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K118" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
-        <v>288</v>
+        <v>451</v>
       </c>
       <c r="D119" t="s">
-        <v>289</v>
+        <v>452</v>
       </c>
       <c r="E119" t="s">
-        <v>290</v>
-      </c>
-      <c r="F119" t="s">
-        <v>291</v>
+        <v>453</v>
       </c>
       <c r="G119" t="s">
-        <v>292</v>
-      </c>
-      <c r="I119" t="s">
-        <v>284</v>
+        <v>454</v>
+      </c>
+      <c r="H119" t="s">
+        <v>455</v>
       </c>
       <c r="J119" t="s">
-        <v>285</v>
+        <v>447</v>
       </c>
       <c r="K119" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
+        <v>448</v>
+      </c>
+      <c r="L119" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
-        <v>294</v>
-      </c>
-      <c r="I120" t="s">
-        <v>284</v>
+        <v>457</v>
       </c>
       <c r="J120" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K120" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
-      </c>
-      <c r="I121" t="s">
-        <v>284</v>
+        <v>458</v>
       </c>
       <c r="J121" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K121" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C122" t="s">
-        <v>296</v>
-      </c>
-      <c r="I122" t="s">
-        <v>284</v>
+        <v>459</v>
       </c>
       <c r="J122" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K122" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C123" t="s">
-        <v>297</v>
-      </c>
-      <c r="I123" t="s">
-        <v>284</v>
+        <v>460</v>
       </c>
       <c r="J123" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K123" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>298</v>
-      </c>
-      <c r="I124" t="s">
-        <v>284</v>
+        <v>461</v>
       </c>
       <c r="J124" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K124" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C125" t="s">
-        <v>299</v>
-      </c>
-      <c r="I125" t="s">
-        <v>284</v>
+        <v>462</v>
       </c>
       <c r="J125" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K125" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>300</v>
-      </c>
-      <c r="I126" t="s">
-        <v>284</v>
+        <v>463</v>
       </c>
       <c r="J126" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K126" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C127" t="s">
-        <v>301</v>
-      </c>
-      <c r="I127" t="s">
-        <v>284</v>
+        <v>464</v>
       </c>
       <c r="J127" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
+        <v>447</v>
+      </c>
+      <c r="K127" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>302</v>
-      </c>
-      <c r="I128" t="s">
-        <v>284</v>
+        <v>465</v>
       </c>
       <c r="J128" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10">
+        <v>447</v>
+      </c>
+      <c r="K128" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C129" t="s">
-        <v>303</v>
+        <v>466</v>
       </c>
       <c r="D129" t="s">
-        <v>304</v>
+        <v>467</v>
       </c>
       <c r="E129" t="s">
-        <v>305</v>
-      </c>
-      <c r="F129" t="s">
-        <v>306</v>
+        <v>468</v>
       </c>
       <c r="G129" t="s">
-        <v>307</v>
-      </c>
-      <c r="I129" t="s">
-        <v>308</v>
+        <v>469</v>
+      </c>
+      <c r="H129" t="s">
+        <v>470</v>
       </c>
       <c r="J129" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K129" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>309</v>
-      </c>
-      <c r="I130" t="s">
-        <v>308</v>
+        <v>472</v>
       </c>
       <c r="J130" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K130" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C131" t="s">
-        <v>310</v>
-      </c>
-      <c r="I131" t="s">
-        <v>308</v>
+        <v>473</v>
       </c>
       <c r="J131" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K131" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>311</v>
-      </c>
-      <c r="I132" t="s">
-        <v>308</v>
+        <v>474</v>
       </c>
       <c r="J132" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K132" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C133" t="s">
-        <v>312</v>
-      </c>
-      <c r="I133" t="s">
-        <v>308</v>
+        <v>475</v>
       </c>
       <c r="J133" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K133" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>313</v>
-      </c>
-      <c r="I134" t="s">
-        <v>308</v>
+        <v>476</v>
       </c>
       <c r="J134" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K134" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C135" t="s">
-        <v>314</v>
-      </c>
-      <c r="I135" t="s">
-        <v>308</v>
+        <v>477</v>
       </c>
       <c r="J135" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K135" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C136" t="s">
-        <v>315</v>
-      </c>
-      <c r="I136" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
       <c r="J136" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K136" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
-        <v>316</v>
-      </c>
-      <c r="I137" t="s">
-        <v>308</v>
+        <v>479</v>
       </c>
       <c r="J137" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K137" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C138" t="s">
-        <v>317</v>
-      </c>
-      <c r="I138" t="s">
-        <v>308</v>
+        <v>480</v>
       </c>
       <c r="J138" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K138" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
-        <v>318</v>
-      </c>
-      <c r="I139" t="s">
-        <v>308</v>
+        <v>481</v>
       </c>
       <c r="J139" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K139" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>319</v>
-      </c>
-      <c r="I140" t="s">
-        <v>308</v>
+        <v>482</v>
       </c>
       <c r="J140" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K140" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>320</v>
-      </c>
-      <c r="I141" t="s">
-        <v>308</v>
+        <v>483</v>
       </c>
       <c r="J141" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K141" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C142" t="s">
-        <v>321</v>
-      </c>
-      <c r="I142" t="s">
-        <v>308</v>
+        <v>484</v>
       </c>
       <c r="J142" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K142" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C143" t="s">
-        <v>322</v>
-      </c>
-      <c r="I143" t="s">
-        <v>308</v>
+        <v>485</v>
       </c>
       <c r="J143" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K143" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>323</v>
-      </c>
-      <c r="I144" t="s">
-        <v>308</v>
+        <v>486</v>
       </c>
       <c r="J144" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10">
+        <v>471</v>
+      </c>
+      <c r="K144" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>324</v>
-      </c>
-      <c r="I145" t="s">
-        <v>325</v>
+        <v>487</v>
       </c>
       <c r="J145" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K145" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>327</v>
-      </c>
-      <c r="I146" t="s">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="J146" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K146" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C147" t="s">
-        <v>328</v>
-      </c>
-      <c r="I147" t="s">
-        <v>325</v>
+        <v>491</v>
       </c>
       <c r="J147" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K147" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C148" t="s">
-        <v>329</v>
-      </c>
-      <c r="I148" t="s">
-        <v>325</v>
+        <v>492</v>
       </c>
       <c r="J148" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K148" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C149" t="s">
-        <v>330</v>
-      </c>
-      <c r="I149" t="s">
-        <v>325</v>
+        <v>493</v>
       </c>
       <c r="J149" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K149" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C150" t="s">
-        <v>331</v>
-      </c>
-      <c r="I150" t="s">
-        <v>325</v>
+        <v>494</v>
       </c>
       <c r="J150" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K150" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
-        <v>332</v>
-      </c>
-      <c r="I151" t="s">
-        <v>325</v>
+        <v>495</v>
       </c>
       <c r="J151" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K151" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C152" t="s">
-        <v>334</v>
-      </c>
-      <c r="I152" t="s">
-        <v>325</v>
+        <v>497</v>
       </c>
       <c r="J152" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K152" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C153" t="s">
-        <v>335</v>
-      </c>
-      <c r="I153" t="s">
-        <v>325</v>
+        <v>498</v>
       </c>
       <c r="J153" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K153" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C154" t="s">
-        <v>336</v>
-      </c>
-      <c r="I154" t="s">
-        <v>325</v>
+        <v>499</v>
       </c>
       <c r="J154" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K154" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C155" t="s">
-        <v>337</v>
-      </c>
-      <c r="I155" t="s">
-        <v>325</v>
+        <v>500</v>
       </c>
       <c r="J155" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K155" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
-        <v>338</v>
-      </c>
-      <c r="I156" t="s">
-        <v>325</v>
+        <v>501</v>
       </c>
       <c r="J156" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K156" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C157" t="s">
-        <v>339</v>
-      </c>
-      <c r="I157" t="s">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="J157" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K157" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C158" t="s">
-        <v>340</v>
-      </c>
-      <c r="I158" t="s">
-        <v>325</v>
+        <v>503</v>
       </c>
       <c r="J158" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K158" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C159" t="s">
-        <v>341</v>
-      </c>
-      <c r="I159" t="s">
-        <v>325</v>
+        <v>504</v>
       </c>
       <c r="J159" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K159" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>342</v>
-      </c>
-      <c r="I160" t="s">
-        <v>325</v>
+        <v>505</v>
       </c>
       <c r="J160" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="161" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K160" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C161" t="s">
-        <v>343</v>
-      </c>
-      <c r="I161" t="s">
-        <v>325</v>
+        <v>506</v>
       </c>
       <c r="J161" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K161" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>344</v>
-      </c>
-      <c r="I162" t="s">
-        <v>325</v>
+        <v>507</v>
       </c>
       <c r="J162" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K162" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>345</v>
-      </c>
-      <c r="I163" t="s">
-        <v>325</v>
+        <v>508</v>
       </c>
       <c r="J163" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="164" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K163" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C164" t="s">
-        <v>346</v>
-      </c>
-      <c r="I164" t="s">
-        <v>325</v>
+        <v>509</v>
       </c>
       <c r="J164" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="165" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K164" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>347</v>
-      </c>
-      <c r="I165" t="s">
-        <v>325</v>
+        <v>510</v>
       </c>
       <c r="J165" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="166" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K165" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C166" t="s">
-        <v>348</v>
-      </c>
-      <c r="I166" t="s">
-        <v>325</v>
+        <v>511</v>
       </c>
       <c r="J166" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="167" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K166" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>349</v>
-      </c>
-      <c r="I167" t="s">
-        <v>325</v>
+        <v>512</v>
       </c>
       <c r="J167" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="168" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K167" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C168" t="s">
-        <v>351</v>
-      </c>
-      <c r="I168" t="s">
-        <v>325</v>
+        <v>514</v>
       </c>
       <c r="J168" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="169" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K168" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C169" t="s">
-        <v>352</v>
-      </c>
-      <c r="I169" t="s">
-        <v>325</v>
+        <v>515</v>
       </c>
       <c r="J169" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="170" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K169" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C170" t="s">
-        <v>353</v>
-      </c>
-      <c r="I170" t="s">
-        <v>325</v>
+        <v>516</v>
       </c>
       <c r="J170" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="171" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K170" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C171" t="s">
-        <v>354</v>
-      </c>
-      <c r="I171" t="s">
-        <v>325</v>
+        <v>517</v>
       </c>
       <c r="J171" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K171" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
       <c r="A172">
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C172" t="s">
-        <v>355</v>
-      </c>
-      <c r="I172" t="s">
-        <v>325</v>
+        <v>518</v>
       </c>
       <c r="J172" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K172" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C173" t="s">
-        <v>356</v>
-      </c>
-      <c r="I173" t="s">
-        <v>325</v>
+        <v>519</v>
       </c>
       <c r="J173" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K173" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C174" t="s">
-        <v>357</v>
-      </c>
-      <c r="I174" t="s">
-        <v>325</v>
+        <v>520</v>
       </c>
       <c r="J174" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K174" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C175" t="s">
-        <v>358</v>
-      </c>
-      <c r="I175" t="s">
-        <v>325</v>
+        <v>521</v>
       </c>
       <c r="J175" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="176" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K175" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
       <c r="A176">
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C176" t="s">
-        <v>359</v>
-      </c>
-      <c r="I176" t="s">
-        <v>325</v>
+        <v>522</v>
       </c>
       <c r="J176" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="177" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K176" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
       <c r="A177">
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C177" t="s">
-        <v>360</v>
-      </c>
-      <c r="I177" t="s">
-        <v>325</v>
+        <v>523</v>
       </c>
       <c r="J177" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="178" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K177" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C178" t="s">
-        <v>361</v>
-      </c>
-      <c r="I178" t="s">
-        <v>325</v>
+        <v>524</v>
       </c>
       <c r="J178" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="179" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K178" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C179" t="s">
-        <v>363</v>
-      </c>
-      <c r="I179" t="s">
-        <v>325</v>
+        <v>526</v>
       </c>
       <c r="J179" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="180" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K179" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C180" t="s">
-        <v>362</v>
-      </c>
-      <c r="I180" t="s">
-        <v>325</v>
+        <v>525</v>
       </c>
       <c r="J180" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="181" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K180" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
       <c r="A181">
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C181" t="s">
-        <v>364</v>
-      </c>
-      <c r="I181" t="s">
-        <v>325</v>
+        <v>527</v>
       </c>
       <c r="J181" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="182" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K181" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C182" t="s">
-        <v>365</v>
-      </c>
-      <c r="I182" t="s">
-        <v>325</v>
+        <v>528</v>
       </c>
       <c r="J182" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="183" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K182" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C183" t="s">
-        <v>366</v>
-      </c>
-      <c r="I183" t="s">
-        <v>325</v>
+        <v>529</v>
       </c>
       <c r="J183" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="184" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K183" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C184" t="s">
-        <v>367</v>
-      </c>
-      <c r="I184" t="s">
-        <v>325</v>
+        <v>530</v>
       </c>
       <c r="J184" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="185" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K184" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
-        <v>368</v>
-      </c>
-      <c r="I185" t="s">
-        <v>325</v>
+        <v>531</v>
       </c>
       <c r="J185" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="186" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K185" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>369</v>
-      </c>
-      <c r="I186" t="s">
-        <v>325</v>
+        <v>532</v>
       </c>
       <c r="J186" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="187" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K186" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C187" t="s">
-        <v>371</v>
-      </c>
-      <c r="I187" t="s">
-        <v>325</v>
+        <v>534</v>
       </c>
       <c r="J187" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="188" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K187" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>372</v>
-      </c>
-      <c r="I188" t="s">
-        <v>325</v>
+        <v>535</v>
       </c>
       <c r="J188" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="189" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K188" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C189" t="s">
-        <v>373</v>
-      </c>
-      <c r="I189" t="s">
-        <v>325</v>
+        <v>536</v>
       </c>
       <c r="J189" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="190" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K189" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C190" t="s">
-        <v>374</v>
-      </c>
-      <c r="I190" t="s">
-        <v>325</v>
+        <v>537</v>
       </c>
       <c r="J190" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="191" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K190" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C191" t="s">
-        <v>375</v>
-      </c>
-      <c r="I191" t="s">
-        <v>325</v>
+        <v>538</v>
       </c>
       <c r="J191" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="192" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K191" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C192" t="s">
-        <v>376</v>
-      </c>
-      <c r="I192" t="s">
-        <v>325</v>
+        <v>539</v>
       </c>
       <c r="J192" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="193" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K192" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
       <c r="A193">
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C193" t="s">
-        <v>377</v>
-      </c>
-      <c r="I193" t="s">
-        <v>325</v>
+        <v>540</v>
       </c>
       <c r="J193" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="194" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K193" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
       <c r="A194">
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C194" t="s">
-        <v>378</v>
-      </c>
-      <c r="I194" t="s">
-        <v>325</v>
+        <v>541</v>
       </c>
       <c r="J194" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="195" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K194" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
       <c r="A195">
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C195" t="s">
-        <v>379</v>
-      </c>
-      <c r="I195" t="s">
-        <v>325</v>
+        <v>542</v>
       </c>
       <c r="J195" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="196" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K195" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
       <c r="A196">
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C196" t="s">
-        <v>370</v>
-      </c>
-      <c r="I196" t="s">
-        <v>325</v>
+        <v>533</v>
       </c>
       <c r="J196" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K196" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C197" t="s">
-        <v>380</v>
-      </c>
-      <c r="I197" t="s">
-        <v>325</v>
+        <v>543</v>
       </c>
       <c r="J197" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10">
+        <v>488</v>
+      </c>
+      <c r="K197" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
       <c r="A198">
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C198" t="s">
-        <v>381</v>
-      </c>
-      <c r="I198" t="s">
-        <v>325</v>
+        <v>544</v>
       </c>
       <c r="J198" t="s">
-        <v>370</v>
+        <v>488</v>
+      </c>
+      <c r="K198" t="s">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L198" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/public/docs/datas/world.xlsx
+++ b/public/docs/datas/world.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24700" windowHeight="17260"/>
+    <workbookView windowWidth="24700" windowHeight="14900"/>
   </bookViews>
   <sheets>
     <sheet name="country" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">country!$A$1:$L$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">country!$A$1:$K$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="662">
   <si>
     <t>no</t>
   </si>
@@ -47,9 +47,6 @@
     <t>enName</t>
   </si>
   <si>
-    <t>shortName</t>
-  </si>
-  <si>
     <t>flag</t>
   </si>
   <si>
@@ -182,6 +179,909 @@
     <t>MNG</t>
   </si>
   <si>
+    <t>缅甸</t>
+  </si>
+  <si>
+    <t>缅甸联邦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of the Union of Myanmar</t>
+  </si>
+  <si>
+    <t>Myanmar.jpg</t>
+  </si>
+  <si>
+    <t>内比都</t>
+  </si>
+  <si>
+    <t>Nay Pyi Taw</t>
+  </si>
+  <si>
+    <t>东南亚</t>
+  </si>
+  <si>
+    <t>MMR</t>
+  </si>
+  <si>
+    <t>文莱</t>
+  </si>
+  <si>
+    <t>文莱达鲁萨兰国</t>
+  </si>
+  <si>
+    <t>Negara Brunei Darussalam</t>
+  </si>
+  <si>
+    <t>Brunei.png</t>
+  </si>
+  <si>
+    <t>斯里巴加湾市</t>
+  </si>
+  <si>
+    <t>Bandar Seri Begawan</t>
+  </si>
+  <si>
+    <t>BRN</t>
+  </si>
+  <si>
+    <t>柬埔寨</t>
+  </si>
+  <si>
+    <t>柬埔寨王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Cambodia</t>
+  </si>
+  <si>
+    <t>Cambodia.png</t>
+  </si>
+  <si>
+    <t>金边</t>
+  </si>
+  <si>
+    <t>Phnom Penh</t>
+  </si>
+  <si>
+    <t>KHM</t>
+  </si>
+  <si>
+    <t>东帝汶</t>
+  </si>
+  <si>
+    <t>东帝汶民主共和国</t>
+  </si>
+  <si>
+    <t>Democratic Republic of Timor-Leste</t>
+  </si>
+  <si>
+    <t>Timor-Leste.png</t>
+  </si>
+  <si>
+    <t>帝力</t>
+  </si>
+  <si>
+    <t>Díli</t>
+  </si>
+  <si>
+    <t>TLS</t>
+  </si>
+  <si>
+    <t>印度尼西亚</t>
+  </si>
+  <si>
+    <t>印度尼西亚共和国</t>
+  </si>
+  <si>
+    <t>Republic of Indonesia</t>
+  </si>
+  <si>
+    <t>Indonesia.png</t>
+  </si>
+  <si>
+    <t>努山塔拉</t>
+  </si>
+  <si>
+    <t>Nusantara</t>
+  </si>
+  <si>
+    <t>IDN</t>
+  </si>
+  <si>
+    <t>老挝</t>
+  </si>
+  <si>
+    <t>老挝人民民主共和国</t>
+  </si>
+  <si>
+    <t>The Lao People’s Democratic Republic</t>
+  </si>
+  <si>
+    <t>Laos.png</t>
+  </si>
+  <si>
+    <t>万象</t>
+  </si>
+  <si>
+    <t>Vientiane</t>
+  </si>
+  <si>
+    <t>LAO</t>
+  </si>
+  <si>
+    <t>马来西亚</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Malaysia.png</t>
+  </si>
+  <si>
+    <t>吉隆坡</t>
+  </si>
+  <si>
+    <t>Kuala Lumpur</t>
+  </si>
+  <si>
+    <t>MYS</t>
+  </si>
+  <si>
+    <t>菲律宾</t>
+  </si>
+  <si>
+    <t>菲律宾共和国</t>
+  </si>
+  <si>
+    <t>Republic of the Philippines</t>
+  </si>
+  <si>
+    <t>Philippines.png</t>
+  </si>
+  <si>
+    <t>大马尼拉市</t>
+  </si>
+  <si>
+    <t>Manila</t>
+  </si>
+  <si>
+    <t>PHL</t>
+  </si>
+  <si>
+    <t>新加坡</t>
+  </si>
+  <si>
+    <t>新加坡共和国</t>
+  </si>
+  <si>
+    <t>Republic of Singapore</t>
+  </si>
+  <si>
+    <t>Singapore.png</t>
+  </si>
+  <si>
+    <t>新加坡市</t>
+  </si>
+  <si>
+    <t>Singapore City</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>泰国</t>
+  </si>
+  <si>
+    <t>泰王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Thailand</t>
+  </si>
+  <si>
+    <t>Thailand.png</t>
+  </si>
+  <si>
+    <t>曼谷</t>
+  </si>
+  <si>
+    <t>Krung Thep Maha Nakhon</t>
+  </si>
+  <si>
+    <t>THA</t>
+  </si>
+  <si>
+    <t>越南</t>
+  </si>
+  <si>
+    <t>越南社会主义共和国</t>
+  </si>
+  <si>
+    <t>The Socialist Republic of Viet Nam</t>
+  </si>
+  <si>
+    <t>Vietnam.png</t>
+  </si>
+  <si>
+    <t>河内</t>
+  </si>
+  <si>
+    <t>Hanoi</t>
+  </si>
+  <si>
+    <t>VNM</t>
+  </si>
+  <si>
+    <t>孟加拉国</t>
+  </si>
+  <si>
+    <t>孟加拉人民共和国</t>
+  </si>
+  <si>
+    <t>The People’s Republic of Bangladesh</t>
+  </si>
+  <si>
+    <t>Bangladesh.png</t>
+  </si>
+  <si>
+    <t>达卡</t>
+  </si>
+  <si>
+    <t>Dhaka</t>
+  </si>
+  <si>
+    <t>南亚</t>
+  </si>
+  <si>
+    <t>BGD</t>
+  </si>
+  <si>
+    <t>不丹</t>
+  </si>
+  <si>
+    <t>不丹王国</t>
+  </si>
+  <si>
+    <t>Kingdom of Bhutan</t>
+  </si>
+  <si>
+    <t>Bhutan.png</t>
+  </si>
+  <si>
+    <t>廷布</t>
+  </si>
+  <si>
+    <t>Thimphu</t>
+  </si>
+  <si>
+    <t>BTN</t>
+  </si>
+  <si>
+    <t>印度</t>
+  </si>
+  <si>
+    <t>印度共和国</t>
+  </si>
+  <si>
+    <t>The Republic of India</t>
+  </si>
+  <si>
+    <t>India.png</t>
+  </si>
+  <si>
+    <t>新德里</t>
+  </si>
+  <si>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>马尔代夫</t>
+  </si>
+  <si>
+    <t>马尔代夫共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Maldives</t>
+  </si>
+  <si>
+    <t>Maldives.png</t>
+  </si>
+  <si>
+    <t>马累</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>MDV</t>
+  </si>
+  <si>
+    <t>尼泊尔</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>Nepal.png</t>
+  </si>
+  <si>
+    <t>加德满都</t>
+  </si>
+  <si>
+    <t>Kathmandu</t>
+  </si>
+  <si>
+    <t>NPL</t>
+  </si>
+  <si>
+    <t>巴基斯坦</t>
+  </si>
+  <si>
+    <t>巴基斯坦伊斯兰共和国</t>
+  </si>
+  <si>
+    <t>Islamic Republic of Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan.png</t>
+  </si>
+  <si>
+    <t>伊斯兰堡</t>
+  </si>
+  <si>
+    <t>Islamabad</t>
+  </si>
+  <si>
+    <t>PAK</t>
+  </si>
+  <si>
+    <t>斯里兰卡</t>
+  </si>
+  <si>
+    <t>斯里兰卡民主社会主义共和国</t>
+  </si>
+  <si>
+    <t>The Democratic Socialist Republic of Sri Lanka</t>
+  </si>
+  <si>
+    <t>Sri Lanka.png</t>
+  </si>
+  <si>
+    <t>科伦坡</t>
+  </si>
+  <si>
+    <t>Colombo</t>
+  </si>
+  <si>
+    <t>LKA</t>
+  </si>
+  <si>
+    <t>哈萨克斯坦</t>
+  </si>
+  <si>
+    <t>哈萨克斯坦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Kazakhstan</t>
+  </si>
+  <si>
+    <t>Kazakhstan.png</t>
+  </si>
+  <si>
+    <t>阿斯塔纳</t>
+  </si>
+  <si>
+    <t>Astana</t>
+  </si>
+  <si>
+    <t>中亚</t>
+  </si>
+  <si>
+    <t>KAZ</t>
+  </si>
+  <si>
+    <t>吉尔吉斯斯坦</t>
+  </si>
+  <si>
+    <t>吉尔吉斯共和国</t>
+  </si>
+  <si>
+    <t>Kyrgyz Republic</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan.png</t>
+  </si>
+  <si>
+    <t>比什凯克</t>
+  </si>
+  <si>
+    <t>Bishkek</t>
+  </si>
+  <si>
+    <t>KGZ</t>
+  </si>
+  <si>
+    <t>塔吉克斯坦</t>
+  </si>
+  <si>
+    <t>塔吉克斯坦共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Tajikistan</t>
+  </si>
+  <si>
+    <t>Tajikistan.png</t>
+  </si>
+  <si>
+    <t>杜尚别</t>
+  </si>
+  <si>
+    <t>Dushanbe</t>
+  </si>
+  <si>
+    <t>TJK</t>
+  </si>
+  <si>
+    <t>土库曼斯坦</t>
+  </si>
+  <si>
+    <t>Turkmenistan</t>
+  </si>
+  <si>
+    <t>Turkmenistan.png</t>
+  </si>
+  <si>
+    <t>阿什哈巴德市</t>
+  </si>
+  <si>
+    <t>Ashgabat</t>
+  </si>
+  <si>
+    <t>TKM</t>
+  </si>
+  <si>
+    <t>乌兹别克斯坦</t>
+  </si>
+  <si>
+    <t>乌兹别克斯坦共和国</t>
+  </si>
+  <si>
+    <t>Republic of Uzbekistan</t>
+  </si>
+  <si>
+    <t>Uzbekistan.png</t>
+  </si>
+  <si>
+    <t>塔什干</t>
+  </si>
+  <si>
+    <t>Tashkent</t>
+  </si>
+  <si>
+    <t>UZB</t>
+  </si>
+  <si>
+    <t>阿富汗</t>
+  </si>
+  <si>
+    <t>西亚</t>
+  </si>
+  <si>
+    <t>亚美尼亚</t>
+  </si>
+  <si>
+    <t>阿塞拜疆</t>
+  </si>
+  <si>
+    <t>阿塞拜疆共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Azerbaijan</t>
+  </si>
+  <si>
+    <t>Azerbaijan.png</t>
+  </si>
+  <si>
+    <t>巴库</t>
+  </si>
+  <si>
+    <t>AZE</t>
+  </si>
+  <si>
+    <t>巴林</t>
+  </si>
+  <si>
+    <t>巴林王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Bahrain</t>
+  </si>
+  <si>
+    <t>Bahrain.png</t>
+  </si>
+  <si>
+    <t>麦纳麦</t>
+  </si>
+  <si>
+    <t>BHR</t>
+  </si>
+  <si>
+    <t>塞浦路斯</t>
+  </si>
+  <si>
+    <t>格鲁吉亚</t>
+  </si>
+  <si>
+    <t>伊朗</t>
+  </si>
+  <si>
+    <t>伊朗伊斯兰共和国</t>
+  </si>
+  <si>
+    <t>The Islamic Republic of Iran</t>
+  </si>
+  <si>
+    <t>Iran.png</t>
+  </si>
+  <si>
+    <t>德黑兰</t>
+  </si>
+  <si>
+    <t>IRN</t>
+  </si>
+  <si>
+    <t>伊拉克</t>
+  </si>
+  <si>
+    <t>以色列</t>
+  </si>
+  <si>
+    <t>以色列国</t>
+  </si>
+  <si>
+    <t>The State of Israel</t>
+  </si>
+  <si>
+    <t>Israel.png</t>
+  </si>
+  <si>
+    <t>耶路撒冷</t>
+  </si>
+  <si>
+    <t>ISR</t>
+  </si>
+  <si>
+    <t>约旦</t>
+  </si>
+  <si>
+    <t>科威特</t>
+  </si>
+  <si>
+    <t>黎巴嫩</t>
+  </si>
+  <si>
+    <t>阿曼</t>
+  </si>
+  <si>
+    <t>巴勒斯坦</t>
+  </si>
+  <si>
+    <t>卡塔尔</t>
+  </si>
+  <si>
+    <t>卡塔尔国</t>
+  </si>
+  <si>
+    <t>The State of Qatar</t>
+  </si>
+  <si>
+    <t>Qatar.png</t>
+  </si>
+  <si>
+    <t>多哈</t>
+  </si>
+  <si>
+    <t>QAT</t>
+  </si>
+  <si>
+    <t>沙特阿拉伯</t>
+  </si>
+  <si>
+    <t>叙利亚</t>
+  </si>
+  <si>
+    <t>土耳其</t>
+  </si>
+  <si>
+    <t>土耳其共和国</t>
+  </si>
+  <si>
+    <t>Republic of Türkiye</t>
+  </si>
+  <si>
+    <t>Türkiye.png</t>
+  </si>
+  <si>
+    <t>安卡拉</t>
+  </si>
+  <si>
+    <t>TUR</t>
+  </si>
+  <si>
+    <t>阿联酋</t>
+  </si>
+  <si>
+    <t>阿拉伯联合酋长国</t>
+  </si>
+  <si>
+    <t>The United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Abu Dhabi.png</t>
+  </si>
+  <si>
+    <t>阿布扎比</t>
+  </si>
+  <si>
+    <t>Abu Dhabi</t>
+  </si>
+  <si>
+    <t>ARE</t>
+  </si>
+  <si>
+    <t>也门</t>
+  </si>
+  <si>
+    <t>比利时</t>
+  </si>
+  <si>
+    <t>比利时王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Belgium</t>
+  </si>
+  <si>
+    <t>Belgium.png</t>
+  </si>
+  <si>
+    <t>布鲁塞尔</t>
+  </si>
+  <si>
+    <t>Brussels</t>
+  </si>
+  <si>
+    <t>欧洲</t>
+  </si>
+  <si>
+    <t>西欧</t>
+  </si>
+  <si>
+    <t>BEL</t>
+  </si>
+  <si>
+    <t>法国</t>
+  </si>
+  <si>
+    <t>法兰西共和国</t>
+  </si>
+  <si>
+    <t>The French Republic</t>
+  </si>
+  <si>
+    <t>France.png</t>
+  </si>
+  <si>
+    <t>巴黎</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>FRA</t>
+  </si>
+  <si>
+    <t>爱尔兰</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Ireland.png</t>
+  </si>
+  <si>
+    <t>都柏林市</t>
+  </si>
+  <si>
+    <t>Dublin</t>
+  </si>
+  <si>
+    <t>IRL</t>
+  </si>
+  <si>
+    <t>卢森堡</t>
+  </si>
+  <si>
+    <t>卢森堡大公国</t>
+  </si>
+  <si>
+    <t>The Grand Duchy of Luxembourg</t>
+  </si>
+  <si>
+    <t>Luxembourg.png</t>
+  </si>
+  <si>
+    <t>卢森堡市</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>LUX</t>
+  </si>
+  <si>
+    <t>摩纳哥</t>
+  </si>
+  <si>
+    <t>摩纳哥公国</t>
+  </si>
+  <si>
+    <t>The Principality of Monaco</t>
+  </si>
+  <si>
+    <t>Monaco.png</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>MCO</t>
+  </si>
+  <si>
+    <t>荷兰</t>
+  </si>
+  <si>
+    <t>荷兰王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of the Netherlands</t>
+  </si>
+  <si>
+    <t>Netherlands.png</t>
+  </si>
+  <si>
+    <t>阿姆斯特丹</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>NLD</t>
+  </si>
+  <si>
+    <t>英国</t>
+  </si>
+  <si>
+    <t>大不列颠及北爱尔兰联合王国</t>
+  </si>
+  <si>
+    <t>The United Kingdom of Great Britain and Northern Ireland</t>
+  </si>
+  <si>
+    <t>United Kingdom.png</t>
+  </si>
+  <si>
+    <t>伦敦</t>
+  </si>
+  <si>
+    <t>London</t>
+  </si>
+  <si>
+    <t>GBR</t>
+  </si>
+  <si>
+    <t>丹麦</t>
+  </si>
+  <si>
+    <t>丹麦王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Denmark</t>
+  </si>
+  <si>
+    <t>Denmark.png</t>
+  </si>
+  <si>
+    <t>哥本哈根</t>
+  </si>
+  <si>
+    <t>Copenhagen</t>
+  </si>
+  <si>
+    <t>北欧</t>
+  </si>
+  <si>
+    <t>DNK</t>
+  </si>
+  <si>
+    <t>芬兰</t>
+  </si>
+  <si>
+    <t>芬兰共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Finland</t>
+  </si>
+  <si>
+    <t>Finland.png</t>
+  </si>
+  <si>
+    <t>赫尔辛基</t>
+  </si>
+  <si>
+    <t>Helsinki</t>
+  </si>
+  <si>
+    <t>FIN</t>
+  </si>
+  <si>
+    <t>冰岛</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>Iceland.png</t>
+  </si>
+  <si>
+    <t>雷克雅未克</t>
+  </si>
+  <si>
+    <t>Reykjavík</t>
+  </si>
+  <si>
+    <t>ISL</t>
+  </si>
+  <si>
+    <t>挪威</t>
+  </si>
+  <si>
+    <t>挪威王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Norway</t>
+  </si>
+  <si>
+    <t>Norway.png</t>
+  </si>
+  <si>
+    <t>奥斯陆</t>
+  </si>
+  <si>
+    <t>Oslo</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>瑞典</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Sweden.png</t>
+  </si>
+  <si>
+    <t>斯德哥尔摩</t>
+  </si>
+  <si>
+    <t>Stockholm</t>
+  </si>
+  <si>
+    <t>SWE</t>
+  </si>
+  <si>
     <t>俄罗斯</t>
   </si>
   <si>
@@ -191,9 +1091,6 @@
     <t>Russian Federation</t>
   </si>
   <si>
-    <t>Russia</t>
-  </si>
-  <si>
     <t>Russia.png</t>
   </si>
   <si>
@@ -203,897 +1100,135 @@
     <t>Moscow</t>
   </si>
   <si>
-    <t>欧洲</t>
-  </si>
-  <si>
     <t>东欧</t>
   </si>
   <si>
     <t>RUS</t>
   </si>
   <si>
-    <t>缅甸</t>
-  </si>
-  <si>
-    <t>缅甸联邦共和国</t>
-  </si>
-  <si>
-    <t>The Republic of the Union of Myanmar</t>
-  </si>
-  <si>
-    <t>Myanmar</t>
-  </si>
-  <si>
-    <t>Myanmar.jpg</t>
-  </si>
-  <si>
-    <t>内比都</t>
-  </si>
-  <si>
-    <t>Nay Pyi Taw</t>
-  </si>
-  <si>
-    <t>东南亚</t>
-  </si>
-  <si>
-    <t>MMR</t>
-  </si>
-  <si>
-    <t>文莱</t>
-  </si>
-  <si>
-    <t>文莱达鲁萨兰国</t>
-  </si>
-  <si>
-    <t>Negara Brunei Darussalam</t>
-  </si>
-  <si>
-    <t>Brunei</t>
-  </si>
-  <si>
-    <t>Brunei.png</t>
-  </si>
-  <si>
-    <t>斯里巴加湾市</t>
-  </si>
-  <si>
-    <t>Bandar Seri Begawan</t>
-  </si>
-  <si>
-    <t>BRN</t>
-  </si>
-  <si>
-    <t>柬埔寨</t>
-  </si>
-  <si>
-    <t>柬埔寨王国</t>
-  </si>
-  <si>
-    <t>The Kingdom of Cambodia</t>
-  </si>
-  <si>
-    <t>Cambodia</t>
-  </si>
-  <si>
-    <t>Cambodia.png</t>
-  </si>
-  <si>
-    <t>金边</t>
-  </si>
-  <si>
-    <t>Phnom Penh</t>
-  </si>
-  <si>
-    <t>KHM</t>
-  </si>
-  <si>
-    <t>东帝汶</t>
-  </si>
-  <si>
-    <t>东帝汶民主共和国</t>
-  </si>
-  <si>
-    <t>Democratic Republic of Timor-Leste</t>
-  </si>
-  <si>
-    <t>Timor-Leste.png</t>
-  </si>
-  <si>
-    <t>帝力</t>
-  </si>
-  <si>
-    <t>Díli</t>
-  </si>
-  <si>
-    <t>TLS</t>
-  </si>
-  <si>
-    <t>印度尼西亚</t>
-  </si>
-  <si>
-    <t>印度尼西亚共和国</t>
-  </si>
-  <si>
-    <t>Republic of Indonesia</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>Indonesia.png</t>
-  </si>
-  <si>
-    <t>努山塔拉</t>
-  </si>
-  <si>
-    <t>Nusantara</t>
-  </si>
-  <si>
-    <t>IDN</t>
-  </si>
-  <si>
-    <t>老挝</t>
-  </si>
-  <si>
-    <t>老挝人民民主共和国</t>
-  </si>
-  <si>
-    <t>The Lao People’s Democratic Republic</t>
-  </si>
-  <si>
-    <t>Laos.png</t>
-  </si>
-  <si>
-    <t>万象</t>
-  </si>
-  <si>
-    <t>Vientiane</t>
-  </si>
-  <si>
-    <t>LAO</t>
-  </si>
-  <si>
-    <t>马来西亚</t>
-  </si>
-  <si>
-    <t>Malaysia</t>
-  </si>
-  <si>
-    <t>Malaysia.png</t>
-  </si>
-  <si>
-    <t>吉隆坡</t>
-  </si>
-  <si>
-    <t>Kuala Lumpur</t>
-  </si>
-  <si>
-    <t>MYS</t>
-  </si>
-  <si>
-    <t>菲律宾</t>
-  </si>
-  <si>
-    <t>菲律宾共和国</t>
-  </si>
-  <si>
-    <t>Republic of the Philippines</t>
-  </si>
-  <si>
-    <t>Philippines</t>
-  </si>
-  <si>
-    <t>Philippines.png</t>
-  </si>
-  <si>
-    <t>大马尼拉市</t>
-  </si>
-  <si>
-    <t>Manila</t>
-  </si>
-  <si>
-    <t>PHL</t>
-  </si>
-  <si>
-    <t>新加坡</t>
-  </si>
-  <si>
-    <t>新加坡共和国</t>
-  </si>
-  <si>
-    <t>Republic of Singapore</t>
-  </si>
-  <si>
-    <t>Singapore</t>
-  </si>
-  <si>
-    <t>Singapore.png</t>
-  </si>
-  <si>
-    <t>新加坡市</t>
-  </si>
-  <si>
-    <t>Singapore City</t>
-  </si>
-  <si>
-    <t>SGP</t>
-  </si>
-  <si>
-    <t>泰国</t>
-  </si>
-  <si>
-    <t>泰王国</t>
-  </si>
-  <si>
-    <t>The Kingdom of Thailand</t>
-  </si>
-  <si>
-    <t>Thailand</t>
-  </si>
-  <si>
-    <t>Thailand.png</t>
-  </si>
-  <si>
-    <t>曼谷</t>
-  </si>
-  <si>
-    <t>Krung Thep Maha Nakhon</t>
-  </si>
-  <si>
-    <t>THA</t>
-  </si>
-  <si>
-    <t>越南</t>
-  </si>
-  <si>
-    <t>越南社会主义共和国</t>
-  </si>
-  <si>
-    <t>The Socialist Republic of Viet Nam</t>
-  </si>
-  <si>
-    <t>Vietnam.png</t>
-  </si>
-  <si>
-    <t>河内</t>
-  </si>
-  <si>
-    <t>Hanoi</t>
-  </si>
-  <si>
-    <t>VNM</t>
-  </si>
-  <si>
-    <t>孟加拉国</t>
-  </si>
-  <si>
-    <t>孟加拉人民共和国</t>
-  </si>
-  <si>
-    <t>The People’s Republic of Bangladesh</t>
-  </si>
-  <si>
-    <t>Bangladesh.png</t>
-  </si>
-  <si>
-    <t>达卡</t>
-  </si>
-  <si>
-    <t>Dhaka</t>
-  </si>
-  <si>
-    <t>南亚</t>
-  </si>
-  <si>
-    <t>BGD</t>
-  </si>
-  <si>
-    <t>不丹</t>
-  </si>
-  <si>
-    <t>不丹王国</t>
-  </si>
-  <si>
-    <t>Kingdom of Bhutan</t>
-  </si>
-  <si>
-    <t>Bhutan.png</t>
-  </si>
-  <si>
-    <t>廷布</t>
-  </si>
-  <si>
-    <t>Thimphu</t>
-  </si>
-  <si>
-    <t>BTN</t>
-  </si>
-  <si>
-    <t>印度</t>
-  </si>
-  <si>
-    <t>印度共和国</t>
-  </si>
-  <si>
-    <t>The Republic of India</t>
-  </si>
-  <si>
-    <t>India.png</t>
-  </si>
-  <si>
-    <t>新德里</t>
-  </si>
-  <si>
-    <t>New Delhi</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>马尔代夫</t>
-  </si>
-  <si>
-    <t>马尔代夫共和国</t>
-  </si>
-  <si>
-    <t>The Republic of Maldives</t>
-  </si>
-  <si>
-    <t>Maldives.png</t>
-  </si>
-  <si>
-    <t>马累</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>MDV</t>
-  </si>
-  <si>
-    <t>尼泊尔</t>
-  </si>
-  <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>Nepal.png</t>
-  </si>
-  <si>
-    <t>加德满都</t>
-  </si>
-  <si>
-    <t>Kathmandu</t>
-  </si>
-  <si>
-    <t>NPL</t>
-  </si>
-  <si>
-    <t>巴基斯坦</t>
-  </si>
-  <si>
-    <t>巴基斯坦伊斯兰共和国</t>
-  </si>
-  <si>
-    <t>Islamic Republic of Pakistan</t>
-  </si>
-  <si>
-    <t>Pakistan.png</t>
-  </si>
-  <si>
-    <t>伊斯兰堡</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
-  </si>
-  <si>
-    <t>PAK</t>
-  </si>
-  <si>
-    <t>斯里兰卡</t>
-  </si>
-  <si>
-    <t>斯里兰卡民主社会主义共和国</t>
-  </si>
-  <si>
-    <t>The Democratic Socialist Republic of Sri Lanka</t>
-  </si>
-  <si>
-    <t>Sri Lanka.png</t>
-  </si>
-  <si>
-    <t>科伦坡</t>
-  </si>
-  <si>
-    <t>Colombo</t>
-  </si>
-  <si>
-    <t>LKA</t>
-  </si>
-  <si>
-    <t>哈萨克斯坦</t>
-  </si>
-  <si>
-    <t>哈萨克斯坦共和国</t>
-  </si>
-  <si>
-    <t>The Republic of Kazakhstan</t>
-  </si>
-  <si>
-    <t>Kazakhstan</t>
-  </si>
-  <si>
-    <t>Kazakhstan.png</t>
-  </si>
-  <si>
-    <t>阿斯塔纳</t>
-  </si>
-  <si>
-    <t>Astana</t>
-  </si>
-  <si>
-    <t>中亚</t>
-  </si>
-  <si>
-    <t>KAZ</t>
-  </si>
-  <si>
-    <t>吉尔吉斯斯坦</t>
-  </si>
-  <si>
-    <t>吉尔吉斯共和国</t>
-  </si>
-  <si>
-    <t>Kyrgyz Republic</t>
-  </si>
-  <si>
-    <t>Kyrgyzstan</t>
-  </si>
-  <si>
-    <t>Kyrgyzstan.png</t>
-  </si>
-  <si>
-    <t>比什凯克</t>
-  </si>
-  <si>
-    <t>Bishkek</t>
-  </si>
-  <si>
-    <t>KGZ</t>
-  </si>
-  <si>
-    <t>塔吉克斯坦</t>
-  </si>
-  <si>
-    <t>塔吉克斯坦共和国</t>
-  </si>
-  <si>
-    <t>The Republic of Tajikistan</t>
-  </si>
-  <si>
-    <t>Tajikistan.png</t>
-  </si>
-  <si>
-    <t>杜尚别</t>
-  </si>
-  <si>
-    <t>Dushanbe</t>
-  </si>
-  <si>
-    <t>TJK</t>
-  </si>
-  <si>
-    <t>土库曼斯坦</t>
-  </si>
-  <si>
-    <t>Turkmenistan</t>
-  </si>
-  <si>
-    <t>Turkmenistan.png</t>
-  </si>
-  <si>
-    <t>阿什哈巴德市</t>
-  </si>
-  <si>
-    <t>Ashgabat</t>
-  </si>
-  <si>
-    <t>TKM</t>
-  </si>
-  <si>
-    <t>乌兹别克斯坦</t>
-  </si>
-  <si>
-    <t>乌兹别克斯坦共和国</t>
-  </si>
-  <si>
-    <t>Republic of Uzbekistan</t>
-  </si>
-  <si>
-    <t>Uzbekistan</t>
-  </si>
-  <si>
-    <t>Uzbekistan.png</t>
-  </si>
-  <si>
-    <t>塔什干</t>
-  </si>
-  <si>
-    <t>Tashkent</t>
-  </si>
-  <si>
-    <t>UZB</t>
-  </si>
-  <si>
-    <t>阿富汗</t>
-  </si>
-  <si>
-    <t>西亚</t>
-  </si>
-  <si>
-    <t>亚美尼亚</t>
-  </si>
-  <si>
-    <t>阿塞拜疆</t>
-  </si>
-  <si>
-    <t>阿塞拜疆共和国</t>
-  </si>
-  <si>
-    <t>The Republic of Azerbaijan</t>
-  </si>
-  <si>
-    <t>Azerbaijan.png</t>
-  </si>
-  <si>
-    <t>巴库</t>
-  </si>
-  <si>
-    <t>AZE</t>
-  </si>
-  <si>
-    <t>巴林</t>
-  </si>
-  <si>
-    <t>巴林王国</t>
-  </si>
-  <si>
-    <t>The Kingdom of Bahrain</t>
-  </si>
-  <si>
-    <t>Bahrain.png</t>
-  </si>
-  <si>
-    <t>麦纳麦</t>
-  </si>
-  <si>
-    <t>BHR</t>
-  </si>
-  <si>
-    <t>塞浦路斯</t>
-  </si>
-  <si>
-    <t>格鲁吉亚</t>
-  </si>
-  <si>
-    <t>伊朗</t>
-  </si>
-  <si>
-    <t>伊朗伊斯兰共和国</t>
-  </si>
-  <si>
-    <t>The Islamic Republic of Iran</t>
-  </si>
-  <si>
-    <t>Iran.png</t>
-  </si>
-  <si>
-    <t>德黑兰</t>
-  </si>
-  <si>
-    <t>IRN</t>
-  </si>
-  <si>
-    <t>伊拉克</t>
-  </si>
-  <si>
-    <t>以色列</t>
-  </si>
-  <si>
-    <t>以色列国</t>
-  </si>
-  <si>
-    <t>The State of Israel</t>
-  </si>
-  <si>
-    <t>Israel.png</t>
-  </si>
-  <si>
-    <t>耶路撒冷</t>
-  </si>
-  <si>
-    <t>ISR</t>
-  </si>
-  <si>
-    <t>约旦</t>
-  </si>
-  <si>
-    <t>科威特</t>
-  </si>
-  <si>
-    <t>黎巴嫩</t>
-  </si>
-  <si>
-    <t>阿曼</t>
-  </si>
-  <si>
-    <t>巴勒斯坦</t>
-  </si>
-  <si>
-    <t>卡塔尔</t>
-  </si>
-  <si>
-    <t>卡塔尔国</t>
-  </si>
-  <si>
-    <t>The State of Qatar</t>
-  </si>
-  <si>
-    <t>Qatar.png</t>
-  </si>
-  <si>
-    <t>多哈</t>
-  </si>
-  <si>
-    <t>QAT</t>
-  </si>
-  <si>
-    <t>沙特阿拉伯</t>
-  </si>
-  <si>
-    <t>叙利亚</t>
-  </si>
-  <si>
-    <t>土耳其</t>
-  </si>
-  <si>
-    <t>土耳其共和国</t>
-  </si>
-  <si>
-    <t>Republic of Türkiye</t>
-  </si>
-  <si>
-    <t>Türkiye.png</t>
-  </si>
-  <si>
-    <t>安卡拉</t>
-  </si>
-  <si>
-    <t>TUR</t>
-  </si>
-  <si>
-    <t>阿联酋</t>
-  </si>
-  <si>
-    <t>阿拉伯联合酋长国</t>
-  </si>
-  <si>
-    <t>The United Arab Emirates</t>
-  </si>
-  <si>
-    <t>Abu Dhabi.png</t>
-  </si>
-  <si>
-    <t>阿布扎比</t>
-  </si>
-  <si>
-    <t>Abu Dhabi</t>
-  </si>
-  <si>
-    <t>ARE</t>
-  </si>
-  <si>
-    <t>也门</t>
-  </si>
-  <si>
-    <t>比利时</t>
-  </si>
-  <si>
-    <t>比利时王国</t>
-  </si>
-  <si>
-    <t>The Kingdom of Belgium</t>
-  </si>
-  <si>
-    <t>Belgium.png</t>
-  </si>
-  <si>
-    <t>布鲁塞尔</t>
-  </si>
-  <si>
-    <t>Brussels</t>
-  </si>
-  <si>
-    <t>西欧</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>法国</t>
-  </si>
-  <si>
-    <t>法兰西共和国</t>
-  </si>
-  <si>
-    <t>The French Republic</t>
-  </si>
-  <si>
-    <t>France.png</t>
-  </si>
-  <si>
-    <t>巴黎</t>
-  </si>
-  <si>
-    <t>Paris</t>
-  </si>
-  <si>
-    <t>FRA</t>
-  </si>
-  <si>
-    <t>爱尔兰</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Ireland.png</t>
-  </si>
-  <si>
-    <t>都柏林市</t>
-  </si>
-  <si>
-    <t>Dublin</t>
-  </si>
-  <si>
-    <t>IRL</t>
-  </si>
-  <si>
-    <t>卢森堡</t>
-  </si>
-  <si>
-    <t>卢森堡大公国</t>
-  </si>
-  <si>
-    <t>The Grand Duchy of Luxembourg</t>
-  </si>
-  <si>
-    <t>Luxembourg.png</t>
-  </si>
-  <si>
-    <t>卢森堡市</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>LUX</t>
-  </si>
-  <si>
-    <t>摩纳哥</t>
-  </si>
-  <si>
-    <t>摩纳哥公国</t>
-  </si>
-  <si>
-    <t>The Principality of Monaco</t>
-  </si>
-  <si>
-    <t>Monaco.png</t>
-  </si>
-  <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>MCO</t>
-  </si>
-  <si>
-    <t>荷兰</t>
-  </si>
-  <si>
-    <t>荷兰王国</t>
-  </si>
-  <si>
-    <t>The Kingdom of the Netherlands</t>
-  </si>
-  <si>
-    <t>Netherlands.png</t>
-  </si>
-  <si>
-    <t>阿姆斯特丹</t>
-  </si>
-  <si>
-    <t>Amsterdam</t>
-  </si>
-  <si>
-    <t>NLD</t>
-  </si>
-  <si>
-    <t>英国</t>
-  </si>
-  <si>
-    <t>大不列颠及北爱尔兰联合王国</t>
-  </si>
-  <si>
-    <t>The United Kingdom of Great Britain and Northern Ireland</t>
-  </si>
-  <si>
-    <t>United Kingdom.png</t>
-  </si>
-  <si>
-    <t>伦敦</t>
-  </si>
-  <si>
-    <t>London</t>
-  </si>
-  <si>
-    <t>GBR</t>
-  </si>
-  <si>
-    <t>丹麦</t>
-  </si>
-  <si>
-    <t>北欧</t>
-  </si>
-  <si>
-    <t>芬兰</t>
-  </si>
-  <si>
-    <t>芬兰共和国</t>
-  </si>
-  <si>
-    <t>The Republic of Finland</t>
-  </si>
-  <si>
-    <t>Finland.png</t>
-  </si>
-  <si>
-    <t>赫尔辛基</t>
-  </si>
-  <si>
-    <t>Helsinki</t>
-  </si>
-  <si>
-    <t>FIN</t>
-  </si>
-  <si>
-    <t>冰岛</t>
-  </si>
-  <si>
-    <t>挪威</t>
-  </si>
-  <si>
-    <t>瑞典</t>
-  </si>
-  <si>
     <t>白俄罗斯</t>
   </si>
   <si>
+    <t>白俄罗斯共和国</t>
+  </si>
+  <si>
+    <t>Republic of Belarus</t>
+  </si>
+  <si>
+    <t>Belarus.png</t>
+  </si>
+  <si>
+    <t>明斯克市</t>
+  </si>
+  <si>
+    <t>Minsk</t>
+  </si>
+  <si>
+    <t>BLR</t>
+  </si>
+  <si>
     <t>爱沙尼亚</t>
   </si>
   <si>
+    <t>爱沙尼亚共和国</t>
+  </si>
+  <si>
+    <t>Republic of Estonia</t>
+  </si>
+  <si>
+    <t>Estonia.png</t>
+  </si>
+  <si>
+    <t>塔林</t>
+  </si>
+  <si>
+    <t>Tallinn</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
     <t>拉脱维亚</t>
   </si>
   <si>
+    <t>拉脱维亚共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Latvia</t>
+  </si>
+  <si>
+    <t>Latvia.png</t>
+  </si>
+  <si>
+    <t>里加</t>
+  </si>
+  <si>
+    <t>Riga</t>
+  </si>
+  <si>
+    <t>LVA</t>
+  </si>
+  <si>
     <t>立陶宛</t>
   </si>
   <si>
+    <t>立陶宛共和国</t>
+  </si>
+  <si>
+    <t>Republic of Lithuania</t>
+  </si>
+  <si>
+    <t>Lithuania.png</t>
+  </si>
+  <si>
+    <t>维尔纽斯</t>
+  </si>
+  <si>
+    <t>Vilnius</t>
+  </si>
+  <si>
+    <t>LTU</t>
+  </si>
+  <si>
     <t>摩尔多瓦</t>
   </si>
   <si>
+    <t>摩尔多瓦共和国</t>
+  </si>
+  <si>
+    <t>Republic of Moldova</t>
+  </si>
+  <si>
+    <t>Moldova.png</t>
+  </si>
+  <si>
+    <t>基希讷乌</t>
+  </si>
+  <si>
+    <t>Kishinev</t>
+  </si>
+  <si>
+    <t>MDA</t>
+  </si>
+  <si>
     <t>乌克兰</t>
   </si>
   <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>Ukraine.png</t>
+  </si>
+  <si>
+    <t>基辅</t>
+  </si>
+  <si>
+    <t>Kyiv</t>
+  </si>
+  <si>
+    <t>UKR</t>
+  </si>
+  <si>
     <t>德国</t>
   </si>
   <si>
@@ -1109,6 +1244,9 @@
     <t>柏林</t>
   </si>
   <si>
+    <t>Berlin</t>
+  </si>
+  <si>
     <t>中欧</t>
   </si>
   <si>
@@ -1118,9 +1256,45 @@
     <t>波兰</t>
   </si>
   <si>
+    <t>波兰共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Poland</t>
+  </si>
+  <si>
+    <t>Poland.png</t>
+  </si>
+  <si>
+    <t>华沙市</t>
+  </si>
+  <si>
+    <t>Warsaw</t>
+  </si>
+  <si>
+    <t>POL</t>
+  </si>
+  <si>
     <t>斯洛伐克</t>
   </si>
   <si>
+    <t>斯洛伐克共和国</t>
+  </si>
+  <si>
+    <t>The Slovak Republic</t>
+  </si>
+  <si>
+    <t>Slovakia.png</t>
+  </si>
+  <si>
+    <t>布拉迪斯拉发</t>
+  </si>
+  <si>
+    <t>Bratislava</t>
+  </si>
+  <si>
+    <t>SVK</t>
+  </si>
+  <si>
     <t>匈牙利</t>
   </si>
   <si>
@@ -1133,6 +1307,9 @@
     <t>布达佩斯</t>
   </si>
   <si>
+    <t>Budapest</t>
+  </si>
+  <si>
     <t>HUN</t>
   </si>
   <si>
@@ -1151,18 +1328,72 @@
     <t>维也纳</t>
   </si>
   <si>
+    <t>Vienna</t>
+  </si>
+  <si>
     <t>AUT</t>
   </si>
   <si>
     <t>捷克</t>
   </si>
   <si>
+    <t>捷克共和国</t>
+  </si>
+  <si>
+    <t>The Czech Republic</t>
+  </si>
+  <si>
+    <t>Czechia.png</t>
+  </si>
+  <si>
+    <t>布拉格</t>
+  </si>
+  <si>
+    <t>Prague</t>
+  </si>
+  <si>
+    <t>CZE</t>
+  </si>
+  <si>
     <t>列支敦士登</t>
   </si>
   <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>Liechtenstein.png</t>
+  </si>
+  <si>
+    <t>瓦杜兹市</t>
+  </si>
+  <si>
+    <t>Vaduz</t>
+  </si>
+  <si>
+    <t>LIE</t>
+  </si>
+  <si>
     <t>瑞士</t>
   </si>
   <si>
+    <t>瑞士联邦</t>
+  </si>
+  <si>
+    <t>Swiss Confederation</t>
+  </si>
+  <si>
+    <t>Switzerland.png</t>
+  </si>
+  <si>
+    <t>伯尔尼</t>
+  </si>
+  <si>
+    <t>Berne</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
     <t>阿尔巴里亚</t>
   </si>
   <si>
@@ -1292,6 +1523,9 @@
     <t>墨西哥城</t>
   </si>
   <si>
+    <t>Ciudad de México</t>
+  </si>
+  <si>
     <t>中美</t>
   </si>
   <si>
@@ -1301,22 +1535,139 @@
     <t>伯利兹</t>
   </si>
   <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Belize.png</t>
+  </si>
+  <si>
+    <t>贝尔莫潘</t>
+  </si>
+  <si>
+    <t>Belmopan</t>
+  </si>
+  <si>
+    <t>BLZ</t>
+  </si>
+  <si>
     <t>哥斯达黎加</t>
   </si>
   <si>
+    <t>哥斯达黎加共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Costa Rica</t>
+  </si>
+  <si>
+    <t>Costa Rica.png</t>
+  </si>
+  <si>
+    <t>圣何塞</t>
+  </si>
+  <si>
+    <t>Saint Jose</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
     <t>萨尔瓦多</t>
   </si>
   <si>
+    <t>萨尔瓦多共和国</t>
+  </si>
+  <si>
+    <t>The Republic of El Salvador</t>
+  </si>
+  <si>
+    <t>El Salvador.png</t>
+  </si>
+  <si>
+    <t>圣萨尔瓦多</t>
+  </si>
+  <si>
+    <t>San Salvador</t>
+  </si>
+  <si>
+    <t>SLV</t>
+  </si>
+  <si>
     <t>危地马拉</t>
   </si>
   <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Guatemala.png</t>
+  </si>
+  <si>
+    <t>危地马拉城</t>
+  </si>
+  <si>
+    <t>Ciudad de Guatemala</t>
+  </si>
+  <si>
+    <t>GTM</t>
+  </si>
+  <si>
     <t>洪都拉斯</t>
   </si>
   <si>
+    <t>洪都拉斯共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Honduras</t>
+  </si>
+  <si>
+    <t>Honduras.png</t>
+  </si>
+  <si>
+    <t>特古西加尔巴</t>
+  </si>
+  <si>
+    <t>Tegucigalpa</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
     <t>尼加拉瓜</t>
   </si>
   <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Nicaragua.png</t>
+  </si>
+  <si>
+    <t>马那瓜</t>
+  </si>
+  <si>
+    <t>Managua</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
     <t>巴拿马</t>
+  </si>
+  <si>
+    <t>巴拿马共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Panama</t>
+  </si>
+  <si>
+    <t>Panama.png</t>
+  </si>
+  <si>
+    <t>巴拿马城</t>
+  </si>
+  <si>
+    <t>Panama City</t>
+  </si>
+  <si>
+    <t>PAN</t>
   </si>
   <si>
     <t>安提瓜和巴布达</t>
@@ -2285,8 +2636,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2607,7 +2959,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="4.57142857142857" customWidth="1"/>
@@ -2615,16 +2967,15 @@
     <col min="3" max="3" width="13.9821428571429" customWidth="1"/>
     <col min="4" max="4" width="21.875" customWidth="1"/>
     <col min="5" max="5" width="28.4196428571429" customWidth="1"/>
-    <col min="6" max="6" width="15.7678571428571" customWidth="1"/>
-    <col min="7" max="7" width="16.0714285714286" customWidth="1"/>
-    <col min="8" max="8" width="16.2142857142857" customWidth="1"/>
-    <col min="9" max="9" width="12.7857142857143" customWidth="1"/>
-    <col min="10" max="10" width="8.78571428571429" customWidth="1"/>
-    <col min="11" max="11" width="7.57142857142857" customWidth="1"/>
-    <col min="12" max="12" width="5.42857142857143" customWidth="1"/>
+    <col min="6" max="6" width="16.0714285714286" customWidth="1"/>
+    <col min="7" max="7" width="16.2142857142857" customWidth="1"/>
+    <col min="8" max="8" width="12.7857142857143" customWidth="1"/>
+    <col min="9" max="9" width="8.78571428571429" customWidth="1"/>
+    <col min="10" max="10" width="7.57142857142857" customWidth="1"/>
+    <col min="11" max="11" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2658,24 +3009,24 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
       <c r="G2" t="s">
@@ -2693,27 +3044,26 @@
       <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>24</v>
       </c>
-      <c r="F3"/>
       <c r="G3" t="s">
         <v>25</v>
       </c>
@@ -2721,32 +3071,32 @@
         <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
         <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>31</v>
       </c>
       <c r="G4" t="s">
@@ -2756,32 +3106,32 @@
         <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
         <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>38</v>
       </c>
       <c r="G5" t="s">
@@ -2791,32 +3141,32 @@
         <v>40</v>
       </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
         <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
         <v>43</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>45</v>
       </c>
       <c r="G6" t="s">
@@ -2826,2377 +3176,2620 @@
         <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
         <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" t="s">
         <v>50</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>51</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>54</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" t="s">
         <v>55</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>56</v>
       </c>
-      <c r="J7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" t="s">
         <v>60</v>
       </c>
-      <c r="D8" t="s">
+      <c r="G8" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="I8" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" t="s">
         <v>63</v>
       </c>
-      <c r="G8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>67</v>
-      </c>
-      <c r="L8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" t="s">
         <v>69</v>
       </c>
-      <c r="D9" t="s">
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" t="s">
         <v>70</v>
       </c>
-      <c r="E9" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" t="s">
-        <v>72</v>
-      </c>
-      <c r="G9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" t="s">
-        <v>67</v>
-      </c>
-      <c r="L9" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" t="s">
         <v>77</v>
       </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G10" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" t="s">
-        <v>67</v>
-      </c>
-      <c r="L10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s">
+        <v>55</v>
+      </c>
+      <c r="K11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
         <v>85</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>86</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>87</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F12" t="s">
         <v>88</v>
       </c>
-      <c r="H11" t="s">
+      <c r="G12" t="s">
         <v>89</v>
       </c>
-      <c r="I11" t="s">
+      <c r="H12" t="s">
         <v>90</v>
       </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>67</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>67</v>
-      </c>
-      <c r="L12" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>93</v>
+      </c>
+      <c r="F13" t="s">
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
-      </c>
-      <c r="L13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F14" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I14" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F15" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G15" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="H15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="I15" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
-      </c>
-      <c r="L15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I16" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F17" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I17" t="s">
-        <v>135</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="K17" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>128</v>
+      </c>
+      <c r="F18" t="s">
+        <v>129</v>
       </c>
       <c r="G18" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H18" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I18" t="s">
-        <v>142</v>
+        <v>18</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K18" t="s">
-        <v>67</v>
-      </c>
-      <c r="L18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>137</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="I19" t="s">
-        <v>149</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K19" t="s">
-        <v>150</v>
-      </c>
-      <c r="L19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E20" t="s">
-        <v>154</v>
+        <v>143</v>
+      </c>
+      <c r="F20" t="s">
+        <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="H20" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="I20" t="s">
-        <v>157</v>
+        <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K20" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>161</v>
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>151</v>
       </c>
       <c r="G21" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="H21" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I21" t="s">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K21" t="s">
-        <v>150</v>
-      </c>
-      <c r="L21" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D22" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
-        <v>168</v>
+        <v>156</v>
+      </c>
+      <c r="F22" t="s">
+        <v>157</v>
       </c>
       <c r="G22" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="H22" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="I22" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K22" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
-        <v>174</v>
+        <v>163</v>
+      </c>
+      <c r="F23" t="s">
+        <v>164</v>
       </c>
       <c r="G23" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="H23" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="I23" t="s">
-        <v>177</v>
+        <v>18</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K23" t="s">
-        <v>150</v>
-      </c>
-      <c r="L23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="D24" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E24" t="s">
-        <v>181</v>
+        <v>170</v>
+      </c>
+      <c r="F24" t="s">
+        <v>171</v>
       </c>
       <c r="G24" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="H24" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="K24" t="s">
-        <v>150</v>
-      </c>
-      <c r="L24" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="D25" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>177</v>
+      </c>
+      <c r="F25" t="s">
+        <v>178</v>
       </c>
       <c r="G25" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H25" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>191</v>
+        <v>18</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="K25" t="s">
-        <v>150</v>
-      </c>
-      <c r="L25" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D26" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="E26" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F26" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="G26" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="H26" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="I26" t="s">
-        <v>199</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="K26" t="s">
-        <v>200</v>
-      </c>
-      <c r="L26" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="E27" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="F27" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="G27" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="H27" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="I27" t="s">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="K27" t="s">
-        <v>200</v>
-      </c>
-      <c r="L27" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="D28" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="E28" t="s">
-        <v>212</v>
+        <v>198</v>
+      </c>
+      <c r="F28" t="s">
+        <v>199</v>
       </c>
       <c r="G28" t="s">
-        <v>213</v>
-      </c>
-      <c r="H28" t="s">
-        <v>214</v>
+        <v>200</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="I28" t="s">
-        <v>215</v>
+        <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="K28" t="s">
-        <v>200</v>
-      </c>
-      <c r="L28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D29" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="E29" t="s">
-        <v>218</v>
+        <v>205</v>
+      </c>
+      <c r="F29" t="s">
+        <v>206</v>
       </c>
       <c r="G29" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H29" t="s">
-        <v>220</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>221</v>
+        <v>208</v>
+      </c>
+      <c r="I29" t="s">
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="K29" t="s">
-        <v>200</v>
-      </c>
-      <c r="L29" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" t="s">
-        <v>225</v>
-      </c>
-      <c r="F30" t="s">
-        <v>226</v>
-      </c>
-      <c r="G30" t="s">
-        <v>227</v>
-      </c>
-      <c r="H30" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="I30" t="s">
-        <v>229</v>
+        <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" t="s">
-        <v>200</v>
-      </c>
-      <c r="L30" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>231</v>
+        <v>212</v>
+      </c>
+      <c r="I31" t="s">
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>213</v>
+      </c>
+      <c r="D32" t="s">
+        <v>214</v>
+      </c>
+      <c r="E32" t="s">
+        <v>215</v>
+      </c>
+      <c r="F32" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" t="s">
+        <v>217</v>
+      </c>
+      <c r="I32" t="s">
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K32" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s">
-        <v>236</v>
+        <v>221</v>
+      </c>
+      <c r="F33" t="s">
+        <v>222</v>
       </c>
       <c r="G33" t="s">
-        <v>237</v>
-      </c>
-      <c r="H33" t="s">
-        <v>238</v>
+        <v>223</v>
+      </c>
+      <c r="I33" t="s">
+        <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K33" t="s">
-        <v>232</v>
-      </c>
-      <c r="L33" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" t="s">
-        <v>241</v>
-      </c>
-      <c r="E34" t="s">
-        <v>242</v>
-      </c>
-      <c r="G34" t="s">
-        <v>243</v>
-      </c>
-      <c r="H34" t="s">
-        <v>244</v>
+        <v>225</v>
+      </c>
+      <c r="I34" t="s">
+        <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" t="s">
-        <v>232</v>
-      </c>
-      <c r="L34" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>246</v>
+        <v>226</v>
+      </c>
+      <c r="I35" t="s">
+        <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>247</v>
+        <v>227</v>
+      </c>
+      <c r="D36" t="s">
+        <v>228</v>
+      </c>
+      <c r="E36" t="s">
+        <v>229</v>
+      </c>
+      <c r="F36" t="s">
+        <v>230</v>
+      </c>
+      <c r="G36" t="s">
+        <v>231</v>
+      </c>
+      <c r="I36" t="s">
+        <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K36" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:11">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>248</v>
-      </c>
-      <c r="D37" t="s">
-        <v>249</v>
-      </c>
-      <c r="E37" t="s">
-        <v>250</v>
-      </c>
-      <c r="G37" t="s">
-        <v>251</v>
-      </c>
-      <c r="H37" t="s">
-        <v>252</v>
+        <v>233</v>
+      </c>
+      <c r="I37" t="s">
+        <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" t="s">
-        <v>232</v>
-      </c>
-      <c r="L37" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>254</v>
+        <v>234</v>
+      </c>
+      <c r="D38" t="s">
+        <v>235</v>
+      </c>
+      <c r="E38" t="s">
+        <v>236</v>
+      </c>
+      <c r="F38" t="s">
+        <v>237</v>
+      </c>
+      <c r="G38" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" t="s">
+        <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K38" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>255</v>
-      </c>
-      <c r="D39" t="s">
-        <v>256</v>
-      </c>
-      <c r="E39" t="s">
-        <v>257</v>
-      </c>
-      <c r="G39" t="s">
-        <v>258</v>
-      </c>
-      <c r="H39" t="s">
-        <v>259</v>
+        <v>240</v>
+      </c>
+      <c r="I39" t="s">
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" t="s">
-        <v>232</v>
-      </c>
-      <c r="L39" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>261</v>
+        <v>241</v>
+      </c>
+      <c r="I40" t="s">
+        <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>262</v>
+        <v>242</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
-      </c>
-      <c r="K41" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>263</v>
+        <v>243</v>
+      </c>
+      <c r="I42" t="s">
+        <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>264</v>
+        <v>244</v>
+      </c>
+      <c r="I43" t="s">
+        <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>265</v>
+        <v>245</v>
+      </c>
+      <c r="D44" t="s">
+        <v>246</v>
+      </c>
+      <c r="E44" t="s">
+        <v>247</v>
+      </c>
+      <c r="F44" t="s">
+        <v>248</v>
+      </c>
+      <c r="G44" t="s">
+        <v>249</v>
+      </c>
+      <c r="I44" t="s">
+        <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K44" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
-      </c>
-      <c r="D45" t="s">
-        <v>267</v>
-      </c>
-      <c r="E45" t="s">
-        <v>268</v>
-      </c>
-      <c r="G45" t="s">
-        <v>269</v>
-      </c>
-      <c r="H45" t="s">
-        <v>270</v>
+        <v>251</v>
+      </c>
+      <c r="I45" t="s">
+        <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" t="s">
-        <v>232</v>
-      </c>
-      <c r="L45" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>272</v>
+        <v>252</v>
+      </c>
+      <c r="I46" t="s">
+        <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>273</v>
+        <v>253</v>
+      </c>
+      <c r="D47" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" t="s">
+        <v>255</v>
+      </c>
+      <c r="F47" t="s">
+        <v>256</v>
+      </c>
+      <c r="G47" t="s">
+        <v>257</v>
+      </c>
+      <c r="I47" t="s">
+        <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K47" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D48" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="E48" t="s">
-        <v>276</v>
+        <v>261</v>
+      </c>
+      <c r="F48" t="s">
+        <v>262</v>
       </c>
       <c r="G48" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="H48" t="s">
-        <v>278</v>
+        <v>264</v>
+      </c>
+      <c r="I48" t="s">
+        <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="K48" t="s">
-        <v>232</v>
-      </c>
-      <c r="L48" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>280</v>
-      </c>
-      <c r="D49" t="s">
-        <v>281</v>
-      </c>
-      <c r="E49" t="s">
-        <v>282</v>
-      </c>
-      <c r="G49" t="s">
-        <v>283</v>
-      </c>
-      <c r="H49" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="I49" t="s">
-        <v>285</v>
+        <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
-      </c>
-      <c r="K49" t="s">
-        <v>232</v>
-      </c>
-      <c r="L49" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>287</v>
+        <v>267</v>
+      </c>
+      <c r="D50" t="s">
+        <v>268</v>
+      </c>
+      <c r="E50" t="s">
+        <v>269</v>
+      </c>
+      <c r="F50" t="s">
+        <v>270</v>
+      </c>
+      <c r="G50" t="s">
+        <v>271</v>
+      </c>
+      <c r="H50" t="s">
+        <v>272</v>
+      </c>
+      <c r="I50" t="s">
+        <v>273</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>274</v>
       </c>
       <c r="K50" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D51" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="E51" t="s">
-        <v>290</v>
+        <v>278</v>
+      </c>
+      <c r="F51" t="s">
+        <v>279</v>
       </c>
       <c r="G51" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="H51" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="I51" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J51" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K51" t="s">
-        <v>294</v>
-      </c>
-      <c r="L51" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E52" t="s">
-        <v>298</v>
+        <v>284</v>
+      </c>
+      <c r="F52" t="s">
+        <v>285</v>
       </c>
       <c r="G52" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="H52" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="I52" t="s">
-        <v>301</v>
+        <v>273</v>
       </c>
       <c r="J52" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K52" t="s">
-        <v>294</v>
-      </c>
-      <c r="L52" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D53" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E53" t="s">
-        <v>304</v>
+        <v>291</v>
+      </c>
+      <c r="F53" t="s">
+        <v>292</v>
       </c>
       <c r="G53" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="H53" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="I53" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="J53" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K53" t="s">
-        <v>294</v>
-      </c>
-      <c r="L53" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="D54" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="E54" t="s">
-        <v>311</v>
+        <v>298</v>
+      </c>
+      <c r="F54" t="s">
+        <v>299</v>
       </c>
       <c r="G54" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="H54" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="I54" t="s">
-        <v>314</v>
+        <v>273</v>
       </c>
       <c r="J54" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K54" t="s">
-        <v>294</v>
-      </c>
-      <c r="L54" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E55" t="s">
-        <v>318</v>
+        <v>304</v>
+      </c>
+      <c r="F55" t="s">
+        <v>305</v>
       </c>
       <c r="G55" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="H55" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="I55" t="s">
-        <v>320</v>
+        <v>273</v>
       </c>
       <c r="J55" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K55" t="s">
-        <v>294</v>
-      </c>
-      <c r="L55" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E56" t="s">
-        <v>324</v>
+        <v>311</v>
+      </c>
+      <c r="F56" t="s">
+        <v>312</v>
       </c>
       <c r="G56" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="H56" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="I56" t="s">
-        <v>327</v>
+        <v>273</v>
       </c>
       <c r="J56" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="K56" t="s">
-        <v>294</v>
-      </c>
-      <c r="L56" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="D57" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="E57" t="s">
-        <v>331</v>
+        <v>318</v>
+      </c>
+      <c r="F57" t="s">
+        <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="H57" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="I57" t="s">
-        <v>334</v>
+        <v>273</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="K57" t="s">
-        <v>294</v>
-      </c>
-      <c r="L57" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>336</v>
+        <v>324</v>
+      </c>
+      <c r="D58" t="s">
+        <v>325</v>
+      </c>
+      <c r="E58" t="s">
+        <v>326</v>
+      </c>
+      <c r="F58" t="s">
+        <v>327</v>
+      </c>
+      <c r="G58" t="s">
+        <v>328</v>
+      </c>
+      <c r="H58" t="s">
+        <v>329</v>
+      </c>
+      <c r="I58" t="s">
+        <v>273</v>
       </c>
       <c r="J58" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="K58" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D59" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="E59" t="s">
-        <v>340</v>
+        <v>332</v>
+      </c>
+      <c r="F59" t="s">
+        <v>333</v>
       </c>
       <c r="G59" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="H59" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="I59" t="s">
-        <v>343</v>
+        <v>273</v>
       </c>
       <c r="J59" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="K59" t="s">
-        <v>337</v>
-      </c>
-      <c r="L59" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>345</v>
+        <v>337</v>
+      </c>
+      <c r="D60" t="s">
+        <v>338</v>
+      </c>
+      <c r="E60" t="s">
+        <v>339</v>
+      </c>
+      <c r="F60" t="s">
+        <v>340</v>
+      </c>
+      <c r="G60" t="s">
+        <v>341</v>
+      </c>
+      <c r="H60" t="s">
+        <v>342</v>
+      </c>
+      <c r="I60" t="s">
+        <v>273</v>
       </c>
       <c r="J60" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="K60" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
+        <v>344</v>
+      </c>
+      <c r="D61" t="s">
+        <v>344</v>
+      </c>
+      <c r="E61" t="s">
+        <v>345</v>
+      </c>
+      <c r="F61" t="s">
         <v>346</v>
       </c>
+      <c r="G61" t="s">
+        <v>347</v>
+      </c>
+      <c r="H61" t="s">
+        <v>348</v>
+      </c>
+      <c r="I61" t="s">
+        <v>273</v>
+      </c>
       <c r="J61" t="s">
-        <v>57</v>
+        <v>322</v>
       </c>
       <c r="K61" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>347</v>
+        <v>350</v>
+      </c>
+      <c r="D62" t="s">
+        <v>351</v>
+      </c>
+      <c r="E62" t="s">
+        <v>352</v>
+      </c>
+      <c r="F62" t="s">
+        <v>353</v>
+      </c>
+      <c r="G62" t="s">
+        <v>354</v>
+      </c>
+      <c r="H62" t="s">
+        <v>355</v>
+      </c>
+      <c r="I62" t="s">
+        <v>273</v>
       </c>
       <c r="J62" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K62" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>348</v>
+        <v>358</v>
+      </c>
+      <c r="D63" t="s">
+        <v>359</v>
+      </c>
+      <c r="E63" t="s">
+        <v>360</v>
+      </c>
+      <c r="F63" t="s">
+        <v>361</v>
+      </c>
+      <c r="G63" t="s">
+        <v>362</v>
+      </c>
+      <c r="H63" t="s">
+        <v>363</v>
+      </c>
+      <c r="I63" t="s">
+        <v>273</v>
       </c>
       <c r="J63" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K63" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>349</v>
+        <v>365</v>
+      </c>
+      <c r="D64" t="s">
+        <v>366</v>
+      </c>
+      <c r="E64" t="s">
+        <v>367</v>
+      </c>
+      <c r="F64" t="s">
+        <v>368</v>
+      </c>
+      <c r="G64" t="s">
+        <v>369</v>
+      </c>
+      <c r="H64" t="s">
+        <v>370</v>
+      </c>
+      <c r="I64" t="s">
+        <v>273</v>
       </c>
       <c r="J64" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>350</v>
+        <v>372</v>
+      </c>
+      <c r="D65" t="s">
+        <v>373</v>
+      </c>
+      <c r="E65" t="s">
+        <v>374</v>
+      </c>
+      <c r="F65" t="s">
+        <v>375</v>
+      </c>
+      <c r="G65" t="s">
+        <v>376</v>
+      </c>
+      <c r="H65" t="s">
+        <v>377</v>
+      </c>
+      <c r="I65" t="s">
+        <v>273</v>
       </c>
       <c r="J65" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K65" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>351</v>
+        <v>379</v>
+      </c>
+      <c r="D66" t="s">
+        <v>380</v>
+      </c>
+      <c r="E66" t="s">
+        <v>381</v>
+      </c>
+      <c r="F66" t="s">
+        <v>382</v>
+      </c>
+      <c r="G66" t="s">
+        <v>383</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I66" t="s">
+        <v>273</v>
       </c>
       <c r="J66" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>352</v>
+        <v>386</v>
+      </c>
+      <c r="D67" t="s">
+        <v>387</v>
+      </c>
+      <c r="E67" t="s">
+        <v>388</v>
+      </c>
+      <c r="F67" t="s">
+        <v>389</v>
+      </c>
+      <c r="G67" t="s">
+        <v>390</v>
+      </c>
+      <c r="H67" t="s">
+        <v>391</v>
+      </c>
+      <c r="I67" t="s">
+        <v>273</v>
       </c>
       <c r="J67" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K67" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>353</v>
+        <v>393</v>
+      </c>
+      <c r="D68" t="s">
+        <v>393</v>
+      </c>
+      <c r="E68" t="s">
+        <v>394</v>
+      </c>
+      <c r="F68" t="s">
+        <v>395</v>
+      </c>
+      <c r="G68" t="s">
+        <v>396</v>
+      </c>
+      <c r="H68" t="s">
+        <v>397</v>
+      </c>
+      <c r="I68" t="s">
+        <v>273</v>
       </c>
       <c r="J68" t="s">
-        <v>57</v>
+        <v>356</v>
       </c>
       <c r="K68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>354</v>
+        <v>399</v>
       </c>
       <c r="D69" t="s">
-        <v>355</v>
+        <v>400</v>
       </c>
       <c r="E69" t="s">
-        <v>356</v>
+        <v>401</v>
+      </c>
+      <c r="F69" t="s">
+        <v>402</v>
       </c>
       <c r="G69" t="s">
-        <v>357</v>
+        <v>403</v>
       </c>
       <c r="H69" t="s">
-        <v>358</v>
+        <v>404</v>
+      </c>
+      <c r="I69" t="s">
+        <v>273</v>
       </c>
       <c r="J69" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K69" t="s">
-        <v>359</v>
-      </c>
-      <c r="L69" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>361</v>
+        <v>407</v>
+      </c>
+      <c r="D70" t="s">
+        <v>408</v>
+      </c>
+      <c r="E70" t="s">
+        <v>409</v>
+      </c>
+      <c r="F70" t="s">
+        <v>410</v>
+      </c>
+      <c r="G70" t="s">
+        <v>411</v>
+      </c>
+      <c r="H70" t="s">
+        <v>412</v>
+      </c>
+      <c r="I70" t="s">
+        <v>273</v>
       </c>
       <c r="J70" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K70" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>362</v>
+        <v>414</v>
+      </c>
+      <c r="D71" t="s">
+        <v>415</v>
+      </c>
+      <c r="E71" t="s">
+        <v>416</v>
+      </c>
+      <c r="F71" t="s">
+        <v>417</v>
+      </c>
+      <c r="G71" t="s">
+        <v>418</v>
+      </c>
+      <c r="H71" t="s">
+        <v>419</v>
+      </c>
+      <c r="I71" t="s">
+        <v>273</v>
       </c>
       <c r="J71" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K71" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="D72" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="E72" t="s">
-        <v>364</v>
+        <v>422</v>
+      </c>
+      <c r="F72" t="s">
+        <v>423</v>
       </c>
       <c r="G72" t="s">
-        <v>365</v>
+        <v>424</v>
       </c>
       <c r="H72" t="s">
-        <v>366</v>
+        <v>425</v>
+      </c>
+      <c r="I72" t="s">
+        <v>273</v>
       </c>
       <c r="J72" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K72" t="s">
-        <v>359</v>
-      </c>
-      <c r="L72" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>368</v>
+        <v>427</v>
       </c>
       <c r="D73" t="s">
-        <v>369</v>
+        <v>428</v>
       </c>
       <c r="E73" t="s">
-        <v>370</v>
+        <v>429</v>
+      </c>
+      <c r="F73" t="s">
+        <v>430</v>
       </c>
       <c r="G73" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="H73" t="s">
-        <v>372</v>
+        <v>432</v>
+      </c>
+      <c r="I73" t="s">
+        <v>273</v>
       </c>
       <c r="J73" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K73" t="s">
-        <v>359</v>
-      </c>
-      <c r="L73" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>374</v>
+        <v>434</v>
+      </c>
+      <c r="D74" t="s">
+        <v>435</v>
+      </c>
+      <c r="E74" t="s">
+        <v>436</v>
+      </c>
+      <c r="F74" t="s">
+        <v>437</v>
+      </c>
+      <c r="G74" t="s">
+        <v>438</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="I74" t="s">
+        <v>273</v>
       </c>
       <c r="J74" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K74" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>375</v>
+        <v>441</v>
+      </c>
+      <c r="D75" t="s">
+        <v>441</v>
+      </c>
+      <c r="E75" t="s">
+        <v>442</v>
+      </c>
+      <c r="F75" t="s">
+        <v>443</v>
+      </c>
+      <c r="G75" t="s">
+        <v>444</v>
+      </c>
+      <c r="H75" t="s">
+        <v>445</v>
+      </c>
+      <c r="I75" t="s">
+        <v>273</v>
       </c>
       <c r="J75" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K75" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>376</v>
+        <v>447</v>
+      </c>
+      <c r="D76" t="s">
+        <v>448</v>
+      </c>
+      <c r="E76" t="s">
+        <v>449</v>
+      </c>
+      <c r="F76" t="s">
+        <v>450</v>
+      </c>
+      <c r="G76" t="s">
+        <v>451</v>
+      </c>
+      <c r="H76" t="s">
+        <v>452</v>
+      </c>
+      <c r="I76" t="s">
+        <v>273</v>
       </c>
       <c r="J76" t="s">
-        <v>57</v>
+        <v>405</v>
       </c>
       <c r="K76" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>377</v>
+        <v>454</v>
+      </c>
+      <c r="I77" t="s">
+        <v>273</v>
       </c>
       <c r="J77" t="s">
-        <v>57</v>
-      </c>
-      <c r="K77" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>379</v>
+        <v>456</v>
+      </c>
+      <c r="I78" t="s">
+        <v>273</v>
       </c>
       <c r="J78" t="s">
-        <v>57</v>
-      </c>
-      <c r="K78" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>380</v>
+        <v>457</v>
+      </c>
+      <c r="I79" t="s">
+        <v>273</v>
       </c>
       <c r="J79" t="s">
-        <v>57</v>
-      </c>
-      <c r="K79" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>381</v>
+        <v>458</v>
+      </c>
+      <c r="I80" t="s">
+        <v>273</v>
       </c>
       <c r="J80" t="s">
-        <v>57</v>
-      </c>
-      <c r="K80" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>382</v>
+        <v>459</v>
+      </c>
+      <c r="I81" t="s">
+        <v>273</v>
       </c>
       <c r="J81" t="s">
-        <v>57</v>
-      </c>
-      <c r="K81" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>383</v>
+        <v>460</v>
+      </c>
+      <c r="I82" t="s">
+        <v>273</v>
       </c>
       <c r="J82" t="s">
-        <v>57</v>
-      </c>
-      <c r="K82" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>384</v>
+        <v>461</v>
       </c>
       <c r="D83" t="s">
-        <v>385</v>
+        <v>462</v>
       </c>
       <c r="E83" t="s">
-        <v>386</v>
+        <v>463</v>
+      </c>
+      <c r="F83" t="s">
+        <v>464</v>
       </c>
       <c r="G83" t="s">
-        <v>387</v>
-      </c>
-      <c r="H83" t="s">
-        <v>388</v>
+        <v>465</v>
+      </c>
+      <c r="I83" t="s">
+        <v>273</v>
       </c>
       <c r="J83" t="s">
-        <v>57</v>
+        <v>455</v>
       </c>
       <c r="K83" t="s">
-        <v>378</v>
-      </c>
-      <c r="L83" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>390</v>
+        <v>467</v>
+      </c>
+      <c r="I84" t="s">
+        <v>273</v>
       </c>
       <c r="J84" t="s">
-        <v>57</v>
-      </c>
-      <c r="K84" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>391</v>
+        <v>468</v>
+      </c>
+      <c r="I85" t="s">
+        <v>273</v>
       </c>
       <c r="J85" t="s">
-        <v>57</v>
-      </c>
-      <c r="K85" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>392</v>
+        <v>469</v>
+      </c>
+      <c r="I86" t="s">
+        <v>273</v>
       </c>
       <c r="J86" t="s">
-        <v>57</v>
-      </c>
-      <c r="K86" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>393</v>
+        <v>470</v>
+      </c>
+      <c r="I87" t="s">
+        <v>273</v>
       </c>
       <c r="J87" t="s">
-        <v>57</v>
-      </c>
-      <c r="K87" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>394</v>
+        <v>471</v>
+      </c>
+      <c r="I88" t="s">
+        <v>273</v>
       </c>
       <c r="J88" t="s">
-        <v>57</v>
-      </c>
-      <c r="K88" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>395</v>
+        <v>472</v>
+      </c>
+      <c r="I89" t="s">
+        <v>273</v>
       </c>
       <c r="J89" t="s">
-        <v>57</v>
-      </c>
-      <c r="K89" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>396</v>
+        <v>473</v>
+      </c>
+      <c r="I90" t="s">
+        <v>273</v>
       </c>
       <c r="J90" t="s">
-        <v>57</v>
-      </c>
-      <c r="K90" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>397</v>
+        <v>474</v>
+      </c>
+      <c r="I91" t="s">
+        <v>273</v>
       </c>
       <c r="J91" t="s">
-        <v>57</v>
-      </c>
-      <c r="K91" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>398</v>
+        <v>475</v>
+      </c>
+      <c r="I92" t="s">
+        <v>273</v>
       </c>
       <c r="J92" t="s">
-        <v>57</v>
-      </c>
-      <c r="K92" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>399</v>
+        <v>476</v>
+      </c>
+      <c r="I93" t="s">
+        <v>273</v>
       </c>
       <c r="J93" t="s">
-        <v>57</v>
-      </c>
-      <c r="K93" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="D94" t="s">
-        <v>400</v>
+        <v>477</v>
       </c>
       <c r="E94" t="s">
-        <v>401</v>
+        <v>478</v>
+      </c>
+      <c r="F94" t="s">
+        <v>479</v>
       </c>
       <c r="G94" t="s">
-        <v>402</v>
+        <v>480</v>
       </c>
       <c r="H94" t="s">
-        <v>403</v>
+        <v>481</v>
       </c>
       <c r="I94" t="s">
-        <v>404</v>
+        <v>482</v>
       </c>
       <c r="J94" t="s">
-        <v>405</v>
+        <v>483</v>
       </c>
       <c r="K94" t="s">
-        <v>406</v>
-      </c>
-      <c r="L94" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>408</v>
+        <v>485</v>
       </c>
       <c r="D95" t="s">
-        <v>409</v>
+        <v>486</v>
       </c>
       <c r="E95" t="s">
-        <v>410</v>
+        <v>487</v>
+      </c>
+      <c r="F95" t="s">
+        <v>488</v>
       </c>
       <c r="G95" t="s">
-        <v>411</v>
+        <v>489</v>
       </c>
       <c r="H95" t="s">
-        <v>412</v>
+        <v>490</v>
       </c>
       <c r="I95" t="s">
-        <v>413</v>
+        <v>482</v>
       </c>
       <c r="J95" t="s">
-        <v>405</v>
+        <v>483</v>
       </c>
       <c r="K95" t="s">
-        <v>406</v>
-      </c>
-      <c r="L95" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>415</v>
+        <v>492</v>
       </c>
       <c r="D96" t="s">
-        <v>416</v>
+        <v>493</v>
       </c>
       <c r="E96" t="s">
-        <v>417</v>
+        <v>494</v>
+      </c>
+      <c r="F96" t="s">
+        <v>495</v>
       </c>
       <c r="G96" t="s">
-        <v>418</v>
+        <v>496</v>
       </c>
       <c r="H96" t="s">
-        <v>419</v>
+        <v>497</v>
+      </c>
+      <c r="I96" t="s">
+        <v>482</v>
       </c>
       <c r="J96" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K96" t="s">
-        <v>420</v>
-      </c>
-      <c r="L96" t="s">
-        <v>421</v>
+        <v>499</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -5204,16 +5797,34 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>422</v>
+        <v>500</v>
+      </c>
+      <c r="D97" t="s">
+        <v>500</v>
+      </c>
+      <c r="E97" t="s">
+        <v>501</v>
+      </c>
+      <c r="F97" t="s">
+        <v>502</v>
+      </c>
+      <c r="G97" t="s">
+        <v>503</v>
+      </c>
+      <c r="H97" t="s">
+        <v>504</v>
+      </c>
+      <c r="I97" t="s">
+        <v>482</v>
       </c>
       <c r="J97" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K97" t="s">
-        <v>420</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -5221,16 +5832,34 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>423</v>
+        <v>506</v>
+      </c>
+      <c r="D98" t="s">
+        <v>507</v>
+      </c>
+      <c r="E98" t="s">
+        <v>508</v>
+      </c>
+      <c r="F98" t="s">
+        <v>509</v>
+      </c>
+      <c r="G98" t="s">
+        <v>510</v>
+      </c>
+      <c r="H98" t="s">
+        <v>511</v>
+      </c>
+      <c r="I98" t="s">
+        <v>482</v>
       </c>
       <c r="J98" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K98" t="s">
-        <v>420</v>
+        <v>512</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -5238,16 +5867,34 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>424</v>
+        <v>513</v>
+      </c>
+      <c r="D99" t="s">
+        <v>514</v>
+      </c>
+      <c r="E99" t="s">
+        <v>515</v>
+      </c>
+      <c r="F99" t="s">
+        <v>516</v>
+      </c>
+      <c r="G99" t="s">
+        <v>517</v>
+      </c>
+      <c r="H99" t="s">
+        <v>518</v>
+      </c>
+      <c r="I99" t="s">
+        <v>482</v>
       </c>
       <c r="J99" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K99" t="s">
-        <v>420</v>
+        <v>519</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -5255,16 +5902,34 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>425</v>
+        <v>520</v>
+      </c>
+      <c r="D100" t="s">
+        <v>520</v>
+      </c>
+      <c r="E100" t="s">
+        <v>521</v>
+      </c>
+      <c r="F100" t="s">
+        <v>522</v>
+      </c>
+      <c r="G100" t="s">
+        <v>523</v>
+      </c>
+      <c r="H100" t="s">
+        <v>524</v>
+      </c>
+      <c r="I100" t="s">
+        <v>482</v>
       </c>
       <c r="J100" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K100" t="s">
-        <v>420</v>
+        <v>525</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -5272,16 +5937,34 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>426</v>
+        <v>526</v>
+      </c>
+      <c r="D101" t="s">
+        <v>527</v>
+      </c>
+      <c r="E101" t="s">
+        <v>528</v>
+      </c>
+      <c r="F101" t="s">
+        <v>529</v>
+      </c>
+      <c r="G101" t="s">
+        <v>530</v>
+      </c>
+      <c r="H101" t="s">
+        <v>531</v>
+      </c>
+      <c r="I101" t="s">
+        <v>482</v>
       </c>
       <c r="J101" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K101" t="s">
-        <v>420</v>
+        <v>532</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -5289,16 +5972,34 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>427</v>
+        <v>533</v>
+      </c>
+      <c r="D102" t="s">
+        <v>533</v>
+      </c>
+      <c r="E102" t="s">
+        <v>534</v>
+      </c>
+      <c r="F102" t="s">
+        <v>535</v>
+      </c>
+      <c r="G102" t="s">
+        <v>536</v>
+      </c>
+      <c r="H102" t="s">
+        <v>537</v>
+      </c>
+      <c r="I102" t="s">
+        <v>482</v>
       </c>
       <c r="J102" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K102" t="s">
-        <v>420</v>
+        <v>538</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -5306,16 +6007,34 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>428</v>
+        <v>539</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F103" t="s">
+        <v>542</v>
+      </c>
+      <c r="G103" t="s">
+        <v>543</v>
+      </c>
+      <c r="H103" t="s">
+        <v>544</v>
+      </c>
+      <c r="I103" t="s">
+        <v>482</v>
       </c>
       <c r="J103" t="s">
-        <v>405</v>
+        <v>498</v>
       </c>
       <c r="K103" t="s">
-        <v>420</v>
+        <v>545</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -5323,16 +6042,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>429</v>
+        <v>546</v>
+      </c>
+      <c r="I104" t="s">
+        <v>482</v>
       </c>
       <c r="J104" t="s">
-        <v>405</v>
-      </c>
-      <c r="K104" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -5340,16 +6059,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>431</v>
+        <v>548</v>
+      </c>
+      <c r="I105" t="s">
+        <v>482</v>
       </c>
       <c r="J105" t="s">
-        <v>405</v>
-      </c>
-      <c r="K105" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -5357,16 +6076,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>432</v>
+        <v>549</v>
+      </c>
+      <c r="I106" t="s">
+        <v>482</v>
       </c>
       <c r="J106" t="s">
-        <v>405</v>
-      </c>
-      <c r="K106" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -5374,16 +6093,16 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>433</v>
+        <v>550</v>
+      </c>
+      <c r="I107" t="s">
+        <v>482</v>
       </c>
       <c r="J107" t="s">
-        <v>405</v>
-      </c>
-      <c r="K107" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -5391,16 +6110,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>434</v>
+        <v>551</v>
+      </c>
+      <c r="I108" t="s">
+        <v>482</v>
       </c>
       <c r="J108" t="s">
-        <v>405</v>
-      </c>
-      <c r="K108" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -5408,16 +6127,16 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C109" t="s">
-        <v>435</v>
+        <v>552</v>
+      </c>
+      <c r="I109" t="s">
+        <v>482</v>
       </c>
       <c r="J109" t="s">
-        <v>405</v>
-      </c>
-      <c r="K109" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -5425,16 +6144,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>436</v>
+        <v>553</v>
+      </c>
+      <c r="I110" t="s">
+        <v>482</v>
       </c>
       <c r="J110" t="s">
-        <v>405</v>
-      </c>
-      <c r="K110" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -5442,16 +6161,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>437</v>
+        <v>554</v>
+      </c>
+      <c r="I111" t="s">
+        <v>482</v>
       </c>
       <c r="J111" t="s">
-        <v>405</v>
-      </c>
-      <c r="K111" t="s">
-        <v>430</v>
+        <v>547</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -5459,1524 +6178,1524 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>438</v>
+        <v>555</v>
+      </c>
+      <c r="I112" t="s">
+        <v>482</v>
       </c>
       <c r="J112" t="s">
-        <v>405</v>
-      </c>
-      <c r="K112" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>439</v>
+        <v>556</v>
+      </c>
+      <c r="I113" t="s">
+        <v>482</v>
       </c>
       <c r="J113" t="s">
-        <v>405</v>
-      </c>
-      <c r="K113" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>440</v>
+        <v>557</v>
+      </c>
+      <c r="I114" t="s">
+        <v>482</v>
       </c>
       <c r="J114" t="s">
-        <v>405</v>
-      </c>
-      <c r="K114" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>441</v>
+        <v>558</v>
+      </c>
+      <c r="I115" t="s">
+        <v>482</v>
       </c>
       <c r="J115" t="s">
-        <v>405</v>
-      </c>
-      <c r="K115" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>442</v>
+        <v>559</v>
+      </c>
+      <c r="I116" t="s">
+        <v>482</v>
       </c>
       <c r="J116" t="s">
-        <v>405</v>
-      </c>
-      <c r="K116" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>443</v>
+        <v>560</v>
       </c>
       <c r="D117" t="s">
-        <v>443</v>
+        <v>560</v>
       </c>
       <c r="E117" t="s">
-        <v>444</v>
+        <v>561</v>
+      </c>
+      <c r="F117" t="s">
+        <v>562</v>
       </c>
       <c r="G117" t="s">
-        <v>445</v>
-      </c>
-      <c r="H117" t="s">
-        <v>446</v>
+        <v>563</v>
+      </c>
+      <c r="I117" t="s">
+        <v>564</v>
       </c>
       <c r="J117" t="s">
-        <v>447</v>
+        <v>565</v>
       </c>
       <c r="K117" t="s">
-        <v>448</v>
-      </c>
-      <c r="L117" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>450</v>
+        <v>567</v>
+      </c>
+      <c r="I118" t="s">
+        <v>564</v>
       </c>
       <c r="J118" t="s">
-        <v>447</v>
-      </c>
-      <c r="K118" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>451</v>
+        <v>568</v>
       </c>
       <c r="D119" t="s">
-        <v>452</v>
+        <v>569</v>
       </c>
       <c r="E119" t="s">
-        <v>453</v>
+        <v>570</v>
+      </c>
+      <c r="F119" t="s">
+        <v>571</v>
       </c>
       <c r="G119" t="s">
-        <v>454</v>
-      </c>
-      <c r="H119" t="s">
-        <v>455</v>
+        <v>572</v>
+      </c>
+      <c r="I119" t="s">
+        <v>564</v>
       </c>
       <c r="J119" t="s">
-        <v>447</v>
+        <v>565</v>
       </c>
       <c r="K119" t="s">
-        <v>448</v>
-      </c>
-      <c r="L119" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>457</v>
+        <v>574</v>
+      </c>
+      <c r="I120" t="s">
+        <v>564</v>
       </c>
       <c r="J120" t="s">
-        <v>447</v>
-      </c>
-      <c r="K120" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>458</v>
+        <v>575</v>
+      </c>
+      <c r="I121" t="s">
+        <v>564</v>
       </c>
       <c r="J121" t="s">
-        <v>447</v>
-      </c>
-      <c r="K121" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>459</v>
+        <v>576</v>
+      </c>
+      <c r="I122" t="s">
+        <v>564</v>
       </c>
       <c r="J122" t="s">
-        <v>447</v>
-      </c>
-      <c r="K122" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
       <c r="A123">
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C123" t="s">
-        <v>460</v>
+        <v>577</v>
+      </c>
+      <c r="I123" t="s">
+        <v>564</v>
       </c>
       <c r="J123" t="s">
-        <v>447</v>
-      </c>
-      <c r="K123" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
       <c r="A124">
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C124" t="s">
-        <v>461</v>
+        <v>578</v>
+      </c>
+      <c r="I124" t="s">
+        <v>564</v>
       </c>
       <c r="J124" t="s">
-        <v>447</v>
-      </c>
-      <c r="K124" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
       <c r="A125">
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C125" t="s">
-        <v>462</v>
+        <v>579</v>
+      </c>
+      <c r="I125" t="s">
+        <v>564</v>
       </c>
       <c r="J125" t="s">
-        <v>447</v>
-      </c>
-      <c r="K125" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
       <c r="A126">
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>463</v>
+        <v>580</v>
+      </c>
+      <c r="I126" t="s">
+        <v>564</v>
       </c>
       <c r="J126" t="s">
-        <v>447</v>
-      </c>
-      <c r="K126" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
       <c r="A127">
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>464</v>
+        <v>581</v>
+      </c>
+      <c r="I127" t="s">
+        <v>564</v>
       </c>
       <c r="J127" t="s">
-        <v>447</v>
-      </c>
-      <c r="K127" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
       <c r="A128">
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>465</v>
+        <v>582</v>
+      </c>
+      <c r="I128" t="s">
+        <v>564</v>
       </c>
       <c r="J128" t="s">
-        <v>447</v>
-      </c>
-      <c r="K128" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
       <c r="A129">
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>466</v>
+        <v>583</v>
       </c>
       <c r="D129" t="s">
-        <v>467</v>
+        <v>584</v>
       </c>
       <c r="E129" t="s">
-        <v>468</v>
+        <v>585</v>
+      </c>
+      <c r="F129" t="s">
+        <v>586</v>
       </c>
       <c r="G129" t="s">
-        <v>469</v>
-      </c>
-      <c r="H129" t="s">
-        <v>470</v>
+        <v>587</v>
+      </c>
+      <c r="I129" t="s">
+        <v>588</v>
       </c>
       <c r="J129" t="s">
-        <v>471</v>
-      </c>
-      <c r="K129" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
       <c r="A130">
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>472</v>
+        <v>589</v>
+      </c>
+      <c r="I130" t="s">
+        <v>588</v>
       </c>
       <c r="J130" t="s">
-        <v>471</v>
-      </c>
-      <c r="K130" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
       <c r="A131">
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>473</v>
+        <v>590</v>
+      </c>
+      <c r="I131" t="s">
+        <v>588</v>
       </c>
       <c r="J131" t="s">
-        <v>471</v>
-      </c>
-      <c r="K131" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
       <c r="A132">
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>474</v>
+        <v>591</v>
+      </c>
+      <c r="I132" t="s">
+        <v>588</v>
       </c>
       <c r="J132" t="s">
-        <v>471</v>
-      </c>
-      <c r="K132" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
       <c r="A133">
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>475</v>
+        <v>592</v>
+      </c>
+      <c r="I133" t="s">
+        <v>588</v>
       </c>
       <c r="J133" t="s">
-        <v>471</v>
-      </c>
-      <c r="K133" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
       <c r="A134">
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>476</v>
+        <v>593</v>
+      </c>
+      <c r="I134" t="s">
+        <v>588</v>
       </c>
       <c r="J134" t="s">
-        <v>471</v>
-      </c>
-      <c r="K134" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
       <c r="A135">
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>477</v>
+        <v>594</v>
+      </c>
+      <c r="I135" t="s">
+        <v>588</v>
       </c>
       <c r="J135" t="s">
-        <v>471</v>
-      </c>
-      <c r="K135" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
       <c r="A136">
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
-        <v>478</v>
+        <v>595</v>
+      </c>
+      <c r="I136" t="s">
+        <v>588</v>
       </c>
       <c r="J136" t="s">
-        <v>471</v>
-      </c>
-      <c r="K136" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
       <c r="A137">
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>479</v>
+        <v>596</v>
+      </c>
+      <c r="I137" t="s">
+        <v>588</v>
       </c>
       <c r="J137" t="s">
-        <v>471</v>
-      </c>
-      <c r="K137" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
       <c r="A138">
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C138" t="s">
-        <v>480</v>
+        <v>597</v>
+      </c>
+      <c r="I138" t="s">
+        <v>588</v>
       </c>
       <c r="J138" t="s">
-        <v>471</v>
-      </c>
-      <c r="K138" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139">
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>481</v>
+        <v>598</v>
+      </c>
+      <c r="I139" t="s">
+        <v>588</v>
       </c>
       <c r="J139" t="s">
-        <v>471</v>
-      </c>
-      <c r="K139" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10">
       <c r="A140">
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>482</v>
+        <v>599</v>
+      </c>
+      <c r="I140" t="s">
+        <v>588</v>
       </c>
       <c r="J140" t="s">
-        <v>471</v>
-      </c>
-      <c r="K140" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
       <c r="A141">
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>483</v>
+        <v>600</v>
+      </c>
+      <c r="I141" t="s">
+        <v>588</v>
       </c>
       <c r="J141" t="s">
-        <v>471</v>
-      </c>
-      <c r="K141" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10">
       <c r="A142">
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>484</v>
+        <v>601</v>
+      </c>
+      <c r="I142" t="s">
+        <v>588</v>
       </c>
       <c r="J142" t="s">
-        <v>471</v>
-      </c>
-      <c r="K142" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143">
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>485</v>
+        <v>602</v>
+      </c>
+      <c r="I143" t="s">
+        <v>588</v>
       </c>
       <c r="J143" t="s">
-        <v>471</v>
-      </c>
-      <c r="K143" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144">
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>486</v>
+        <v>603</v>
+      </c>
+      <c r="I144" t="s">
+        <v>588</v>
       </c>
       <c r="J144" t="s">
-        <v>471</v>
-      </c>
-      <c r="K144" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145">
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>487</v>
+        <v>604</v>
+      </c>
+      <c r="I145" t="s">
+        <v>605</v>
       </c>
       <c r="J145" t="s">
-        <v>488</v>
-      </c>
-      <c r="K145" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146">
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C146" t="s">
-        <v>490</v>
+        <v>607</v>
+      </c>
+      <c r="I146" t="s">
+        <v>605</v>
       </c>
       <c r="J146" t="s">
-        <v>488</v>
-      </c>
-      <c r="K146" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
       <c r="A147">
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>491</v>
+        <v>608</v>
+      </c>
+      <c r="I147" t="s">
+        <v>605</v>
       </c>
       <c r="J147" t="s">
-        <v>488</v>
-      </c>
-      <c r="K147" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
       <c r="A148">
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C148" t="s">
-        <v>492</v>
+        <v>609</v>
+      </c>
+      <c r="I148" t="s">
+        <v>605</v>
       </c>
       <c r="J148" t="s">
-        <v>488</v>
-      </c>
-      <c r="K148" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
       <c r="A149">
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>493</v>
+        <v>610</v>
+      </c>
+      <c r="I149" t="s">
+        <v>605</v>
       </c>
       <c r="J149" t="s">
-        <v>488</v>
-      </c>
-      <c r="K149" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150">
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>494</v>
+        <v>611</v>
+      </c>
+      <c r="I150" t="s">
+        <v>605</v>
       </c>
       <c r="J150" t="s">
-        <v>488</v>
-      </c>
-      <c r="K150" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10">
       <c r="A151">
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>495</v>
+        <v>612</v>
+      </c>
+      <c r="I151" t="s">
+        <v>605</v>
       </c>
       <c r="J151" t="s">
-        <v>488</v>
-      </c>
-      <c r="K151" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152">
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>497</v>
+        <v>614</v>
+      </c>
+      <c r="I152" t="s">
+        <v>605</v>
       </c>
       <c r="J152" t="s">
-        <v>488</v>
-      </c>
-      <c r="K152" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153">
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>498</v>
+        <v>615</v>
+      </c>
+      <c r="I153" t="s">
+        <v>605</v>
       </c>
       <c r="J153" t="s">
-        <v>488</v>
-      </c>
-      <c r="K153" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154">
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C154" t="s">
-        <v>499</v>
+        <v>616</v>
+      </c>
+      <c r="I154" t="s">
+        <v>605</v>
       </c>
       <c r="J154" t="s">
-        <v>488</v>
-      </c>
-      <c r="K154" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155">
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>500</v>
+        <v>617</v>
+      </c>
+      <c r="I155" t="s">
+        <v>605</v>
       </c>
       <c r="J155" t="s">
-        <v>488</v>
-      </c>
-      <c r="K155" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156">
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>501</v>
+        <v>618</v>
+      </c>
+      <c r="I156" t="s">
+        <v>605</v>
       </c>
       <c r="J156" t="s">
-        <v>488</v>
-      </c>
-      <c r="K156" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157">
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>502</v>
+        <v>619</v>
+      </c>
+      <c r="I157" t="s">
+        <v>605</v>
       </c>
       <c r="J157" t="s">
-        <v>488</v>
-      </c>
-      <c r="K157" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158">
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>503</v>
+        <v>620</v>
+      </c>
+      <c r="I158" t="s">
+        <v>605</v>
       </c>
       <c r="J158" t="s">
-        <v>488</v>
-      </c>
-      <c r="K158" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159">
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>504</v>
+        <v>621</v>
+      </c>
+      <c r="I159" t="s">
+        <v>605</v>
       </c>
       <c r="J159" t="s">
-        <v>488</v>
-      </c>
-      <c r="K159" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160">
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>505</v>
+        <v>622</v>
+      </c>
+      <c r="I160" t="s">
+        <v>605</v>
       </c>
       <c r="J160" t="s">
-        <v>488</v>
-      </c>
-      <c r="K160" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10">
       <c r="A161">
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>506</v>
+        <v>623</v>
+      </c>
+      <c r="I161" t="s">
+        <v>605</v>
       </c>
       <c r="J161" t="s">
-        <v>488</v>
-      </c>
-      <c r="K161" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162">
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>507</v>
+        <v>624</v>
+      </c>
+      <c r="I162" t="s">
+        <v>605</v>
       </c>
       <c r="J162" t="s">
-        <v>488</v>
-      </c>
-      <c r="K162" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
       <c r="A163">
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>508</v>
+        <v>625</v>
+      </c>
+      <c r="I163" t="s">
+        <v>605</v>
       </c>
       <c r="J163" t="s">
-        <v>488</v>
-      </c>
-      <c r="K163" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164">
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>509</v>
+        <v>626</v>
+      </c>
+      <c r="I164" t="s">
+        <v>605</v>
       </c>
       <c r="J164" t="s">
-        <v>488</v>
-      </c>
-      <c r="K164" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10">
       <c r="A165">
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>510</v>
+        <v>627</v>
+      </c>
+      <c r="I165" t="s">
+        <v>605</v>
       </c>
       <c r="J165" t="s">
-        <v>488</v>
-      </c>
-      <c r="K165" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10">
       <c r="A166">
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>511</v>
+        <v>628</v>
+      </c>
+      <c r="I166" t="s">
+        <v>605</v>
       </c>
       <c r="J166" t="s">
-        <v>488</v>
-      </c>
-      <c r="K166" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167">
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>512</v>
+        <v>629</v>
+      </c>
+      <c r="I167" t="s">
+        <v>605</v>
       </c>
       <c r="J167" t="s">
-        <v>488</v>
-      </c>
-      <c r="K167" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
       <c r="A168">
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>514</v>
+        <v>631</v>
+      </c>
+      <c r="I168" t="s">
+        <v>605</v>
       </c>
       <c r="J168" t="s">
-        <v>488</v>
-      </c>
-      <c r="K168" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
       <c r="A169">
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>515</v>
+        <v>632</v>
+      </c>
+      <c r="I169" t="s">
+        <v>605</v>
       </c>
       <c r="J169" t="s">
-        <v>488</v>
-      </c>
-      <c r="K169" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10">
       <c r="A170">
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>516</v>
+        <v>633</v>
+      </c>
+      <c r="I170" t="s">
+        <v>605</v>
       </c>
       <c r="J170" t="s">
-        <v>488</v>
-      </c>
-      <c r="K170" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
       <c r="A171">
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>517</v>
+        <v>634</v>
+      </c>
+      <c r="I171" t="s">
+        <v>605</v>
       </c>
       <c r="J171" t="s">
-        <v>488</v>
-      </c>
-      <c r="K171" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
       <c r="A172">
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>518</v>
+        <v>635</v>
+      </c>
+      <c r="I172" t="s">
+        <v>605</v>
       </c>
       <c r="J172" t="s">
-        <v>488</v>
-      </c>
-      <c r="K172" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
       <c r="A173">
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>519</v>
+        <v>636</v>
+      </c>
+      <c r="I173" t="s">
+        <v>605</v>
       </c>
       <c r="J173" t="s">
-        <v>488</v>
-      </c>
-      <c r="K173" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
       <c r="A174">
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>520</v>
+        <v>637</v>
+      </c>
+      <c r="I174" t="s">
+        <v>605</v>
       </c>
       <c r="J174" t="s">
-        <v>488</v>
-      </c>
-      <c r="K174" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="175" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
       <c r="A175">
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>521</v>
+        <v>638</v>
+      </c>
+      <c r="I175" t="s">
+        <v>605</v>
       </c>
       <c r="J175" t="s">
-        <v>488</v>
-      </c>
-      <c r="K175" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
       <c r="A176">
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>522</v>
+        <v>639</v>
+      </c>
+      <c r="I176" t="s">
+        <v>605</v>
       </c>
       <c r="J176" t="s">
-        <v>488</v>
-      </c>
-      <c r="K176" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
       <c r="A177">
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>523</v>
+        <v>640</v>
+      </c>
+      <c r="I177" t="s">
+        <v>605</v>
       </c>
       <c r="J177" t="s">
-        <v>488</v>
-      </c>
-      <c r="K177" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178">
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>524</v>
+        <v>641</v>
+      </c>
+      <c r="I178" t="s">
+        <v>605</v>
       </c>
       <c r="J178" t="s">
-        <v>488</v>
-      </c>
-      <c r="K178" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179">
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>526</v>
+        <v>643</v>
+      </c>
+      <c r="I179" t="s">
+        <v>605</v>
       </c>
       <c r="J179" t="s">
-        <v>488</v>
-      </c>
-      <c r="K179" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10">
       <c r="A180">
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>525</v>
+        <v>642</v>
+      </c>
+      <c r="I180" t="s">
+        <v>605</v>
       </c>
       <c r="J180" t="s">
-        <v>488</v>
-      </c>
-      <c r="K180" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
       <c r="A181">
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>527</v>
+        <v>644</v>
+      </c>
+      <c r="I181" t="s">
+        <v>605</v>
       </c>
       <c r="J181" t="s">
-        <v>488</v>
-      </c>
-      <c r="K181" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="182" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
       <c r="A182">
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>528</v>
+        <v>645</v>
+      </c>
+      <c r="I182" t="s">
+        <v>605</v>
       </c>
       <c r="J182" t="s">
-        <v>488</v>
-      </c>
-      <c r="K182" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10">
       <c r="A183">
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>529</v>
+        <v>646</v>
+      </c>
+      <c r="I183" t="s">
+        <v>605</v>
       </c>
       <c r="J183" t="s">
-        <v>488</v>
-      </c>
-      <c r="K183" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184">
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>530</v>
+        <v>647</v>
+      </c>
+      <c r="I184" t="s">
+        <v>605</v>
       </c>
       <c r="J184" t="s">
-        <v>488</v>
-      </c>
-      <c r="K184" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="185" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
       <c r="A185">
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>531</v>
+        <v>648</v>
+      </c>
+      <c r="I185" t="s">
+        <v>605</v>
       </c>
       <c r="J185" t="s">
-        <v>488</v>
-      </c>
-      <c r="K185" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="186" spans="1:11">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10">
       <c r="A186">
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C186" t="s">
-        <v>532</v>
+        <v>649</v>
+      </c>
+      <c r="I186" t="s">
+        <v>605</v>
       </c>
       <c r="J186" t="s">
-        <v>488</v>
-      </c>
-      <c r="K186" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
       <c r="A187">
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>534</v>
+        <v>651</v>
+      </c>
+      <c r="I187" t="s">
+        <v>605</v>
       </c>
       <c r="J187" t="s">
-        <v>488</v>
-      </c>
-      <c r="K187" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
       <c r="A188">
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C188" t="s">
-        <v>535</v>
+        <v>652</v>
+      </c>
+      <c r="I188" t="s">
+        <v>605</v>
       </c>
       <c r="J188" t="s">
-        <v>488</v>
-      </c>
-      <c r="K188" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10">
       <c r="A189">
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>536</v>
+        <v>653</v>
+      </c>
+      <c r="I189" t="s">
+        <v>605</v>
       </c>
       <c r="J189" t="s">
-        <v>488</v>
-      </c>
-      <c r="K189" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
       <c r="A190">
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>537</v>
+        <v>654</v>
+      </c>
+      <c r="I190" t="s">
+        <v>605</v>
       </c>
       <c r="J190" t="s">
-        <v>488</v>
-      </c>
-      <c r="K190" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="191" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
       <c r="A191">
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C191" t="s">
-        <v>538</v>
+        <v>655</v>
+      </c>
+      <c r="I191" t="s">
+        <v>605</v>
       </c>
       <c r="J191" t="s">
-        <v>488</v>
-      </c>
-      <c r="K191" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="192" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
       <c r="A192">
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>539</v>
+        <v>656</v>
+      </c>
+      <c r="I192" t="s">
+        <v>605</v>
       </c>
       <c r="J192" t="s">
-        <v>488</v>
-      </c>
-      <c r="K192" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
       <c r="A193">
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>540</v>
+        <v>657</v>
+      </c>
+      <c r="I193" t="s">
+        <v>605</v>
       </c>
       <c r="J193" t="s">
-        <v>488</v>
-      </c>
-      <c r="K193" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="194" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
       <c r="A194">
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C194" t="s">
-        <v>541</v>
+        <v>658</v>
+      </c>
+      <c r="I194" t="s">
+        <v>605</v>
       </c>
       <c r="J194" t="s">
-        <v>488</v>
-      </c>
-      <c r="K194" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
       <c r="A195">
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C195" t="s">
-        <v>542</v>
+        <v>659</v>
+      </c>
+      <c r="I195" t="s">
+        <v>605</v>
       </c>
       <c r="J195" t="s">
-        <v>488</v>
-      </c>
-      <c r="K195" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
       <c r="A196">
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C196" t="s">
-        <v>533</v>
+        <v>650</v>
+      </c>
+      <c r="I196" t="s">
+        <v>605</v>
       </c>
       <c r="J196" t="s">
-        <v>488</v>
-      </c>
-      <c r="K196" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
       <c r="A197">
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C197" t="s">
-        <v>543</v>
+        <v>660</v>
+      </c>
+      <c r="I197" t="s">
+        <v>605</v>
       </c>
       <c r="J197" t="s">
-        <v>488</v>
-      </c>
-      <c r="K197" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
       <c r="A198">
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>544</v>
+        <v>661</v>
+      </c>
+      <c r="I198" t="s">
+        <v>605</v>
       </c>
       <c r="J198" t="s">
-        <v>488</v>
-      </c>
-      <c r="K198" t="s">
-        <v>533</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L198" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K198" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/docs/datas/world.xlsx
+++ b/public/docs/datas/world.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24700" windowHeight="14900"/>
+    <workbookView windowWidth="22780" windowHeight="14900"/>
   </bookViews>
   <sheets>
     <sheet name="country" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="912">
   <si>
     <t>no</t>
   </si>
@@ -665,12 +665,45 @@
     <t>阿富汗</t>
   </si>
   <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>Afghanistan.png</t>
+  </si>
+  <si>
+    <t>喀布尔</t>
+  </si>
+  <si>
+    <t>kabul</t>
+  </si>
+  <si>
     <t>西亚</t>
   </si>
   <si>
+    <t>AFG</t>
+  </si>
+  <si>
     <t>亚美尼亚</t>
   </si>
   <si>
+    <t>亚美尼亚共和国</t>
+  </si>
+  <si>
+    <t>Republic of Armenia</t>
+  </si>
+  <si>
+    <t>Armania.png</t>
+  </si>
+  <si>
+    <t>埃里温</t>
+  </si>
+  <si>
+    <t>Yerevan</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
     <t>阿塞拜疆</t>
   </si>
   <si>
@@ -686,6 +719,9 @@
     <t>巴库</t>
   </si>
   <si>
+    <t>Baku</t>
+  </si>
+  <si>
     <t>AZE</t>
   </si>
   <si>
@@ -704,15 +740,51 @@
     <t>麦纳麦</t>
   </si>
   <si>
+    <t>Manama</t>
+  </si>
+  <si>
     <t>BHR</t>
   </si>
   <si>
     <t>塞浦路斯</t>
   </si>
   <si>
+    <t>塞浦路斯共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Cyprus</t>
+  </si>
+  <si>
+    <t>Cyprus.png</t>
+  </si>
+  <si>
+    <t>尼科西亚</t>
+  </si>
+  <si>
+    <t>Nicosia</t>
+  </si>
+  <si>
+    <t>CYP</t>
+  </si>
+  <si>
     <t>格鲁吉亚</t>
   </si>
   <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Georgia.png</t>
+  </si>
+  <si>
+    <t>第比利斯</t>
+  </si>
+  <si>
+    <t>Tbilisi</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
     <t>伊朗</t>
   </si>
   <si>
@@ -728,12 +800,33 @@
     <t>德黑兰</t>
   </si>
   <si>
+    <t>Tehran</t>
+  </si>
+  <si>
     <t>IRN</t>
   </si>
   <si>
     <t>伊拉克</t>
   </si>
   <si>
+    <t>伊拉克共和国</t>
+  </si>
+  <si>
+    <t>Republic of Iraq</t>
+  </si>
+  <si>
+    <t>Iraq.png</t>
+  </si>
+  <si>
+    <t>巴格达</t>
+  </si>
+  <si>
+    <t>Baghdad</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
     <t>以色列</t>
   </si>
   <si>
@@ -749,24 +842,117 @@
     <t>耶路撒冷</t>
   </si>
   <si>
+    <t>JERUSALEM</t>
+  </si>
+  <si>
     <t>ISR</t>
   </si>
   <si>
     <t>约旦</t>
   </si>
   <si>
+    <t>约旦哈希姆王国</t>
+  </si>
+  <si>
+    <t>The Hashemite Kingdom of Jordan</t>
+  </si>
+  <si>
+    <t>Jordan.png</t>
+  </si>
+  <si>
+    <t>安曼</t>
+  </si>
+  <si>
+    <t>Amman</t>
+  </si>
+  <si>
+    <t>JOR</t>
+  </si>
+  <si>
     <t>科威特</t>
   </si>
   <si>
+    <t>科威特国</t>
+  </si>
+  <si>
+    <t>The State of Kuwait</t>
+  </si>
+  <si>
+    <t>Kuwait.png</t>
+  </si>
+  <si>
+    <t>科威特城</t>
+  </si>
+  <si>
+    <t>Kuwait City</t>
+  </si>
+  <si>
+    <t>KWT</t>
+  </si>
+  <si>
     <t>黎巴嫩</t>
   </si>
   <si>
+    <t>黎巴嫩共和国</t>
+  </si>
+  <si>
+    <t>The Lebanese Republic</t>
+  </si>
+  <si>
+    <t>Lebanon.png</t>
+  </si>
+  <si>
+    <t>贝鲁特</t>
+  </si>
+  <si>
+    <t>Beirut</t>
+  </si>
+  <si>
+    <t>LBN</t>
+  </si>
+  <si>
     <t>阿曼</t>
   </si>
   <si>
+    <t>阿曼苏丹国</t>
+  </si>
+  <si>
+    <t>The Sultanate of Oman</t>
+  </si>
+  <si>
+    <t>Oman.png</t>
+  </si>
+  <si>
+    <t>马斯喀特</t>
+  </si>
+  <si>
+    <t>Muscat</t>
+  </si>
+  <si>
+    <t>OMN</t>
+  </si>
+  <si>
     <t>巴勒斯坦</t>
   </si>
   <si>
+    <t>巴勒斯坦国</t>
+  </si>
+  <si>
+    <t>The State of Palestine</t>
+  </si>
+  <si>
+    <t>Palestine.png</t>
+  </si>
+  <si>
+    <t>拉姆安拉</t>
+  </si>
+  <si>
+    <t>Ramallah</t>
+  </si>
+  <si>
+    <t>PSE</t>
+  </si>
+  <si>
     <t>卡塔尔</t>
   </si>
   <si>
@@ -782,15 +968,54 @@
     <t>多哈</t>
   </si>
   <si>
+    <t>Doha</t>
+  </si>
+  <si>
     <t>QAT</t>
   </si>
   <si>
     <t>沙特阿拉伯</t>
   </si>
   <si>
+    <t>沙特阿拉伯王国</t>
+  </si>
+  <si>
+    <t>Kingdom of Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Saudi Arabia.png</t>
+  </si>
+  <si>
+    <t>利雅得</t>
+  </si>
+  <si>
+    <t>Riyadh</t>
+  </si>
+  <si>
+    <t>SAU</t>
+  </si>
+  <si>
     <t>叙利亚</t>
   </si>
   <si>
+    <t>阿拉伯叙利亚共和国</t>
+  </si>
+  <si>
+    <t>The Syrian Arab Republic</t>
+  </si>
+  <si>
+    <t>Syria.png</t>
+  </si>
+  <si>
+    <t>大马士革市</t>
+  </si>
+  <si>
+    <t>Damascus</t>
+  </si>
+  <si>
+    <t>SYR</t>
+  </si>
+  <si>
     <t>土耳其</t>
   </si>
   <si>
@@ -806,6 +1031,9 @@
     <t>安卡拉</t>
   </si>
   <si>
+    <t>Ankara</t>
+  </si>
+  <si>
     <t>TUR</t>
   </si>
   <si>
@@ -833,6 +1061,24 @@
     <t>也门</t>
   </si>
   <si>
+    <t>也门共和国</t>
+  </si>
+  <si>
+    <t>Republic of Yemen</t>
+  </si>
+  <si>
+    <t>Yemen.png</t>
+  </si>
+  <si>
+    <t>萨那市</t>
+  </si>
+  <si>
+    <t>Sana'a</t>
+  </si>
+  <si>
+    <t>YEM</t>
+  </si>
+  <si>
     <t>比利时</t>
   </si>
   <si>
@@ -1394,27 +1640,132 @@
     <t>CHE</t>
   </si>
   <si>
-    <t>阿尔巴里亚</t>
+    <t>阿尔巴尼亚</t>
+  </si>
+  <si>
+    <t>阿尔巴尼亚共和国</t>
+  </si>
+  <si>
+    <t>Republic of Albania</t>
+  </si>
+  <si>
+    <t>Albania.png</t>
+  </si>
+  <si>
+    <t>地拉那</t>
+  </si>
+  <si>
+    <t>Tirana</t>
   </si>
   <si>
     <t>南欧</t>
   </si>
   <si>
+    <t>ALB</t>
+  </si>
+  <si>
     <t>安道尔</t>
   </si>
   <si>
+    <t>安道尔公国</t>
+  </si>
+  <si>
+    <t>Principality of Andorra</t>
+  </si>
+  <si>
+    <t>Andorra.png</t>
+  </si>
+  <si>
+    <t>安道尔城</t>
+  </si>
+  <si>
+    <t>Andorra La Vella</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
     <t>波斯尼亚和黑塞哥维那</t>
   </si>
   <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina.png</t>
+  </si>
+  <si>
+    <t>萨拉热窝</t>
+  </si>
+  <si>
+    <t>Saraybosna</t>
+  </si>
+  <si>
+    <t>BIH</t>
+  </si>
+  <si>
     <t>保加利亚</t>
   </si>
   <si>
+    <t>保加利亚共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Bulgaria</t>
+  </si>
+  <si>
+    <t>Bulgaria.png</t>
+  </si>
+  <si>
+    <t>索非亚</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>BGR</t>
+  </si>
+  <si>
     <t>克罗地亚</t>
   </si>
   <si>
+    <t>克罗地亚共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Croatia</t>
+  </si>
+  <si>
+    <t>Croatia.png</t>
+  </si>
+  <si>
+    <t>萨格勒布</t>
+  </si>
+  <si>
+    <t>Zagreb</t>
+  </si>
+  <si>
+    <t>HRV</t>
+  </si>
+  <si>
     <t>希腊</t>
   </si>
   <si>
+    <t>希腊共和国</t>
+  </si>
+  <si>
+    <t>The Hellenic Republic</t>
+  </si>
+  <si>
+    <t>Greece.png</t>
+  </si>
+  <si>
+    <t>雅典</t>
+  </si>
+  <si>
+    <t>Athens</t>
+  </si>
+  <si>
+    <t>GRC</t>
+  </si>
+  <si>
     <t>意大利</t>
   </si>
   <si>
@@ -1430,39 +1781,216 @@
     <t>罗马</t>
   </si>
   <si>
+    <t>Rome</t>
+  </si>
+  <si>
     <t>ITA</t>
   </si>
   <si>
     <t>北马其顿</t>
   </si>
   <si>
+    <t>北马其顿共和国</t>
+  </si>
+  <si>
+    <t>The Republic of North Macedonia</t>
+  </si>
+  <si>
+    <t>New Macedonia.png</t>
+  </si>
+  <si>
+    <t>斯科普里</t>
+  </si>
+  <si>
+    <t>Skopje</t>
+  </si>
+  <si>
+    <t>MKD</t>
+  </si>
+  <si>
     <t>马耳他</t>
   </si>
   <si>
+    <t>马耳他共和国</t>
+  </si>
+  <si>
+    <t>Republic of Malta</t>
+  </si>
+  <si>
+    <t>Malta.png</t>
+  </si>
+  <si>
+    <t>瓦莱塔</t>
+  </si>
+  <si>
+    <t>Valletta</t>
+  </si>
+  <si>
+    <t>MLT</t>
+  </si>
+  <si>
     <t>黑山</t>
   </si>
   <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Montenegro.png</t>
+  </si>
+  <si>
+    <t>波德戈里察</t>
+  </si>
+  <si>
+    <t>Podgorica</t>
+  </si>
+  <si>
+    <t>MNE</t>
+  </si>
+  <si>
     <t>葡萄牙</t>
   </si>
   <si>
+    <t>葡萄牙共和国</t>
+  </si>
+  <si>
+    <t>The Portuguese Republic</t>
+  </si>
+  <si>
+    <t>Portuguese.png</t>
+  </si>
+  <si>
+    <t>里斯本</t>
+  </si>
+  <si>
+    <t>Lisbon</t>
+  </si>
+  <si>
+    <t>PRT</t>
+  </si>
+  <si>
     <t>罗马尼亚</t>
   </si>
   <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Romania.png</t>
+  </si>
+  <si>
+    <t>布加勒斯特</t>
+  </si>
+  <si>
+    <t>Bucharest</t>
+  </si>
+  <si>
+    <t>ROU</t>
+  </si>
+  <si>
     <t>圣马力诺</t>
   </si>
   <si>
+    <t>圣马力诺共和国</t>
+  </si>
+  <si>
+    <t>The Republic of San Marino</t>
+  </si>
+  <si>
+    <t>San Marino.png</t>
+  </si>
+  <si>
+    <t>圣马力诺市</t>
+  </si>
+  <si>
+    <t>San Marino</t>
+  </si>
+  <si>
+    <t>SMR</t>
+  </si>
+  <si>
     <t>塞尔维亚</t>
   </si>
   <si>
+    <t>塞尔维亚共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Serbia</t>
+  </si>
+  <si>
+    <t>Serbia.png</t>
+  </si>
+  <si>
+    <t>贝尔格莱德</t>
+  </si>
+  <si>
+    <t>Belgrade</t>
+  </si>
+  <si>
+    <t>SRB</t>
+  </si>
+  <si>
     <t>斯洛文尼亚</t>
   </si>
   <si>
+    <t>斯洛文尼亚共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Slovenia</t>
+  </si>
+  <si>
+    <t>Slovenia.png</t>
+  </si>
+  <si>
+    <t>卢布尔雅那</t>
+  </si>
+  <si>
+    <t>Ljubljana</t>
+  </si>
+  <si>
+    <t>SVN</t>
+  </si>
+  <si>
     <t>西班牙</t>
   </si>
   <si>
+    <t>西班牙王国</t>
+  </si>
+  <si>
+    <t>The Kingdom of Spain</t>
+  </si>
+  <si>
+    <t>Spain.png</t>
+  </si>
+  <si>
+    <t>马德里</t>
+  </si>
+  <si>
+    <t>Madrid</t>
+  </si>
+  <si>
+    <t>ESP</t>
+  </si>
+  <si>
     <t>梵蒂冈</t>
   </si>
   <si>
+    <t>梵蒂冈城国</t>
+  </si>
+  <si>
+    <t>The Vatican City State</t>
+  </si>
+  <si>
+    <t>Vatican City.png</t>
+  </si>
+  <si>
+    <t>梵蒂冈城</t>
+  </si>
+  <si>
+    <t>Vatican City</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
     <t>加拿大</t>
   </si>
   <si>
@@ -1673,45 +2201,261 @@
     <t>安提瓜和巴布达</t>
   </si>
   <si>
+    <t>Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>Antigua and Barbuda.png</t>
+  </si>
+  <si>
+    <t>圣约翰</t>
+  </si>
+  <si>
+    <t>Saint John’s</t>
+  </si>
+  <si>
     <t>加勒比</t>
   </si>
   <si>
+    <t>ATG</t>
+  </si>
+  <si>
     <t>巴哈马</t>
   </si>
   <si>
+    <t>巴哈马国</t>
+  </si>
+  <si>
+    <t>Commonwealth of The Bahamas</t>
+  </si>
+  <si>
+    <t>Bahamas.png</t>
+  </si>
+  <si>
+    <t>拿骚</t>
+  </si>
+  <si>
+    <t>Nassau</t>
+  </si>
+  <si>
+    <t>BHS</t>
+  </si>
+  <si>
     <t>巴巴多斯</t>
   </si>
   <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Barbados.png</t>
+  </si>
+  <si>
+    <t>布里奇顿</t>
+  </si>
+  <si>
+    <t>Bridgetown</t>
+  </si>
+  <si>
+    <t>BRB</t>
+  </si>
+  <si>
     <t>古巴</t>
   </si>
   <si>
+    <t>古巴共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Cuba</t>
+  </si>
+  <si>
+    <t>Cuba.png</t>
+  </si>
+  <si>
+    <t>哈瓦那</t>
+  </si>
+  <si>
+    <t>Havana</t>
+  </si>
+  <si>
+    <t>CUB</t>
+  </si>
+  <si>
     <t>多米尼克</t>
   </si>
   <si>
+    <t>多米尼克国</t>
+  </si>
+  <si>
+    <t>The Commonwealth of Dominica</t>
+  </si>
+  <si>
+    <t>Dominica.png</t>
+  </si>
+  <si>
+    <t>罗索</t>
+  </si>
+  <si>
+    <t>Roseau</t>
+  </si>
+  <si>
+    <t>DMA</t>
+  </si>
+  <si>
     <t>多米尼加</t>
   </si>
   <si>
+    <t>多米尼加共和国</t>
+  </si>
+  <si>
+    <t>The Dominican Republic</t>
+  </si>
+  <si>
+    <t>Dominican Republic.png</t>
+  </si>
+  <si>
+    <t>圣多明各</t>
+  </si>
+  <si>
+    <t>Santo Domingo</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
     <t>格林纳达</t>
   </si>
   <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>Grenada.png</t>
+  </si>
+  <si>
+    <t>圣乔治</t>
+  </si>
+  <si>
+    <t>St. George's</t>
+  </si>
+  <si>
+    <t>GRD</t>
+  </si>
+  <si>
     <t>海地</t>
   </si>
   <si>
+    <t>海地共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Haiti</t>
+  </si>
+  <si>
+    <t>Haiti.png</t>
+  </si>
+  <si>
+    <t>太子港</t>
+  </si>
+  <si>
+    <t>Port of Prince</t>
+  </si>
+  <si>
+    <t>HT</t>
+  </si>
+  <si>
     <t>牙买加</t>
   </si>
   <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Jamaica.png</t>
+  </si>
+  <si>
+    <t>金斯敦</t>
+  </si>
+  <si>
+    <t>Kingston</t>
+  </si>
+  <si>
+    <t>JAM</t>
+  </si>
+  <si>
     <t>圣基茨和尼维斯</t>
   </si>
   <si>
+    <t>圣基茨和尼维斯联邦</t>
+  </si>
+  <si>
+    <t>The Federation of Saint Kitts and Nevis</t>
+  </si>
+  <si>
+    <t>Saint Kitts and Nevis.png</t>
+  </si>
+  <si>
+    <t>巴斯特尔</t>
+  </si>
+  <si>
+    <t>Basseterre</t>
+  </si>
+  <si>
+    <t>KNA</t>
+  </si>
+  <si>
     <t>圣卢西亚</t>
   </si>
   <si>
+    <t>Saint Lucia</t>
+  </si>
+  <si>
+    <t>Saint Lucia.png</t>
+  </si>
+  <si>
+    <t>卡斯特里</t>
+  </si>
+  <si>
+    <t>Castries</t>
+  </si>
+  <si>
+    <t>LCA</t>
+  </si>
+  <si>
     <t>圣文森特和格林纳丁斯</t>
   </si>
   <si>
+    <t>Saint Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t>Saint Vincent and the Grenadines.png</t>
+  </si>
+  <si>
+    <t>金斯顿</t>
+  </si>
+  <si>
+    <t>Kingstown</t>
+  </si>
+  <si>
+    <t>VCT</t>
+  </si>
+  <si>
     <t>特立尼达和多巴哥</t>
   </si>
   <si>
+    <t>特立尼达和多巴哥共和国</t>
+  </si>
+  <si>
+    <t>The Republic of Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>Trinidad and Tobago.png</t>
+  </si>
+  <si>
+    <t>西班牙港</t>
+  </si>
+  <si>
+    <t>Port of Spain</t>
+  </si>
+  <si>
+    <t>TTO</t>
+  </si>
+  <si>
     <t>阿根廷</t>
   </si>
   <si>
@@ -1724,6 +2468,9 @@
     <t>布宜诺斯艾利斯</t>
   </si>
   <si>
+    <t>Buenos Aires</t>
+  </si>
+  <si>
     <t>南美洲</t>
   </si>
   <si>
@@ -1749,6 +2496,9 @@
   </si>
   <si>
     <t>巴西利亚</t>
+  </si>
+  <si>
+    <t>Brasilia</t>
   </si>
   <si>
     <t>BRA</t>
@@ -2028,7 +2778,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2038,6 +2788,13 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FF333333"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -2506,16 +3263,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2524,121 +3278,127 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -4000,11 +4760,29 @@
       <c r="C30" t="s">
         <v>210</v>
       </c>
+      <c r="D30" t="s">
+        <v>210</v>
+      </c>
+      <c r="E30" t="s">
+        <v>211</v>
+      </c>
+      <c r="F30" t="s">
+        <v>212</v>
+      </c>
+      <c r="G30" t="s">
+        <v>213</v>
+      </c>
+      <c r="H30" t="s">
+        <v>214</v>
+      </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
       <c r="J30" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K30" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4015,13 +4793,31 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>212</v>
+        <v>217</v>
+      </c>
+      <c r="D31" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31" t="s">
+        <v>220</v>
+      </c>
+      <c r="G31" t="s">
+        <v>221</v>
+      </c>
+      <c r="H31" t="s">
+        <v>222</v>
       </c>
       <c r="I31" t="s">
         <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K31" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4032,28 +4828,31 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="D32" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="E32" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="F32" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G32" t="s">
-        <v>217</v>
+        <v>228</v>
+      </c>
+      <c r="H32" t="s">
+        <v>229</v>
       </c>
       <c r="I32" t="s">
         <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K32" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4064,28 +4863,31 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D33" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E33" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="F33" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="G33" t="s">
-        <v>223</v>
+        <v>235</v>
+      </c>
+      <c r="H33" t="s">
+        <v>236</v>
       </c>
       <c r="I33" t="s">
         <v>18</v>
       </c>
       <c r="J33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K33" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4096,13 +4898,31 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>238</v>
+      </c>
+      <c r="D34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E34" t="s">
+        <v>240</v>
+      </c>
+      <c r="F34" t="s">
+        <v>241</v>
+      </c>
+      <c r="G34" t="s">
+        <v>242</v>
+      </c>
+      <c r="H34" t="s">
+        <v>243</v>
       </c>
       <c r="I34" t="s">
         <v>18</v>
       </c>
       <c r="J34" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K34" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4113,13 +4933,31 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>245</v>
+      </c>
+      <c r="D35" t="s">
+        <v>245</v>
+      </c>
+      <c r="E35" t="s">
+        <v>246</v>
+      </c>
+      <c r="F35" t="s">
+        <v>247</v>
+      </c>
+      <c r="G35" t="s">
+        <v>248</v>
+      </c>
+      <c r="H35" t="s">
+        <v>249</v>
       </c>
       <c r="I35" t="s">
         <v>18</v>
       </c>
       <c r="J35" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K35" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4130,28 +4968,31 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="D36" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="E36" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="F36" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G36" t="s">
-        <v>231</v>
+        <v>255</v>
+      </c>
+      <c r="H36" t="s">
+        <v>256</v>
       </c>
       <c r="I36" t="s">
         <v>18</v>
       </c>
       <c r="J36" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K36" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4162,13 +5003,31 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>233</v>
+        <v>258</v>
+      </c>
+      <c r="D37" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" t="s">
+        <v>260</v>
+      </c>
+      <c r="F37" t="s">
+        <v>261</v>
+      </c>
+      <c r="G37" t="s">
+        <v>262</v>
+      </c>
+      <c r="H37" t="s">
+        <v>263</v>
       </c>
       <c r="I37" t="s">
         <v>18</v>
       </c>
       <c r="J37" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K37" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4179,28 +5038,31 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="D38" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="E38" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
       <c r="F38" t="s">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="G38" t="s">
-        <v>238</v>
+        <v>269</v>
+      </c>
+      <c r="H38" t="s">
+        <v>270</v>
       </c>
       <c r="I38" t="s">
         <v>18</v>
       </c>
       <c r="J38" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K38" t="s">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4211,13 +5073,31 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>240</v>
+        <v>272</v>
+      </c>
+      <c r="D39" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" t="s">
+        <v>274</v>
+      </c>
+      <c r="F39" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" t="s">
+        <v>276</v>
+      </c>
+      <c r="H39" t="s">
+        <v>277</v>
       </c>
       <c r="I39" t="s">
         <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K39" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4228,13 +5108,31 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>279</v>
+      </c>
+      <c r="D40" t="s">
+        <v>280</v>
+      </c>
+      <c r="E40" t="s">
+        <v>281</v>
+      </c>
+      <c r="F40" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" t="s">
+        <v>283</v>
+      </c>
+      <c r="H40" t="s">
+        <v>284</v>
       </c>
       <c r="I40" t="s">
         <v>18</v>
       </c>
       <c r="J40" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K40" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -4245,13 +5143,31 @@
         <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>242</v>
+        <v>286</v>
+      </c>
+      <c r="D41" t="s">
+        <v>287</v>
+      </c>
+      <c r="E41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F41" t="s">
+        <v>289</v>
+      </c>
+      <c r="G41" t="s">
+        <v>290</v>
+      </c>
+      <c r="H41" t="s">
+        <v>291</v>
       </c>
       <c r="I41" t="s">
         <v>18</v>
       </c>
       <c r="J41" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -4262,13 +5178,31 @@
         <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>243</v>
+        <v>293</v>
+      </c>
+      <c r="D42" t="s">
+        <v>294</v>
+      </c>
+      <c r="E42" t="s">
+        <v>295</v>
+      </c>
+      <c r="F42" t="s">
+        <v>296</v>
+      </c>
+      <c r="G42" t="s">
+        <v>297</v>
+      </c>
+      <c r="H42" t="s">
+        <v>298</v>
       </c>
       <c r="I42" t="s">
         <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K42" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -4279,13 +5213,31 @@
         <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>244</v>
+        <v>300</v>
+      </c>
+      <c r="D43" t="s">
+        <v>301</v>
+      </c>
+      <c r="E43" t="s">
+        <v>302</v>
+      </c>
+      <c r="F43" t="s">
+        <v>303</v>
+      </c>
+      <c r="G43" t="s">
+        <v>304</v>
+      </c>
+      <c r="H43" t="s">
+        <v>305</v>
       </c>
       <c r="I43" t="s">
         <v>18</v>
       </c>
       <c r="J43" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K43" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -4296,28 +5248,31 @@
         <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
       <c r="D44" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="E44" t="s">
-        <v>247</v>
+        <v>309</v>
       </c>
       <c r="F44" t="s">
-        <v>248</v>
+        <v>310</v>
       </c>
       <c r="G44" t="s">
-        <v>249</v>
+        <v>311</v>
+      </c>
+      <c r="H44" t="s">
+        <v>312</v>
       </c>
       <c r="I44" t="s">
         <v>18</v>
       </c>
       <c r="J44" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K44" t="s">
-        <v>250</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -4328,13 +5283,31 @@
         <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>251</v>
+        <v>314</v>
+      </c>
+      <c r="D45" t="s">
+        <v>315</v>
+      </c>
+      <c r="E45" t="s">
+        <v>316</v>
+      </c>
+      <c r="F45" t="s">
+        <v>317</v>
+      </c>
+      <c r="G45" t="s">
+        <v>318</v>
+      </c>
+      <c r="H45" t="s">
+        <v>319</v>
       </c>
       <c r="I45" t="s">
         <v>18</v>
       </c>
       <c r="J45" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K45" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -4345,13 +5318,31 @@
         <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>252</v>
+        <v>321</v>
+      </c>
+      <c r="D46" t="s">
+        <v>322</v>
+      </c>
+      <c r="E46" t="s">
+        <v>323</v>
+      </c>
+      <c r="F46" t="s">
+        <v>324</v>
+      </c>
+      <c r="G46" t="s">
+        <v>325</v>
+      </c>
+      <c r="H46" t="s">
+        <v>326</v>
       </c>
       <c r="I46" t="s">
         <v>18</v>
       </c>
       <c r="J46" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K46" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -4362,28 +5353,31 @@
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>253</v>
+        <v>328</v>
       </c>
       <c r="D47" t="s">
-        <v>254</v>
+        <v>329</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>330</v>
       </c>
       <c r="F47" t="s">
-        <v>256</v>
+        <v>331</v>
       </c>
       <c r="G47" t="s">
-        <v>257</v>
+        <v>332</v>
+      </c>
+      <c r="H47" t="s">
+        <v>333</v>
       </c>
       <c r="I47" t="s">
         <v>18</v>
       </c>
       <c r="J47" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K47" t="s">
-        <v>258</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -4394,31 +5388,31 @@
         <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="D48" t="s">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="F48" t="s">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="G48" t="s">
-        <v>263</v>
+        <v>339</v>
       </c>
       <c r="H48" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="I48" t="s">
         <v>18</v>
       </c>
       <c r="J48" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="K48" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -4429,13 +5423,31 @@
         <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>266</v>
+        <v>342</v>
+      </c>
+      <c r="D49" t="s">
+        <v>343</v>
+      </c>
+      <c r="E49" t="s">
+        <v>344</v>
+      </c>
+      <c r="F49" t="s">
+        <v>345</v>
+      </c>
+      <c r="G49" t="s">
+        <v>346</v>
+      </c>
+      <c r="H49" t="s">
+        <v>347</v>
       </c>
       <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="J49" t="s">
-        <v>211</v>
+        <v>215</v>
+      </c>
+      <c r="K49" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -4446,31 +5458,31 @@
         <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>349</v>
       </c>
       <c r="D50" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="E50" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
       <c r="F50" t="s">
-        <v>270</v>
+        <v>352</v>
       </c>
       <c r="G50" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="I50" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J50" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K50" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -4481,31 +5493,31 @@
         <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="D51" t="s">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="E51" t="s">
-        <v>278</v>
+        <v>360</v>
       </c>
       <c r="F51" t="s">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="G51" t="s">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c r="H51" t="s">
-        <v>281</v>
+        <v>363</v>
       </c>
       <c r="I51" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J51" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K51" t="s">
-        <v>282</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4516,31 +5528,31 @@
         <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>283</v>
+        <v>365</v>
       </c>
       <c r="D52" t="s">
-        <v>283</v>
+        <v>365</v>
       </c>
       <c r="E52" t="s">
-        <v>284</v>
+        <v>366</v>
       </c>
       <c r="F52" t="s">
-        <v>285</v>
+        <v>367</v>
       </c>
       <c r="G52" t="s">
-        <v>286</v>
+        <v>368</v>
       </c>
       <c r="H52" t="s">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="I52" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J52" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K52" t="s">
-        <v>288</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -4551,31 +5563,31 @@
         <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="D53" t="s">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="E53" t="s">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="F53" t="s">
-        <v>292</v>
+        <v>374</v>
       </c>
       <c r="G53" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="H53" t="s">
-        <v>294</v>
+        <v>376</v>
       </c>
       <c r="I53" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J53" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K53" t="s">
-        <v>295</v>
+        <v>377</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4586,31 +5598,31 @@
         <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>296</v>
+        <v>378</v>
       </c>
       <c r="D54" t="s">
-        <v>297</v>
+        <v>379</v>
       </c>
       <c r="E54" t="s">
-        <v>298</v>
+        <v>380</v>
       </c>
       <c r="F54" t="s">
-        <v>299</v>
+        <v>381</v>
       </c>
       <c r="G54" t="s">
-        <v>296</v>
+        <v>378</v>
       </c>
       <c r="H54" t="s">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="I54" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J54" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K54" t="s">
-        <v>301</v>
+        <v>383</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -4621,31 +5633,31 @@
         <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="D55" t="s">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="E55" t="s">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="F55" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="G55" t="s">
-        <v>306</v>
+        <v>388</v>
       </c>
       <c r="H55" t="s">
-        <v>307</v>
+        <v>389</v>
       </c>
       <c r="I55" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J55" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K55" t="s">
-        <v>308</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -4656,31 +5668,31 @@
         <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>309</v>
+        <v>391</v>
       </c>
       <c r="D56" t="s">
-        <v>310</v>
+        <v>392</v>
       </c>
       <c r="E56" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="F56" t="s">
-        <v>312</v>
+        <v>394</v>
       </c>
       <c r="G56" t="s">
-        <v>313</v>
+        <v>395</v>
       </c>
       <c r="H56" t="s">
-        <v>314</v>
+        <v>396</v>
       </c>
       <c r="I56" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J56" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="K56" t="s">
-        <v>315</v>
+        <v>397</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -4691,31 +5703,31 @@
         <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>316</v>
+        <v>398</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>399</v>
       </c>
       <c r="E57" t="s">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="F57" t="s">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="G57" t="s">
-        <v>320</v>
+        <v>402</v>
       </c>
       <c r="H57" t="s">
-        <v>321</v>
+        <v>403</v>
       </c>
       <c r="I57" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J57" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="K57" t="s">
-        <v>323</v>
+        <v>405</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -4726,31 +5738,31 @@
         <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>324</v>
+        <v>406</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="E58" t="s">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="F58" t="s">
-        <v>327</v>
+        <v>409</v>
       </c>
       <c r="G58" t="s">
-        <v>328</v>
+        <v>410</v>
       </c>
       <c r="H58" t="s">
-        <v>329</v>
+        <v>411</v>
       </c>
       <c r="I58" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J58" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="K58" t="s">
-        <v>330</v>
+        <v>412</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -4761,31 +5773,31 @@
         <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="D59" t="s">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="E59" t="s">
-        <v>332</v>
+        <v>414</v>
       </c>
       <c r="F59" t="s">
-        <v>333</v>
+        <v>415</v>
       </c>
       <c r="G59" t="s">
-        <v>334</v>
+        <v>416</v>
       </c>
       <c r="H59" t="s">
-        <v>335</v>
+        <v>417</v>
       </c>
       <c r="I59" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J59" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="K59" t="s">
-        <v>336</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -4796,31 +5808,31 @@
         <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>337</v>
+        <v>419</v>
       </c>
       <c r="D60" t="s">
-        <v>338</v>
+        <v>420</v>
       </c>
       <c r="E60" t="s">
-        <v>339</v>
+        <v>421</v>
       </c>
       <c r="F60" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="G60" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="H60" t="s">
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="I60" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J60" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="K60" t="s">
-        <v>343</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -4831,31 +5843,31 @@
         <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="D61" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="E61" t="s">
-        <v>345</v>
+        <v>427</v>
       </c>
       <c r="F61" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="G61" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="H61" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="I61" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J61" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="K61" t="s">
-        <v>349</v>
+        <v>431</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -4866,31 +5878,31 @@
         <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="D62" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="E62" t="s">
-        <v>352</v>
+        <v>434</v>
       </c>
       <c r="F62" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="G62" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="H62" t="s">
+        <v>437</v>
+      </c>
+      <c r="I62" t="s">
         <v>355</v>
       </c>
-      <c r="I62" t="s">
-        <v>273</v>
-      </c>
       <c r="J62" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K62" t="s">
-        <v>357</v>
+        <v>439</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -4901,31 +5913,31 @@
         <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="D63" t="s">
-        <v>359</v>
+        <v>441</v>
       </c>
       <c r="E63" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
       <c r="F63" t="s">
-        <v>361</v>
+        <v>443</v>
       </c>
       <c r="G63" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="H63" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="I63" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J63" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K63" t="s">
-        <v>364</v>
+        <v>446</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4936,31 +5948,31 @@
         <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>365</v>
+        <v>447</v>
       </c>
       <c r="D64" t="s">
-        <v>366</v>
+        <v>448</v>
       </c>
       <c r="E64" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="F64" t="s">
-        <v>368</v>
+        <v>450</v>
       </c>
       <c r="G64" t="s">
-        <v>369</v>
+        <v>451</v>
       </c>
       <c r="H64" t="s">
-        <v>370</v>
+        <v>452</v>
       </c>
       <c r="I64" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J64" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K64" t="s">
-        <v>371</v>
+        <v>453</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -4971,31 +5983,31 @@
         <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>372</v>
+        <v>454</v>
       </c>
       <c r="D65" t="s">
-        <v>373</v>
+        <v>455</v>
       </c>
       <c r="E65" t="s">
-        <v>374</v>
+        <v>456</v>
       </c>
       <c r="F65" t="s">
-        <v>375</v>
+        <v>457</v>
       </c>
       <c r="G65" t="s">
-        <v>376</v>
+        <v>458</v>
       </c>
       <c r="H65" t="s">
-        <v>377</v>
+        <v>459</v>
       </c>
       <c r="I65" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J65" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K65" t="s">
-        <v>378</v>
+        <v>460</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -5006,31 +6018,31 @@
         <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="D66" t="s">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="E66" t="s">
-        <v>381</v>
+        <v>463</v>
       </c>
       <c r="F66" t="s">
-        <v>382</v>
+        <v>464</v>
       </c>
       <c r="G66" t="s">
-        <v>383</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>384</v>
+        <v>465</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="I66" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J66" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K66" t="s">
-        <v>385</v>
+        <v>467</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -5041,31 +6053,31 @@
         <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>386</v>
+        <v>468</v>
       </c>
       <c r="D67" t="s">
-        <v>387</v>
+        <v>469</v>
       </c>
       <c r="E67" t="s">
-        <v>388</v>
+        <v>470</v>
       </c>
       <c r="F67" t="s">
-        <v>389</v>
+        <v>471</v>
       </c>
       <c r="G67" t="s">
-        <v>390</v>
+        <v>472</v>
       </c>
       <c r="H67" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="I67" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J67" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K67" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -5076,31 +6088,31 @@
         <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>393</v>
+        <v>475</v>
       </c>
       <c r="D68" t="s">
-        <v>393</v>
+        <v>475</v>
       </c>
       <c r="E68" t="s">
-        <v>394</v>
+        <v>476</v>
       </c>
       <c r="F68" t="s">
-        <v>395</v>
+        <v>477</v>
       </c>
       <c r="G68" t="s">
-        <v>396</v>
+        <v>478</v>
       </c>
       <c r="H68" t="s">
-        <v>397</v>
+        <v>479</v>
       </c>
       <c r="I68" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J68" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="K68" t="s">
-        <v>398</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -5111,31 +6123,31 @@
         <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>399</v>
+        <v>481</v>
       </c>
       <c r="D69" t="s">
-        <v>400</v>
+        <v>482</v>
       </c>
       <c r="E69" t="s">
-        <v>401</v>
+        <v>483</v>
       </c>
       <c r="F69" t="s">
-        <v>402</v>
+        <v>484</v>
       </c>
       <c r="G69" t="s">
-        <v>403</v>
+        <v>485</v>
       </c>
       <c r="H69" t="s">
-        <v>404</v>
+        <v>486</v>
       </c>
       <c r="I69" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J69" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K69" t="s">
-        <v>406</v>
+        <v>488</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -5146,31 +6158,31 @@
         <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>407</v>
+        <v>489</v>
       </c>
       <c r="D70" t="s">
-        <v>408</v>
+        <v>490</v>
       </c>
       <c r="E70" t="s">
-        <v>409</v>
+        <v>491</v>
       </c>
       <c r="F70" t="s">
-        <v>410</v>
+        <v>492</v>
       </c>
       <c r="G70" t="s">
-        <v>411</v>
+        <v>493</v>
       </c>
       <c r="H70" t="s">
-        <v>412</v>
+        <v>494</v>
       </c>
       <c r="I70" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J70" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K70" t="s">
-        <v>413</v>
+        <v>495</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -5181,31 +6193,31 @@
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="D71" t="s">
-        <v>415</v>
+        <v>497</v>
       </c>
       <c r="E71" t="s">
-        <v>416</v>
+        <v>498</v>
       </c>
       <c r="F71" t="s">
-        <v>417</v>
+        <v>499</v>
       </c>
       <c r="G71" t="s">
-        <v>418</v>
+        <v>500</v>
       </c>
       <c r="H71" t="s">
-        <v>419</v>
+        <v>501</v>
       </c>
       <c r="I71" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J71" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K71" t="s">
-        <v>420</v>
+        <v>502</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -5216,31 +6228,31 @@
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="D72" t="s">
-        <v>421</v>
+        <v>503</v>
       </c>
       <c r="E72" t="s">
-        <v>422</v>
+        <v>504</v>
       </c>
       <c r="F72" t="s">
-        <v>423</v>
+        <v>505</v>
       </c>
       <c r="G72" t="s">
-        <v>424</v>
+        <v>506</v>
       </c>
       <c r="H72" t="s">
-        <v>425</v>
+        <v>507</v>
       </c>
       <c r="I72" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J72" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K72" t="s">
-        <v>426</v>
+        <v>508</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -5251,31 +6263,31 @@
         <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>427</v>
+        <v>509</v>
       </c>
       <c r="D73" t="s">
-        <v>428</v>
+        <v>510</v>
       </c>
       <c r="E73" t="s">
-        <v>429</v>
+        <v>511</v>
       </c>
       <c r="F73" t="s">
-        <v>430</v>
+        <v>512</v>
       </c>
       <c r="G73" t="s">
-        <v>431</v>
+        <v>513</v>
       </c>
       <c r="H73" t="s">
-        <v>432</v>
+        <v>514</v>
       </c>
       <c r="I73" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J73" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K73" t="s">
-        <v>433</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -5286,31 +6298,31 @@
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>434</v>
+        <v>516</v>
       </c>
       <c r="D74" t="s">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="E74" t="s">
-        <v>436</v>
+        <v>518</v>
       </c>
       <c r="F74" t="s">
-        <v>437</v>
+        <v>519</v>
       </c>
       <c r="G74" t="s">
-        <v>438</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>439</v>
+        <v>520</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>521</v>
       </c>
       <c r="I74" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J74" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K74" t="s">
-        <v>440</v>
+        <v>522</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -5321,31 +6333,31 @@
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>441</v>
+        <v>523</v>
       </c>
       <c r="D75" t="s">
-        <v>441</v>
+        <v>523</v>
       </c>
       <c r="E75" t="s">
-        <v>442</v>
+        <v>524</v>
       </c>
       <c r="F75" t="s">
-        <v>443</v>
+        <v>525</v>
       </c>
       <c r="G75" t="s">
-        <v>444</v>
+        <v>526</v>
       </c>
       <c r="H75" t="s">
-        <v>445</v>
+        <v>527</v>
       </c>
       <c r="I75" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J75" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K75" t="s">
-        <v>446</v>
+        <v>528</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -5356,31 +6368,31 @@
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>447</v>
+        <v>529</v>
       </c>
       <c r="D76" t="s">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="E76" t="s">
-        <v>449</v>
+        <v>531</v>
       </c>
       <c r="F76" t="s">
-        <v>450</v>
+        <v>532</v>
       </c>
       <c r="G76" t="s">
-        <v>451</v>
+        <v>533</v>
       </c>
       <c r="H76" t="s">
-        <v>452</v>
+        <v>534</v>
       </c>
       <c r="I76" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J76" t="s">
-        <v>405</v>
+        <v>487</v>
       </c>
       <c r="K76" t="s">
-        <v>453</v>
+        <v>535</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -5391,13 +6403,31 @@
         <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>454</v>
+        <v>536</v>
+      </c>
+      <c r="D77" t="s">
+        <v>537</v>
+      </c>
+      <c r="E77" t="s">
+        <v>538</v>
+      </c>
+      <c r="F77" t="s">
+        <v>539</v>
+      </c>
+      <c r="G77" t="s">
+        <v>540</v>
+      </c>
+      <c r="H77" t="s">
+        <v>541</v>
       </c>
       <c r="I77" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J77" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K77" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -5408,13 +6438,31 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>456</v>
+        <v>544</v>
+      </c>
+      <c r="D78" t="s">
+        <v>545</v>
+      </c>
+      <c r="E78" t="s">
+        <v>546</v>
+      </c>
+      <c r="F78" t="s">
+        <v>547</v>
+      </c>
+      <c r="G78" t="s">
+        <v>548</v>
+      </c>
+      <c r="H78" t="s">
+        <v>549</v>
       </c>
       <c r="I78" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J78" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K78" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -5425,13 +6473,31 @@
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>457</v>
+        <v>551</v>
+      </c>
+      <c r="D79" t="s">
+        <v>551</v>
+      </c>
+      <c r="E79" t="s">
+        <v>552</v>
+      </c>
+      <c r="F79" t="s">
+        <v>553</v>
+      </c>
+      <c r="G79" t="s">
+        <v>554</v>
+      </c>
+      <c r="H79" t="s">
+        <v>555</v>
       </c>
       <c r="I79" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J79" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K79" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -5442,13 +6508,31 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>458</v>
+        <v>557</v>
+      </c>
+      <c r="D80" t="s">
+        <v>558</v>
+      </c>
+      <c r="E80" t="s">
+        <v>559</v>
+      </c>
+      <c r="F80" t="s">
+        <v>560</v>
+      </c>
+      <c r="G80" t="s">
+        <v>561</v>
+      </c>
+      <c r="H80" t="s">
+        <v>562</v>
       </c>
       <c r="I80" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J80" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K80" t="s">
+        <v>563</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -5459,13 +6543,31 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>459</v>
+        <v>564</v>
+      </c>
+      <c r="D81" t="s">
+        <v>565</v>
+      </c>
+      <c r="E81" t="s">
+        <v>566</v>
+      </c>
+      <c r="F81" t="s">
+        <v>567</v>
+      </c>
+      <c r="G81" t="s">
+        <v>568</v>
+      </c>
+      <c r="H81" t="s">
+        <v>569</v>
       </c>
       <c r="I81" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J81" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K81" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -5476,13 +6578,31 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>460</v>
+        <v>571</v>
+      </c>
+      <c r="D82" t="s">
+        <v>572</v>
+      </c>
+      <c r="E82" t="s">
+        <v>573</v>
+      </c>
+      <c r="F82" t="s">
+        <v>574</v>
+      </c>
+      <c r="G82" t="s">
+        <v>575</v>
+      </c>
+      <c r="H82" t="s">
+        <v>576</v>
       </c>
       <c r="I82" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J82" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K82" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -5493,28 +6613,31 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>461</v>
+        <v>578</v>
       </c>
       <c r="D83" t="s">
-        <v>462</v>
+        <v>579</v>
       </c>
       <c r="E83" t="s">
-        <v>463</v>
+        <v>580</v>
       </c>
       <c r="F83" t="s">
-        <v>464</v>
+        <v>581</v>
       </c>
       <c r="G83" t="s">
-        <v>465</v>
+        <v>582</v>
+      </c>
+      <c r="H83" t="s">
+        <v>583</v>
       </c>
       <c r="I83" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J83" t="s">
-        <v>455</v>
+        <v>542</v>
       </c>
       <c r="K83" t="s">
-        <v>466</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -5525,13 +6648,31 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>467</v>
+        <v>585</v>
+      </c>
+      <c r="D84" t="s">
+        <v>586</v>
+      </c>
+      <c r="E84" t="s">
+        <v>587</v>
+      </c>
+      <c r="F84" t="s">
+        <v>588</v>
+      </c>
+      <c r="G84" t="s">
+        <v>589</v>
+      </c>
+      <c r="H84" t="s">
+        <v>590</v>
       </c>
       <c r="I84" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J84" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K84" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -5542,13 +6683,31 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>468</v>
+        <v>592</v>
+      </c>
+      <c r="D85" t="s">
+        <v>593</v>
+      </c>
+      <c r="E85" t="s">
+        <v>594</v>
+      </c>
+      <c r="F85" t="s">
+        <v>595</v>
+      </c>
+      <c r="G85" t="s">
+        <v>596</v>
+      </c>
+      <c r="H85" t="s">
+        <v>597</v>
       </c>
       <c r="I85" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J85" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K85" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -5559,13 +6718,31 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>469</v>
+        <v>599</v>
+      </c>
+      <c r="D86" t="s">
+        <v>599</v>
+      </c>
+      <c r="E86" t="s">
+        <v>600</v>
+      </c>
+      <c r="F86" t="s">
+        <v>601</v>
+      </c>
+      <c r="G86" t="s">
+        <v>602</v>
+      </c>
+      <c r="H86" t="s">
+        <v>603</v>
       </c>
       <c r="I86" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J86" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K86" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -5576,13 +6753,31 @@
         <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>470</v>
+        <v>605</v>
+      </c>
+      <c r="D87" t="s">
+        <v>606</v>
+      </c>
+      <c r="E87" t="s">
+        <v>607</v>
+      </c>
+      <c r="F87" t="s">
+        <v>608</v>
+      </c>
+      <c r="G87" t="s">
+        <v>609</v>
+      </c>
+      <c r="H87" t="s">
+        <v>610</v>
       </c>
       <c r="I87" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J87" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K87" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -5593,13 +6788,31 @@
         <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>471</v>
+        <v>612</v>
+      </c>
+      <c r="D88" t="s">
+        <v>612</v>
+      </c>
+      <c r="E88" t="s">
+        <v>613</v>
+      </c>
+      <c r="F88" t="s">
+        <v>614</v>
+      </c>
+      <c r="G88" t="s">
+        <v>615</v>
+      </c>
+      <c r="H88" t="s">
+        <v>616</v>
       </c>
       <c r="I88" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J88" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K88" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -5610,13 +6823,31 @@
         <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>472</v>
+        <v>618</v>
+      </c>
+      <c r="D89" t="s">
+        <v>619</v>
+      </c>
+      <c r="E89" t="s">
+        <v>620</v>
+      </c>
+      <c r="F89" t="s">
+        <v>621</v>
+      </c>
+      <c r="G89" t="s">
+        <v>622</v>
+      </c>
+      <c r="H89" t="s">
+        <v>623</v>
       </c>
       <c r="I89" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J89" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K89" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -5627,13 +6858,31 @@
         <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>473</v>
+        <v>625</v>
+      </c>
+      <c r="D90" t="s">
+        <v>626</v>
+      </c>
+      <c r="E90" t="s">
+        <v>627</v>
+      </c>
+      <c r="F90" t="s">
+        <v>628</v>
+      </c>
+      <c r="G90" t="s">
+        <v>629</v>
+      </c>
+      <c r="H90" t="s">
+        <v>630</v>
       </c>
       <c r="I90" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J90" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K90" t="s">
+        <v>631</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -5644,13 +6893,31 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>474</v>
+        <v>632</v>
+      </c>
+      <c r="D91" t="s">
+        <v>633</v>
+      </c>
+      <c r="E91" t="s">
+        <v>634</v>
+      </c>
+      <c r="F91" t="s">
+        <v>635</v>
+      </c>
+      <c r="G91" t="s">
+        <v>636</v>
+      </c>
+      <c r="H91" t="s">
+        <v>637</v>
       </c>
       <c r="I91" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J91" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K91" t="s">
+        <v>638</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -5661,13 +6928,31 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>475</v>
+        <v>639</v>
+      </c>
+      <c r="D92" t="s">
+        <v>640</v>
+      </c>
+      <c r="E92" t="s">
+        <v>641</v>
+      </c>
+      <c r="F92" t="s">
+        <v>642</v>
+      </c>
+      <c r="G92" t="s">
+        <v>643</v>
+      </c>
+      <c r="H92" t="s">
+        <v>644</v>
       </c>
       <c r="I92" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J92" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K92" t="s">
+        <v>645</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -5678,13 +6963,31 @@
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>476</v>
+        <v>646</v>
+      </c>
+      <c r="D93" t="s">
+        <v>647</v>
+      </c>
+      <c r="E93" t="s">
+        <v>648</v>
+      </c>
+      <c r="F93" t="s">
+        <v>649</v>
+      </c>
+      <c r="G93" t="s">
+        <v>650</v>
+      </c>
+      <c r="H93" t="s">
+        <v>651</v>
       </c>
       <c r="I93" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="J93" t="s">
-        <v>455</v>
+        <v>542</v>
+      </c>
+      <c r="K93" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -5695,31 +6998,31 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>477</v>
+        <v>653</v>
       </c>
       <c r="D94" t="s">
-        <v>477</v>
+        <v>653</v>
       </c>
       <c r="E94" t="s">
-        <v>478</v>
+        <v>654</v>
       </c>
       <c r="F94" t="s">
-        <v>479</v>
+        <v>655</v>
       </c>
       <c r="G94" t="s">
-        <v>480</v>
+        <v>656</v>
       </c>
       <c r="H94" t="s">
-        <v>481</v>
+        <v>657</v>
       </c>
       <c r="I94" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J94" t="s">
-        <v>483</v>
+        <v>659</v>
       </c>
       <c r="K94" t="s">
-        <v>484</v>
+        <v>660</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -5730,31 +7033,31 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>485</v>
+        <v>661</v>
       </c>
       <c r="D95" t="s">
-        <v>486</v>
+        <v>662</v>
       </c>
       <c r="E95" t="s">
-        <v>487</v>
+        <v>663</v>
       </c>
       <c r="F95" t="s">
-        <v>488</v>
+        <v>664</v>
       </c>
       <c r="G95" t="s">
-        <v>489</v>
+        <v>665</v>
       </c>
       <c r="H95" t="s">
-        <v>490</v>
+        <v>666</v>
       </c>
       <c r="I95" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J95" t="s">
-        <v>483</v>
+        <v>659</v>
       </c>
       <c r="K95" t="s">
-        <v>491</v>
+        <v>667</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -5765,31 +7068,31 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>492</v>
+        <v>668</v>
       </c>
       <c r="D96" t="s">
-        <v>493</v>
+        <v>669</v>
       </c>
       <c r="E96" t="s">
-        <v>494</v>
+        <v>670</v>
       </c>
       <c r="F96" t="s">
-        <v>495</v>
+        <v>671</v>
       </c>
       <c r="G96" t="s">
-        <v>496</v>
+        <v>672</v>
       </c>
       <c r="H96" t="s">
-        <v>497</v>
+        <v>673</v>
       </c>
       <c r="I96" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J96" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K96" t="s">
-        <v>499</v>
+        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -5800,31 +7103,31 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>500</v>
+        <v>676</v>
       </c>
       <c r="D97" t="s">
-        <v>500</v>
+        <v>676</v>
       </c>
       <c r="E97" t="s">
-        <v>501</v>
+        <v>677</v>
       </c>
       <c r="F97" t="s">
-        <v>502</v>
+        <v>678</v>
       </c>
       <c r="G97" t="s">
-        <v>503</v>
+        <v>679</v>
       </c>
       <c r="H97" t="s">
-        <v>504</v>
+        <v>680</v>
       </c>
       <c r="I97" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J97" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K97" t="s">
-        <v>505</v>
+        <v>681</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -5835,31 +7138,31 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>506</v>
+        <v>682</v>
       </c>
       <c r="D98" t="s">
-        <v>507</v>
+        <v>683</v>
       </c>
       <c r="E98" t="s">
-        <v>508</v>
+        <v>684</v>
       </c>
       <c r="F98" t="s">
-        <v>509</v>
+        <v>685</v>
       </c>
       <c r="G98" t="s">
-        <v>510</v>
+        <v>686</v>
       </c>
       <c r="H98" t="s">
-        <v>511</v>
+        <v>687</v>
       </c>
       <c r="I98" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J98" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K98" t="s">
-        <v>512</v>
+        <v>688</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -5870,31 +7173,31 @@
         <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>513</v>
+        <v>689</v>
       </c>
       <c r="D99" t="s">
-        <v>514</v>
+        <v>690</v>
       </c>
       <c r="E99" t="s">
-        <v>515</v>
+        <v>691</v>
       </c>
       <c r="F99" t="s">
-        <v>516</v>
+        <v>692</v>
       </c>
       <c r="G99" t="s">
-        <v>517</v>
+        <v>693</v>
       </c>
       <c r="H99" t="s">
-        <v>518</v>
+        <v>694</v>
       </c>
       <c r="I99" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J99" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K99" t="s">
-        <v>519</v>
+        <v>695</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -5905,31 +7208,31 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>520</v>
+        <v>696</v>
       </c>
       <c r="D100" t="s">
-        <v>520</v>
+        <v>696</v>
       </c>
       <c r="E100" t="s">
-        <v>521</v>
+        <v>697</v>
       </c>
       <c r="F100" t="s">
-        <v>522</v>
+        <v>698</v>
       </c>
       <c r="G100" t="s">
-        <v>523</v>
+        <v>699</v>
       </c>
       <c r="H100" t="s">
-        <v>524</v>
+        <v>700</v>
       </c>
       <c r="I100" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J100" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K100" t="s">
-        <v>525</v>
+        <v>701</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -5940,31 +7243,31 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>526</v>
+        <v>702</v>
       </c>
       <c r="D101" t="s">
-        <v>527</v>
+        <v>703</v>
       </c>
       <c r="E101" t="s">
-        <v>528</v>
+        <v>704</v>
       </c>
       <c r="F101" t="s">
-        <v>529</v>
+        <v>705</v>
       </c>
       <c r="G101" t="s">
-        <v>530</v>
+        <v>706</v>
       </c>
       <c r="H101" t="s">
-        <v>531</v>
+        <v>707</v>
       </c>
       <c r="I101" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J101" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K101" t="s">
-        <v>532</v>
+        <v>708</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -5975,31 +7278,31 @@
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>533</v>
+        <v>709</v>
       </c>
       <c r="D102" t="s">
-        <v>533</v>
+        <v>709</v>
       </c>
       <c r="E102" t="s">
-        <v>534</v>
+        <v>710</v>
       </c>
       <c r="F102" t="s">
-        <v>535</v>
+        <v>711</v>
       </c>
       <c r="G102" t="s">
-        <v>536</v>
+        <v>712</v>
       </c>
       <c r="H102" t="s">
-        <v>537</v>
+        <v>713</v>
       </c>
       <c r="I102" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J102" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K102" t="s">
-        <v>538</v>
+        <v>714</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -6010,31 +7313,31 @@
         <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>539</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>541</v>
+        <v>715</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>717</v>
       </c>
       <c r="F103" t="s">
-        <v>542</v>
+        <v>718</v>
       </c>
       <c r="G103" t="s">
-        <v>543</v>
+        <v>719</v>
       </c>
       <c r="H103" t="s">
-        <v>544</v>
+        <v>720</v>
       </c>
       <c r="I103" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J103" t="s">
-        <v>498</v>
+        <v>674</v>
       </c>
       <c r="K103" t="s">
-        <v>545</v>
+        <v>721</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -6045,13 +7348,31 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>546</v>
+        <v>722</v>
+      </c>
+      <c r="D104" t="s">
+        <v>722</v>
+      </c>
+      <c r="E104" t="s">
+        <v>723</v>
+      </c>
+      <c r="F104" t="s">
+        <v>724</v>
+      </c>
+      <c r="G104" t="s">
+        <v>725</v>
+      </c>
+      <c r="H104" t="s">
+        <v>726</v>
       </c>
       <c r="I104" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J104" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K104" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -6062,13 +7383,31 @@
         <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>548</v>
+        <v>729</v>
+      </c>
+      <c r="D105" t="s">
+        <v>730</v>
+      </c>
+      <c r="E105" t="s">
+        <v>731</v>
+      </c>
+      <c r="F105" t="s">
+        <v>732</v>
+      </c>
+      <c r="G105" t="s">
+        <v>733</v>
+      </c>
+      <c r="H105" t="s">
+        <v>734</v>
       </c>
       <c r="I105" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J105" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K105" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -6079,13 +7418,31 @@
         <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>549</v>
+        <v>736</v>
+      </c>
+      <c r="D106" t="s">
+        <v>736</v>
+      </c>
+      <c r="E106" t="s">
+        <v>737</v>
+      </c>
+      <c r="F106" t="s">
+        <v>738</v>
+      </c>
+      <c r="G106" t="s">
+        <v>739</v>
+      </c>
+      <c r="H106" t="s">
+        <v>740</v>
       </c>
       <c r="I106" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J106" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K106" t="s">
+        <v>741</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -6096,13 +7453,31 @@
         <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>550</v>
+        <v>742</v>
+      </c>
+      <c r="D107" t="s">
+        <v>743</v>
+      </c>
+      <c r="E107" t="s">
+        <v>744</v>
+      </c>
+      <c r="F107" t="s">
+        <v>745</v>
+      </c>
+      <c r="G107" t="s">
+        <v>746</v>
+      </c>
+      <c r="H107" t="s">
+        <v>747</v>
       </c>
       <c r="I107" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J107" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K107" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -6113,13 +7488,31 @@
         <v>11</v>
       </c>
       <c r="C108" t="s">
-        <v>551</v>
+        <v>749</v>
+      </c>
+      <c r="D108" t="s">
+        <v>750</v>
+      </c>
+      <c r="E108" t="s">
+        <v>751</v>
+      </c>
+      <c r="F108" t="s">
+        <v>752</v>
+      </c>
+      <c r="G108" t="s">
+        <v>753</v>
+      </c>
+      <c r="H108" t="s">
+        <v>754</v>
       </c>
       <c r="I108" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J108" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K108" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -6130,13 +7523,31 @@
         <v>11</v>
       </c>
       <c r="C109" t="s">
-        <v>552</v>
+        <v>756</v>
+      </c>
+      <c r="D109" t="s">
+        <v>757</v>
+      </c>
+      <c r="E109" t="s">
+        <v>758</v>
+      </c>
+      <c r="F109" t="s">
+        <v>759</v>
+      </c>
+      <c r="G109" t="s">
+        <v>760</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>761</v>
       </c>
       <c r="I109" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J109" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K109" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -6147,13 +7558,31 @@
         <v>11</v>
       </c>
       <c r="C110" t="s">
-        <v>553</v>
+        <v>763</v>
+      </c>
+      <c r="D110" t="s">
+        <v>763</v>
+      </c>
+      <c r="E110" t="s">
+        <v>764</v>
+      </c>
+      <c r="F110" t="s">
+        <v>765</v>
+      </c>
+      <c r="G110" t="s">
+        <v>766</v>
+      </c>
+      <c r="H110" t="s">
+        <v>767</v>
       </c>
       <c r="I110" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J110" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K110" t="s">
+        <v>768</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -6164,13 +7593,31 @@
         <v>11</v>
       </c>
       <c r="C111" t="s">
-        <v>554</v>
+        <v>769</v>
+      </c>
+      <c r="D111" t="s">
+        <v>770</v>
+      </c>
+      <c r="E111" t="s">
+        <v>771</v>
+      </c>
+      <c r="F111" t="s">
+        <v>772</v>
+      </c>
+      <c r="G111" t="s">
+        <v>773</v>
+      </c>
+      <c r="H111" t="s">
+        <v>774</v>
       </c>
       <c r="I111" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J111" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K111" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -6181,13 +7628,31 @@
         <v>11</v>
       </c>
       <c r="C112" t="s">
-        <v>555</v>
+        <v>776</v>
+      </c>
+      <c r="D112" t="s">
+        <v>776</v>
+      </c>
+      <c r="E112" t="s">
+        <v>777</v>
+      </c>
+      <c r="F112" t="s">
+        <v>778</v>
+      </c>
+      <c r="G112" t="s">
+        <v>779</v>
+      </c>
+      <c r="H112" t="s">
+        <v>780</v>
       </c>
       <c r="I112" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J112" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K112" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -6198,13 +7663,31 @@
         <v>11</v>
       </c>
       <c r="C113" t="s">
-        <v>556</v>
+        <v>782</v>
+      </c>
+      <c r="D113" t="s">
+        <v>783</v>
+      </c>
+      <c r="E113" t="s">
+        <v>784</v>
+      </c>
+      <c r="F113" t="s">
+        <v>785</v>
+      </c>
+      <c r="G113" t="s">
+        <v>786</v>
+      </c>
+      <c r="H113" t="s">
+        <v>787</v>
       </c>
       <c r="I113" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J113" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K113" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -6215,13 +7698,31 @@
         <v>11</v>
       </c>
       <c r="C114" t="s">
-        <v>557</v>
+        <v>789</v>
+      </c>
+      <c r="D114" t="s">
+        <v>789</v>
+      </c>
+      <c r="E114" t="s">
+        <v>790</v>
+      </c>
+      <c r="F114" t="s">
+        <v>791</v>
+      </c>
+      <c r="G114" t="s">
+        <v>792</v>
+      </c>
+      <c r="H114" t="s">
+        <v>793</v>
       </c>
       <c r="I114" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J114" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K114" t="s">
+        <v>794</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -6232,13 +7733,31 @@
         <v>11</v>
       </c>
       <c r="C115" t="s">
-        <v>558</v>
+        <v>795</v>
+      </c>
+      <c r="D115" t="s">
+        <v>795</v>
+      </c>
+      <c r="E115" t="s">
+        <v>796</v>
+      </c>
+      <c r="F115" t="s">
+        <v>797</v>
+      </c>
+      <c r="G115" t="s">
+        <v>798</v>
+      </c>
+      <c r="H115" t="s">
+        <v>799</v>
       </c>
       <c r="I115" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J115" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K115" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -6249,13 +7768,31 @@
         <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>559</v>
+        <v>801</v>
+      </c>
+      <c r="D116" t="s">
+        <v>802</v>
+      </c>
+      <c r="E116" t="s">
+        <v>803</v>
+      </c>
+      <c r="F116" t="s">
+        <v>804</v>
+      </c>
+      <c r="G116" t="s">
+        <v>805</v>
+      </c>
+      <c r="H116" t="s">
+        <v>806</v>
       </c>
       <c r="I116" t="s">
-        <v>482</v>
+        <v>658</v>
       </c>
       <c r="J116" t="s">
-        <v>547</v>
+        <v>727</v>
+      </c>
+      <c r="K116" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -6266,28 +7803,31 @@
         <v>11</v>
       </c>
       <c r="C117" t="s">
-        <v>560</v>
+        <v>808</v>
       </c>
       <c r="D117" t="s">
-        <v>560</v>
+        <v>808</v>
       </c>
       <c r="E117" t="s">
-        <v>561</v>
+        <v>809</v>
       </c>
       <c r="F117" t="s">
-        <v>562</v>
+        <v>810</v>
       </c>
       <c r="G117" t="s">
-        <v>563</v>
+        <v>811</v>
+      </c>
+      <c r="H117" t="s">
+        <v>812</v>
       </c>
       <c r="I117" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J117" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
       <c r="K117" t="s">
-        <v>566</v>
+        <v>815</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -6298,13 +7838,13 @@
         <v>11</v>
       </c>
       <c r="C118" t="s">
-        <v>567</v>
+        <v>816</v>
       </c>
       <c r="I118" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J118" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -6315,28 +7855,31 @@
         <v>11</v>
       </c>
       <c r="C119" t="s">
-        <v>568</v>
+        <v>817</v>
       </c>
       <c r="D119" t="s">
-        <v>569</v>
+        <v>818</v>
       </c>
       <c r="E119" t="s">
-        <v>570</v>
+        <v>819</v>
       </c>
       <c r="F119" t="s">
-        <v>571</v>
+        <v>820</v>
       </c>
       <c r="G119" t="s">
-        <v>572</v>
+        <v>821</v>
+      </c>
+      <c r="H119" t="s">
+        <v>822</v>
       </c>
       <c r="I119" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J119" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
       <c r="K119" t="s">
-        <v>573</v>
+        <v>823</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -6347,13 +7890,13 @@
         <v>11</v>
       </c>
       <c r="C120" t="s">
-        <v>574</v>
+        <v>824</v>
       </c>
       <c r="I120" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J120" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -6364,13 +7907,13 @@
         <v>11</v>
       </c>
       <c r="C121" t="s">
-        <v>575</v>
+        <v>825</v>
       </c>
       <c r="I121" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J121" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -6381,13 +7924,13 @@
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>576</v>
+        <v>826</v>
       </c>
       <c r="I122" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J122" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -6398,13 +7941,13 @@
         <v>11</v>
       </c>
       <c r="C123" t="s">
-        <v>577</v>
+        <v>827</v>
       </c>
       <c r="I123" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J123" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -6415,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="C124" t="s">
-        <v>578</v>
+        <v>828</v>
       </c>
       <c r="I124" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J124" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -6432,13 +7975,13 @@
         <v>11</v>
       </c>
       <c r="C125" t="s">
-        <v>579</v>
+        <v>829</v>
       </c>
       <c r="I125" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J125" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -6449,13 +7992,13 @@
         <v>11</v>
       </c>
       <c r="C126" t="s">
-        <v>580</v>
+        <v>830</v>
       </c>
       <c r="I126" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J126" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -6466,13 +8009,13 @@
         <v>11</v>
       </c>
       <c r="C127" t="s">
-        <v>581</v>
+        <v>831</v>
       </c>
       <c r="I127" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J127" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -6483,13 +8026,13 @@
         <v>11</v>
       </c>
       <c r="C128" t="s">
-        <v>582</v>
+        <v>832</v>
       </c>
       <c r="I128" t="s">
-        <v>564</v>
+        <v>813</v>
       </c>
       <c r="J128" t="s">
-        <v>565</v>
+        <v>814</v>
       </c>
     </row>
     <row r="129" spans="1:10">
@@ -6500,25 +8043,25 @@
         <v>11</v>
       </c>
       <c r="C129" t="s">
-        <v>583</v>
+        <v>833</v>
       </c>
       <c r="D129" t="s">
-        <v>584</v>
+        <v>834</v>
       </c>
       <c r="E129" t="s">
-        <v>585</v>
+        <v>835</v>
       </c>
       <c r="F129" t="s">
-        <v>586</v>
+        <v>836</v>
       </c>
       <c r="G129" t="s">
-        <v>587</v>
+        <v>837</v>
       </c>
       <c r="I129" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J129" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="130" spans="1:10">
@@ -6529,13 +8072,13 @@
         <v>11</v>
       </c>
       <c r="C130" t="s">
-        <v>589</v>
+        <v>839</v>
       </c>
       <c r="I130" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J130" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="131" spans="1:10">
@@ -6546,13 +8089,13 @@
         <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>590</v>
+        <v>840</v>
       </c>
       <c r="I131" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J131" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="132" spans="1:10">
@@ -6563,13 +8106,13 @@
         <v>11</v>
       </c>
       <c r="C132" t="s">
-        <v>591</v>
+        <v>841</v>
       </c>
       <c r="I132" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J132" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="133" spans="1:10">
@@ -6580,13 +8123,13 @@
         <v>11</v>
       </c>
       <c r="C133" t="s">
-        <v>592</v>
+        <v>842</v>
       </c>
       <c r="I133" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J133" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="134" spans="1:10">
@@ -6597,13 +8140,13 @@
         <v>11</v>
       </c>
       <c r="C134" t="s">
-        <v>593</v>
+        <v>843</v>
       </c>
       <c r="I134" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J134" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="135" spans="1:10">
@@ -6614,13 +8157,13 @@
         <v>11</v>
       </c>
       <c r="C135" t="s">
-        <v>594</v>
+        <v>844</v>
       </c>
       <c r="I135" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J135" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="136" spans="1:10">
@@ -6631,13 +8174,13 @@
         <v>11</v>
       </c>
       <c r="C136" t="s">
-        <v>595</v>
+        <v>845</v>
       </c>
       <c r="I136" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J136" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="137" spans="1:10">
@@ -6648,13 +8191,13 @@
         <v>11</v>
       </c>
       <c r="C137" t="s">
-        <v>596</v>
+        <v>846</v>
       </c>
       <c r="I137" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J137" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="138" spans="1:10">
@@ -6665,13 +8208,13 @@
         <v>11</v>
       </c>
       <c r="C138" t="s">
-        <v>597</v>
+        <v>847</v>
       </c>
       <c r="I138" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J138" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="139" spans="1:10">
@@ -6682,13 +8225,13 @@
         <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>598</v>
+        <v>848</v>
       </c>
       <c r="I139" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J139" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="140" spans="1:10">
@@ -6699,13 +8242,13 @@
         <v>11</v>
       </c>
       <c r="C140" t="s">
-        <v>599</v>
+        <v>849</v>
       </c>
       <c r="I140" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J140" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="141" spans="1:10">
@@ -6716,13 +8259,13 @@
         <v>11</v>
       </c>
       <c r="C141" t="s">
-        <v>600</v>
+        <v>850</v>
       </c>
       <c r="I141" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J141" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="142" spans="1:10">
@@ -6733,13 +8276,13 @@
         <v>11</v>
       </c>
       <c r="C142" t="s">
-        <v>601</v>
+        <v>851</v>
       </c>
       <c r="I142" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J142" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="143" spans="1:10">
@@ -6750,13 +8293,13 @@
         <v>11</v>
       </c>
       <c r="C143" t="s">
-        <v>602</v>
+        <v>852</v>
       </c>
       <c r="I143" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J143" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="144" spans="1:10">
@@ -6767,13 +8310,13 @@
         <v>11</v>
       </c>
       <c r="C144" t="s">
-        <v>603</v>
+        <v>853</v>
       </c>
       <c r="I144" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
       <c r="J144" t="s">
-        <v>588</v>
+        <v>838</v>
       </c>
     </row>
     <row r="145" spans="1:10">
@@ -6784,13 +8327,13 @@
         <v>11</v>
       </c>
       <c r="C145" t="s">
-        <v>604</v>
+        <v>854</v>
       </c>
       <c r="I145" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J145" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="146" spans="1:10">
@@ -6801,13 +8344,13 @@
         <v>11</v>
       </c>
       <c r="C146" t="s">
-        <v>607</v>
+        <v>857</v>
       </c>
       <c r="I146" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J146" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="147" spans="1:10">
@@ -6818,13 +8361,13 @@
         <v>11</v>
       </c>
       <c r="C147" t="s">
-        <v>608</v>
+        <v>858</v>
       </c>
       <c r="I147" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J147" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="148" spans="1:10">
@@ -6835,13 +8378,13 @@
         <v>11</v>
       </c>
       <c r="C148" t="s">
-        <v>609</v>
+        <v>859</v>
       </c>
       <c r="I148" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J148" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="149" spans="1:10">
@@ -6852,13 +8395,13 @@
         <v>11</v>
       </c>
       <c r="C149" t="s">
-        <v>610</v>
+        <v>860</v>
       </c>
       <c r="I149" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J149" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="150" spans="1:10">
@@ -6869,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>611</v>
+        <v>861</v>
       </c>
       <c r="I150" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J150" t="s">
-        <v>606</v>
+        <v>856</v>
       </c>
     </row>
     <row r="151" spans="1:10">
@@ -6886,13 +8429,13 @@
         <v>11</v>
       </c>
       <c r="C151" t="s">
-        <v>612</v>
+        <v>862</v>
       </c>
       <c r="I151" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J151" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="152" spans="1:10">
@@ -6903,13 +8446,13 @@
         <v>11</v>
       </c>
       <c r="C152" t="s">
-        <v>614</v>
+        <v>864</v>
       </c>
       <c r="I152" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J152" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="153" spans="1:10">
@@ -6920,13 +8463,13 @@
         <v>11</v>
       </c>
       <c r="C153" t="s">
-        <v>615</v>
+        <v>865</v>
       </c>
       <c r="I153" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J153" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="154" spans="1:10">
@@ -6937,13 +8480,13 @@
         <v>11</v>
       </c>
       <c r="C154" t="s">
-        <v>616</v>
+        <v>866</v>
       </c>
       <c r="I154" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J154" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="155" spans="1:10">
@@ -6954,13 +8497,13 @@
         <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>617</v>
+        <v>867</v>
       </c>
       <c r="I155" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J155" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="156" spans="1:10">
@@ -6971,13 +8514,13 @@
         <v>11</v>
       </c>
       <c r="C156" t="s">
-        <v>618</v>
+        <v>868</v>
       </c>
       <c r="I156" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J156" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="157" spans="1:10">
@@ -6988,13 +8531,13 @@
         <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>619</v>
+        <v>869</v>
       </c>
       <c r="I157" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J157" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="158" spans="1:10">
@@ -7005,13 +8548,13 @@
         <v>11</v>
       </c>
       <c r="C158" t="s">
-        <v>620</v>
+        <v>870</v>
       </c>
       <c r="I158" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J158" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="159" spans="1:10">
@@ -7022,13 +8565,13 @@
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>621</v>
+        <v>871</v>
       </c>
       <c r="I159" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J159" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="160" spans="1:10">
@@ -7039,13 +8582,13 @@
         <v>11</v>
       </c>
       <c r="C160" t="s">
-        <v>622</v>
+        <v>872</v>
       </c>
       <c r="I160" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J160" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="161" spans="1:10">
@@ -7056,13 +8599,13 @@
         <v>11</v>
       </c>
       <c r="C161" t="s">
-        <v>623</v>
+        <v>873</v>
       </c>
       <c r="I161" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J161" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="162" spans="1:10">
@@ -7073,13 +8616,13 @@
         <v>11</v>
       </c>
       <c r="C162" t="s">
-        <v>624</v>
+        <v>874</v>
       </c>
       <c r="I162" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J162" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="163" spans="1:10">
@@ -7090,13 +8633,13 @@
         <v>11</v>
       </c>
       <c r="C163" t="s">
-        <v>625</v>
+        <v>875</v>
       </c>
       <c r="I163" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J163" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="164" spans="1:10">
@@ -7107,13 +8650,13 @@
         <v>11</v>
       </c>
       <c r="C164" t="s">
-        <v>626</v>
+        <v>876</v>
       </c>
       <c r="I164" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J164" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="165" spans="1:10">
@@ -7124,13 +8667,13 @@
         <v>11</v>
       </c>
       <c r="C165" t="s">
-        <v>627</v>
+        <v>877</v>
       </c>
       <c r="I165" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J165" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="166" spans="1:10">
@@ -7141,13 +8684,13 @@
         <v>11</v>
       </c>
       <c r="C166" t="s">
-        <v>628</v>
+        <v>878</v>
       </c>
       <c r="I166" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J166" t="s">
-        <v>613</v>
+        <v>863</v>
       </c>
     </row>
     <row r="167" spans="1:10">
@@ -7158,13 +8701,13 @@
         <v>11</v>
       </c>
       <c r="C167" t="s">
-        <v>629</v>
+        <v>879</v>
       </c>
       <c r="I167" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J167" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="168" spans="1:10">
@@ -7175,13 +8718,13 @@
         <v>11</v>
       </c>
       <c r="C168" t="s">
-        <v>631</v>
+        <v>881</v>
       </c>
       <c r="I168" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J168" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="169" spans="1:10">
@@ -7192,13 +8735,13 @@
         <v>11</v>
       </c>
       <c r="C169" t="s">
-        <v>632</v>
+        <v>882</v>
       </c>
       <c r="I169" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J169" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="170" spans="1:10">
@@ -7209,13 +8752,13 @@
         <v>11</v>
       </c>
       <c r="C170" t="s">
-        <v>633</v>
+        <v>883</v>
       </c>
       <c r="I170" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J170" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="171" spans="1:10">
@@ -7226,13 +8769,13 @@
         <v>11</v>
       </c>
       <c r="C171" t="s">
-        <v>634</v>
+        <v>884</v>
       </c>
       <c r="I171" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J171" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="172" spans="1:10">
@@ -7243,13 +8786,13 @@
         <v>11</v>
       </c>
       <c r="C172" t="s">
-        <v>635</v>
+        <v>885</v>
       </c>
       <c r="I172" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J172" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="173" spans="1:10">
@@ -7260,13 +8803,13 @@
         <v>11</v>
       </c>
       <c r="C173" t="s">
-        <v>636</v>
+        <v>886</v>
       </c>
       <c r="I173" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J173" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="174" spans="1:10">
@@ -7277,13 +8820,13 @@
         <v>11</v>
       </c>
       <c r="C174" t="s">
-        <v>637</v>
+        <v>887</v>
       </c>
       <c r="I174" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J174" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="175" spans="1:10">
@@ -7294,13 +8837,13 @@
         <v>11</v>
       </c>
       <c r="C175" t="s">
-        <v>638</v>
+        <v>888</v>
       </c>
       <c r="I175" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J175" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="176" spans="1:10">
@@ -7311,13 +8854,13 @@
         <v>11</v>
       </c>
       <c r="C176" t="s">
-        <v>639</v>
+        <v>889</v>
       </c>
       <c r="I176" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J176" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="177" spans="1:10">
@@ -7328,13 +8871,13 @@
         <v>11</v>
       </c>
       <c r="C177" t="s">
-        <v>640</v>
+        <v>890</v>
       </c>
       <c r="I177" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J177" t="s">
-        <v>630</v>
+        <v>880</v>
       </c>
     </row>
     <row r="178" spans="1:10">
@@ -7345,13 +8888,13 @@
         <v>11</v>
       </c>
       <c r="C178" t="s">
-        <v>641</v>
+        <v>891</v>
       </c>
       <c r="I178" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J178" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="179" spans="1:10">
@@ -7362,13 +8905,13 @@
         <v>11</v>
       </c>
       <c r="C179" t="s">
-        <v>643</v>
+        <v>893</v>
       </c>
       <c r="I179" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J179" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="180" spans="1:10">
@@ -7379,13 +8922,13 @@
         <v>11</v>
       </c>
       <c r="C180" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
       <c r="I180" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J180" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="181" spans="1:10">
@@ -7396,13 +8939,13 @@
         <v>11</v>
       </c>
       <c r="C181" t="s">
-        <v>644</v>
+        <v>894</v>
       </c>
       <c r="I181" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J181" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="182" spans="1:10">
@@ -7413,13 +8956,13 @@
         <v>11</v>
       </c>
       <c r="C182" t="s">
-        <v>645</v>
+        <v>895</v>
       </c>
       <c r="I182" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J182" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="183" spans="1:10">
@@ -7430,13 +8973,13 @@
         <v>11</v>
       </c>
       <c r="C183" t="s">
-        <v>646</v>
+        <v>896</v>
       </c>
       <c r="I183" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J183" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="184" spans="1:10">
@@ -7447,13 +8990,13 @@
         <v>11</v>
       </c>
       <c r="C184" t="s">
-        <v>647</v>
+        <v>897</v>
       </c>
       <c r="I184" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J184" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="185" spans="1:10">
@@ -7464,13 +9007,13 @@
         <v>11</v>
       </c>
       <c r="C185" t="s">
-        <v>648</v>
+        <v>898</v>
       </c>
       <c r="I185" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J185" t="s">
-        <v>642</v>
+        <v>892</v>
       </c>
     </row>
     <row r="186" spans="1:10">
@@ -7481,13 +9024,13 @@
         <v>11</v>
       </c>
       <c r="C186" t="s">
-        <v>649</v>
+        <v>899</v>
       </c>
       <c r="I186" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J186" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="187" spans="1:10">
@@ -7498,13 +9041,13 @@
         <v>11</v>
       </c>
       <c r="C187" t="s">
-        <v>651</v>
+        <v>901</v>
       </c>
       <c r="I187" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J187" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="188" spans="1:10">
@@ -7515,13 +9058,13 @@
         <v>11</v>
       </c>
       <c r="C188" t="s">
-        <v>652</v>
+        <v>902</v>
       </c>
       <c r="I188" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J188" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="189" spans="1:10">
@@ -7532,13 +9075,13 @@
         <v>11</v>
       </c>
       <c r="C189" t="s">
-        <v>653</v>
+        <v>903</v>
       </c>
       <c r="I189" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J189" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="190" spans="1:10">
@@ -7549,13 +9092,13 @@
         <v>11</v>
       </c>
       <c r="C190" t="s">
-        <v>654</v>
+        <v>904</v>
       </c>
       <c r="I190" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J190" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="191" spans="1:10">
@@ -7566,13 +9109,13 @@
         <v>11</v>
       </c>
       <c r="C191" t="s">
-        <v>655</v>
+        <v>905</v>
       </c>
       <c r="I191" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J191" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="192" spans="1:10">
@@ -7583,13 +9126,13 @@
         <v>11</v>
       </c>
       <c r="C192" t="s">
-        <v>656</v>
+        <v>906</v>
       </c>
       <c r="I192" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J192" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="193" spans="1:10">
@@ -7600,13 +9143,13 @@
         <v>11</v>
       </c>
       <c r="C193" t="s">
-        <v>657</v>
+        <v>907</v>
       </c>
       <c r="I193" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J193" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="194" spans="1:10">
@@ -7617,13 +9160,13 @@
         <v>11</v>
       </c>
       <c r="C194" t="s">
-        <v>658</v>
+        <v>908</v>
       </c>
       <c r="I194" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J194" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="195" spans="1:10">
@@ -7634,13 +9177,13 @@
         <v>11</v>
       </c>
       <c r="C195" t="s">
-        <v>659</v>
+        <v>909</v>
       </c>
       <c r="I195" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J195" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="196" spans="1:10">
@@ -7651,13 +9194,13 @@
         <v>11</v>
       </c>
       <c r="C196" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
       <c r="I196" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J196" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="197" spans="1:10">
@@ -7668,13 +9211,13 @@
         <v>11</v>
       </c>
       <c r="C197" t="s">
-        <v>660</v>
+        <v>910</v>
       </c>
       <c r="I197" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J197" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="198" spans="1:10">
@@ -7685,13 +9228,13 @@
         <v>11</v>
       </c>
       <c r="C198" t="s">
-        <v>661</v>
+        <v>911</v>
       </c>
       <c r="I198" t="s">
-        <v>605</v>
+        <v>855</v>
       </c>
       <c r="J198" t="s">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
